--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCA2F8A2-062C-4A5E-818D-F36E799EB912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6AA809-8049-42EA-B3E7-F9ED9AD5ACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4957,553 +4957,553 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6310,7 +6310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F71509A-80AB-4522-96A3-A8BD878AEDF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2957C43-6129-4450-BEC8-C319C4F7AB33}">
   <dimension ref="B2:AG1155"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32208,7 +32208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EC3923-F16B-4093-80B8-F6FB384C7F53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC707BF1-7D2C-4B44-B8A8-70138F4D15E9}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46685,7 +46685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8872C5F9-50D6-44D4-ACD9-0CA33F90EB55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F34788-4B98-4D6C-9943-809C806CF78B}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48792,7 +48792,7 @@
         <v>1607</v>
       </c>
       <c r="P100" t="s">
-        <v>1570</v>
+        <v>1598</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -48806,7 +48806,7 @@
         <v>1608</v>
       </c>
       <c r="P101" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q101">
         <v>0.95</v>
@@ -48820,10 +48820,10 @@
         <v>1609</v>
       </c>
       <c r="P102" t="s">
-        <v>1560</v>
+        <v>1590</v>
       </c>
       <c r="Q102">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="103" spans="14:17" x14ac:dyDescent="0.45">
@@ -48834,7 +48834,7 @@
         <v>1610</v>
       </c>
       <c r="P103" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -48862,7 +48862,7 @@
         <v>1612</v>
       </c>
       <c r="P105" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -48876,7 +48876,7 @@
         <v>1613</v>
       </c>
       <c r="P106" t="s">
-        <v>1559</v>
+        <v>1568</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -48890,7 +48890,7 @@
         <v>1614</v>
       </c>
       <c r="P107" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -48904,7 +48904,7 @@
         <v>1615</v>
       </c>
       <c r="P108" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -48918,7 +48918,7 @@
         <v>1616</v>
       </c>
       <c r="P109" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="Q109">
         <v>0.85</v>
@@ -48932,7 +48932,7 @@
         <v>1617</v>
       </c>
       <c r="P110" t="s">
-        <v>1594</v>
+        <v>1585</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -48946,7 +48946,7 @@
         <v>1618</v>
       </c>
       <c r="P111" t="s">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -48974,7 +48974,7 @@
         <v>1620</v>
       </c>
       <c r="P113" t="s">
-        <v>1598</v>
+        <v>1580</v>
       </c>
       <c r="Q113">
         <v>0.95</v>
@@ -48988,7 +48988,7 @@
         <v>1621</v>
       </c>
       <c r="P114" t="s">
-        <v>1580</v>
+        <v>1598</v>
       </c>
       <c r="Q114">
         <v>0.95</v>
@@ -49030,7 +49030,7 @@
         <v>1624</v>
       </c>
       <c r="P117" t="s">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -49044,7 +49044,7 @@
         <v>1625</v>
       </c>
       <c r="P118" t="s">
-        <v>1580</v>
+        <v>1599</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -49072,7 +49072,7 @@
         <v>1627</v>
       </c>
       <c r="P120" t="s">
-        <v>1559</v>
+        <v>1580</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -49100,7 +49100,7 @@
         <v>1629</v>
       </c>
       <c r="P122" t="s">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="Q122">
         <v>0.95</v>
@@ -49114,7 +49114,7 @@
         <v>1630</v>
       </c>
       <c r="P123" t="s">
-        <v>1591</v>
+        <v>1603</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -49128,7 +49128,7 @@
         <v>1631</v>
       </c>
       <c r="P124" t="s">
-        <v>1575</v>
+        <v>1587</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -49142,7 +49142,7 @@
         <v>1632</v>
       </c>
       <c r="P125" t="s">
-        <v>1568</v>
+        <v>1593</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -49156,7 +49156,7 @@
         <v>1633</v>
       </c>
       <c r="P126" t="s">
-        <v>1570</v>
+        <v>1606</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -49170,7 +49170,7 @@
         <v>1634</v>
       </c>
       <c r="P127" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -49184,7 +49184,7 @@
         <v>1635</v>
       </c>
       <c r="P128" t="s">
-        <v>1569</v>
+        <v>1598</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -49198,7 +49198,7 @@
         <v>1636</v>
       </c>
       <c r="P129" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="Q129">
         <v>0.85</v>
@@ -49212,7 +49212,7 @@
         <v>1637</v>
       </c>
       <c r="P130" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="Q130">
         <v>0.85</v>
@@ -49226,10 +49226,10 @@
         <v>1638</v>
       </c>
       <c r="P131" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
       <c r="Q131">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -49240,10 +49240,10 @@
         <v>1639</v>
       </c>
       <c r="P132" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q132">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="133" spans="14:17" x14ac:dyDescent="0.45">
@@ -49254,7 +49254,7 @@
         <v>1640</v>
       </c>
       <c r="P133" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -49268,10 +49268,10 @@
         <v>1641</v>
       </c>
       <c r="P134" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q134">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="135" spans="14:17" x14ac:dyDescent="0.45">
@@ -49282,10 +49282,10 @@
         <v>1642</v>
       </c>
       <c r="P135" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q135">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="136" spans="14:17" x14ac:dyDescent="0.45">
@@ -49296,7 +49296,7 @@
         <v>1643</v>
       </c>
       <c r="P136" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -49310,7 +49310,7 @@
         <v>1644</v>
       </c>
       <c r="P137" t="s">
-        <v>1568</v>
+        <v>1593</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -49338,10 +49338,10 @@
         <v>1646</v>
       </c>
       <c r="P139" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="Q139">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="140" spans="14:17" x14ac:dyDescent="0.45">
@@ -49352,10 +49352,10 @@
         <v>1647</v>
       </c>
       <c r="P140" t="s">
-        <v>1568</v>
+        <v>1593</v>
       </c>
       <c r="Q140">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="141" spans="14:17" x14ac:dyDescent="0.45">
@@ -49366,10 +49366,10 @@
         <v>1648</v>
       </c>
       <c r="P141" t="s">
-        <v>1605</v>
+        <v>1569</v>
       </c>
       <c r="Q141">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="142" spans="14:17" x14ac:dyDescent="0.45">
@@ -49380,7 +49380,7 @@
         <v>1649</v>
       </c>
       <c r="P142" t="s">
-        <v>1580</v>
+        <v>1603</v>
       </c>
       <c r="Q142">
         <v>0.85</v>
@@ -49394,7 +49394,7 @@
         <v>1650</v>
       </c>
       <c r="P143" t="s">
-        <v>1585</v>
+        <v>1570</v>
       </c>
       <c r="Q143">
         <v>0.85</v>
@@ -49408,7 +49408,7 @@
         <v>1651</v>
       </c>
       <c r="P144" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="Q144">
         <v>0.85</v>
@@ -49422,7 +49422,7 @@
         <v>1652</v>
       </c>
       <c r="P145" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -49450,7 +49450,7 @@
         <v>1654</v>
       </c>
       <c r="P147" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="Q147">
         <v>0.95</v>
@@ -49464,10 +49464,10 @@
         <v>1655</v>
       </c>
       <c r="P148" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="Q148">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="149" spans="14:17" x14ac:dyDescent="0.45">
@@ -49478,7 +49478,7 @@
         <v>1656</v>
       </c>
       <c r="P149" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -49506,7 +49506,7 @@
         <v>1658</v>
       </c>
       <c r="P151" t="s">
-        <v>1603</v>
+        <v>1565</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -49520,7 +49520,7 @@
         <v>1659</v>
       </c>
       <c r="P152" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -49548,7 +49548,7 @@
         <v>1661</v>
       </c>
       <c r="P154" t="s">
-        <v>1580</v>
+        <v>1603</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -49562,7 +49562,7 @@
         <v>1662</v>
       </c>
       <c r="P155" t="s">
-        <v>1600</v>
+        <v>1580</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -49576,7 +49576,7 @@
         <v>1663</v>
       </c>
       <c r="P156" t="s">
-        <v>1596</v>
+        <v>1575</v>
       </c>
       <c r="Q156">
         <v>0.85</v>
@@ -49590,7 +49590,7 @@
         <v>1664</v>
       </c>
       <c r="P157" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="Q157">
         <v>0.85</v>
@@ -49604,10 +49604,10 @@
         <v>1665</v>
       </c>
       <c r="P158" t="s">
-        <v>1565</v>
+        <v>1606</v>
       </c>
       <c r="Q158">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="159" spans="14:17" x14ac:dyDescent="0.45">
@@ -49618,10 +49618,10 @@
         <v>1666</v>
       </c>
       <c r="P159" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="Q159">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="160" spans="14:17" x14ac:dyDescent="0.45">
@@ -49635,7 +49635,7 @@
         <v>1559</v>
       </c>
       <c r="Q160">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="161" spans="14:17" x14ac:dyDescent="0.45">
@@ -49646,7 +49646,7 @@
         <v>1668</v>
       </c>
       <c r="P161" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -49660,7 +49660,7 @@
         <v>1669</v>
       </c>
       <c r="P162" t="s">
-        <v>1587</v>
+        <v>1575</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -49674,7 +49674,7 @@
         <v>1670</v>
       </c>
       <c r="P163" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -49688,7 +49688,7 @@
         <v>1671</v>
       </c>
       <c r="P164" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -49702,10 +49702,10 @@
         <v>1672</v>
       </c>
       <c r="P165" t="s">
-        <v>1593</v>
+        <v>1565</v>
       </c>
       <c r="Q165">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="166" spans="14:17" x14ac:dyDescent="0.45">
@@ -49716,10 +49716,10 @@
         <v>1673</v>
       </c>
       <c r="P166" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
       <c r="Q166">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="167" spans="14:17" x14ac:dyDescent="0.45">
@@ -49730,10 +49730,10 @@
         <v>1674</v>
       </c>
       <c r="P167" t="s">
-        <v>1590</v>
+        <v>1563</v>
       </c>
       <c r="Q167">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="168" spans="14:17" x14ac:dyDescent="0.45">
@@ -49744,10 +49744,10 @@
         <v>1675</v>
       </c>
       <c r="P168" t="s">
-        <v>1575</v>
+        <v>1605</v>
       </c>
       <c r="Q168">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="169" spans="14:17" x14ac:dyDescent="0.45">
@@ -49758,10 +49758,10 @@
         <v>1676</v>
       </c>
       <c r="P169" t="s">
-        <v>1588</v>
+        <v>1603</v>
       </c>
       <c r="Q169">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="170" spans="14:17" x14ac:dyDescent="0.45">
@@ -49772,10 +49772,10 @@
         <v>1677</v>
       </c>
       <c r="P170" t="s">
-        <v>1561</v>
+        <v>1596</v>
       </c>
       <c r="Q170">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="171" spans="14:17" x14ac:dyDescent="0.45">
@@ -49786,7 +49786,7 @@
         <v>1678</v>
       </c>
       <c r="P171" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -49814,7 +49814,7 @@
         <v>1680</v>
       </c>
       <c r="P173" t="s">
-        <v>1580</v>
+        <v>1559</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -49828,7 +49828,7 @@
         <v>1681</v>
       </c>
       <c r="P174" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -49842,7 +49842,7 @@
         <v>1682</v>
       </c>
       <c r="P175" t="s">
-        <v>1606</v>
+        <v>1575</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -49856,10 +49856,10 @@
         <v>1683</v>
       </c>
       <c r="P176" t="s">
-        <v>1580</v>
+        <v>1605</v>
       </c>
       <c r="Q176">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="177" spans="14:17" x14ac:dyDescent="0.45">
@@ -49870,10 +49870,10 @@
         <v>1684</v>
       </c>
       <c r="P177" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
       <c r="Q177">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="178" spans="14:17" x14ac:dyDescent="0.45">
@@ -49884,10 +49884,10 @@
         <v>1685</v>
       </c>
       <c r="P178" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="Q178">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -49898,10 +49898,10 @@
         <v>1686</v>
       </c>
       <c r="P179" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q179">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -49912,10 +49912,10 @@
         <v>1687</v>
       </c>
       <c r="P180" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="Q180">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -49926,10 +49926,10 @@
         <v>1688</v>
       </c>
       <c r="P181" t="s">
-        <v>1563</v>
+        <v>1606</v>
       </c>
       <c r="Q181">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -49940,7 +49940,7 @@
         <v>1689</v>
       </c>
       <c r="P182" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -49954,7 +49954,7 @@
         <v>1690</v>
       </c>
       <c r="P183" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -49968,7 +49968,7 @@
         <v>1691</v>
       </c>
       <c r="P184" t="s">
-        <v>1569</v>
+        <v>1599</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -49982,7 +49982,7 @@
         <v>1692</v>
       </c>
       <c r="P185" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -49996,7 +49996,7 @@
         <v>1693</v>
       </c>
       <c r="P186" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -50010,10 +50010,10 @@
         <v>1694</v>
       </c>
       <c r="P187" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q187">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -50024,10 +50024,10 @@
         <v>1695</v>
       </c>
       <c r="P188" t="s">
-        <v>1575</v>
+        <v>1561</v>
       </c>
       <c r="Q188">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="189" spans="14:17" x14ac:dyDescent="0.45">
@@ -50038,10 +50038,10 @@
         <v>1696</v>
       </c>
       <c r="P189" t="s">
-        <v>1605</v>
+        <v>1591</v>
       </c>
       <c r="Q189">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="190" spans="14:17" x14ac:dyDescent="0.45">
@@ -50052,10 +50052,10 @@
         <v>1697</v>
       </c>
       <c r="P190" t="s">
-        <v>1569</v>
+        <v>1603</v>
       </c>
       <c r="Q190">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="191" spans="14:17" x14ac:dyDescent="0.45">
@@ -50066,7 +50066,7 @@
         <v>1698</v>
       </c>
       <c r="P191" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -50080,7 +50080,7 @@
         <v>1699</v>
       </c>
       <c r="P192" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -50108,7 +50108,7 @@
         <v>1701</v>
       </c>
       <c r="P194" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="Q194">
         <v>0.85</v>
@@ -50122,7 +50122,7 @@
         <v>1702</v>
       </c>
       <c r="P195" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="Q195">
         <v>0.85</v>
@@ -50136,7 +50136,7 @@
         <v>1703</v>
       </c>
       <c r="P196" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q196">
         <v>0.85</v>
@@ -50150,7 +50150,7 @@
         <v>1704</v>
       </c>
       <c r="P197" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="Q197">
         <v>0.85</v>
@@ -50164,7 +50164,7 @@
         <v>1705</v>
       </c>
       <c r="P198" t="s">
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -50178,7 +50178,7 @@
         <v>1706</v>
       </c>
       <c r="P199" t="s">
-        <v>1575</v>
+        <v>1594</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -50192,7 +50192,7 @@
         <v>1707</v>
       </c>
       <c r="P200" t="s">
-        <v>1583</v>
+        <v>1565</v>
       </c>
       <c r="Q200">
         <v>0.95</v>
@@ -50206,7 +50206,7 @@
         <v>1708</v>
       </c>
       <c r="P201" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="Q201">
         <v>0.95</v>
@@ -50220,10 +50220,10 @@
         <v>1709</v>
       </c>
       <c r="P202" t="s">
-        <v>1606</v>
+        <v>1569</v>
       </c>
       <c r="Q202">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="203" spans="14:17" x14ac:dyDescent="0.45">
@@ -50234,7 +50234,7 @@
         <v>1710</v>
       </c>
       <c r="P203" t="s">
-        <v>1561</v>
+        <v>1605</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -50248,7 +50248,7 @@
         <v>1711</v>
       </c>
       <c r="P204" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -50262,7 +50262,7 @@
         <v>1712</v>
       </c>
       <c r="P205" t="s">
-        <v>1591</v>
+        <v>1572</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -50276,7 +50276,7 @@
         <v>1713</v>
       </c>
       <c r="P206" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="Q206">
         <v>0.85</v>
@@ -50290,7 +50290,7 @@
         <v>1714</v>
       </c>
       <c r="P207" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q207">
         <v>0.85</v>
@@ -50304,7 +50304,7 @@
         <v>1715</v>
       </c>
       <c r="P208" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="Q208">
         <v>0.85</v>
@@ -50318,7 +50318,7 @@
         <v>1716</v>
       </c>
       <c r="P209" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -50332,7 +50332,7 @@
         <v>1717</v>
       </c>
       <c r="P210" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -50346,7 +50346,7 @@
         <v>1718</v>
       </c>
       <c r="P211" t="s">
-        <v>1560</v>
+        <v>1575</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -50360,7 +50360,7 @@
         <v>1719</v>
       </c>
       <c r="P212" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -50374,7 +50374,7 @@
         <v>1720</v>
       </c>
       <c r="P213" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -50388,7 +50388,7 @@
         <v>1721</v>
       </c>
       <c r="P214" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q214">
         <v>0.85</v>
@@ -50402,10 +50402,10 @@
         <v>1722</v>
       </c>
       <c r="P215" t="s">
-        <v>1590</v>
+        <v>1561</v>
       </c>
       <c r="Q215">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -50416,10 +50416,10 @@
         <v>1723</v>
       </c>
       <c r="P216" t="s">
-        <v>1575</v>
+        <v>1588</v>
       </c>
       <c r="Q216">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -50430,10 +50430,10 @@
         <v>1724</v>
       </c>
       <c r="P217" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q217">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -50444,10 +50444,10 @@
         <v>1725</v>
       </c>
       <c r="P218" t="s">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="Q218">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -50458,7 +50458,7 @@
         <v>1726</v>
       </c>
       <c r="P219" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -50472,7 +50472,7 @@
         <v>1727</v>
       </c>
       <c r="P220" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -50486,7 +50486,7 @@
         <v>1728</v>
       </c>
       <c r="P221" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -50500,7 +50500,7 @@
         <v>1729</v>
       </c>
       <c r="P222" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -50514,7 +50514,7 @@
         <v>1730</v>
       </c>
       <c r="P223" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -50528,10 +50528,10 @@
         <v>1731</v>
       </c>
       <c r="P224" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="Q224">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="225" spans="14:17" x14ac:dyDescent="0.45">
@@ -50542,7 +50542,7 @@
         <v>1732</v>
       </c>
       <c r="P225" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="Q225">
         <v>0.95</v>
@@ -50556,7 +50556,7 @@
         <v>1733</v>
       </c>
       <c r="P226" t="s">
-        <v>1586</v>
+        <v>1560</v>
       </c>
       <c r="Q226">
         <v>0.95</v>
@@ -50570,10 +50570,10 @@
         <v>1734</v>
       </c>
       <c r="P227" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="Q227">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="228" spans="14:17" x14ac:dyDescent="0.45">
@@ -50584,7 +50584,7 @@
         <v>1735</v>
       </c>
       <c r="P228" t="s">
-        <v>1605</v>
+        <v>1559</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -50598,7 +50598,7 @@
         <v>1736</v>
       </c>
       <c r="P229" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -50612,7 +50612,7 @@
         <v>1737</v>
       </c>
       <c r="P230" t="s">
-        <v>1605</v>
+        <v>1572</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -50626,7 +50626,7 @@
         <v>1738</v>
       </c>
       <c r="P231" t="s">
-        <v>1575</v>
+        <v>1594</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -50654,7 +50654,7 @@
         <v>1740</v>
       </c>
       <c r="P233" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -50668,7 +50668,7 @@
         <v>1741</v>
       </c>
       <c r="P234" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -50682,7 +50682,7 @@
         <v>1742</v>
       </c>
       <c r="P235" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -50696,7 +50696,7 @@
         <v>1743</v>
       </c>
       <c r="P236" t="s">
-        <v>1603</v>
+        <v>1575</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -50710,10 +50710,10 @@
         <v>1744</v>
       </c>
       <c r="P237" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
       <c r="Q237">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="238" spans="14:17" x14ac:dyDescent="0.45">
@@ -50724,10 +50724,10 @@
         <v>1745</v>
       </c>
       <c r="P238" t="s">
-        <v>1560</v>
+        <v>1583</v>
       </c>
       <c r="Q238">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -50738,7 +50738,7 @@
         <v>1746</v>
       </c>
       <c r="P239" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -50752,10 +50752,10 @@
         <v>1747</v>
       </c>
       <c r="P240" t="s">
-        <v>1569</v>
+        <v>1605</v>
       </c>
       <c r="Q240">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -50766,10 +50766,10 @@
         <v>1748</v>
       </c>
       <c r="P241" t="s">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="Q241">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="242" spans="14:17" x14ac:dyDescent="0.45">
@@ -50780,10 +50780,10 @@
         <v>1749</v>
       </c>
       <c r="P242" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q242">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="243" spans="14:17" x14ac:dyDescent="0.45">
@@ -50794,7 +50794,7 @@
         <v>1750</v>
       </c>
       <c r="P243" t="s">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -50808,7 +50808,7 @@
         <v>1751</v>
       </c>
       <c r="P244" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -50822,7 +50822,7 @@
         <v>1752</v>
       </c>
       <c r="P245" t="s">
-        <v>1570</v>
+        <v>1585</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -50836,7 +50836,7 @@
         <v>1753</v>
       </c>
       <c r="P246" t="s">
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -50850,7 +50850,7 @@
         <v>1754</v>
       </c>
       <c r="P247" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -50864,10 +50864,10 @@
         <v>1755</v>
       </c>
       <c r="P248" t="s">
-        <v>1601</v>
+        <v>1560</v>
       </c>
       <c r="Q248">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="249" spans="14:17" x14ac:dyDescent="0.45">
@@ -50878,7 +50878,7 @@
         <v>1756</v>
       </c>
       <c r="P249" t="s">
-        <v>1593</v>
+        <v>1605</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -50892,7 +50892,7 @@
         <v>1757</v>
       </c>
       <c r="P250" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -50906,7 +50906,7 @@
         <v>1758</v>
       </c>
       <c r="P251" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -50920,7 +50920,7 @@
         <v>1759</v>
       </c>
       <c r="P252" t="s">
-        <v>1603</v>
+        <v>1575</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -50934,7 +50934,7 @@
         <v>1760</v>
       </c>
       <c r="P253" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -50951,7 +50951,7 @@
         <v>1580</v>
       </c>
       <c r="Q254">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="255" spans="14:17" x14ac:dyDescent="0.45">
@@ -50962,10 +50962,10 @@
         <v>1762</v>
       </c>
       <c r="P255" t="s">
-        <v>1565</v>
+        <v>1596</v>
       </c>
       <c r="Q255">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="256" spans="14:17" x14ac:dyDescent="0.45">
@@ -50976,10 +50976,10 @@
         <v>1763</v>
       </c>
       <c r="P256" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q256">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="257" spans="14:17" x14ac:dyDescent="0.45">
@@ -50990,10 +50990,10 @@
         <v>1764</v>
       </c>
       <c r="P257" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q257">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="258" spans="14:17" x14ac:dyDescent="0.45">
@@ -51004,10 +51004,10 @@
         <v>1765</v>
       </c>
       <c r="P258" t="s">
-        <v>1590</v>
+        <v>1602</v>
       </c>
       <c r="Q258">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -51018,7 +51018,7 @@
         <v>1766</v>
       </c>
       <c r="P259" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="Q259">
         <v>0.95</v>
@@ -51032,10 +51032,10 @@
         <v>1767</v>
       </c>
       <c r="P260" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="Q260">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -51046,7 +51046,7 @@
         <v>1768</v>
       </c>
       <c r="P261" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -51060,7 +51060,7 @@
         <v>1769</v>
       </c>
       <c r="P262" t="s">
-        <v>1559</v>
+        <v>1606</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -51074,7 +51074,7 @@
         <v>1770</v>
       </c>
       <c r="P263" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -51088,7 +51088,7 @@
         <v>1771</v>
       </c>
       <c r="P264" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -51102,7 +51102,7 @@
         <v>1772</v>
       </c>
       <c r="P265" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -51116,10 +51116,10 @@
         <v>1773</v>
       </c>
       <c r="P266" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="Q266">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -51130,10 +51130,10 @@
         <v>1774</v>
       </c>
       <c r="P267" t="s">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="Q267">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -51144,10 +51144,10 @@
         <v>1775</v>
       </c>
       <c r="P268" t="s">
-        <v>1580</v>
+        <v>1598</v>
       </c>
       <c r="Q268">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -51158,10 +51158,10 @@
         <v>1776</v>
       </c>
       <c r="P269" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q269">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -51172,10 +51172,10 @@
         <v>1777</v>
       </c>
       <c r="P270" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="Q270">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="271" spans="14:17" x14ac:dyDescent="0.45">
@@ -51186,7 +51186,7 @@
         <v>1778</v>
       </c>
       <c r="P271" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="Q271">
         <v>0.95</v>
@@ -51200,7 +51200,7 @@
         <v>1779</v>
       </c>
       <c r="P272" t="s">
-        <v>1590</v>
+        <v>1575</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -51214,7 +51214,7 @@
         <v>1780</v>
       </c>
       <c r="P273" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -51228,7 +51228,7 @@
         <v>1781</v>
       </c>
       <c r="P274" t="s">
-        <v>1606</v>
+        <v>1570</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -51256,7 +51256,7 @@
         <v>1783</v>
       </c>
       <c r="P276" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -51270,7 +51270,7 @@
         <v>1784</v>
       </c>
       <c r="P277" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -51284,7 +51284,7 @@
         <v>1785</v>
       </c>
       <c r="P278" t="s">
-        <v>1568</v>
+        <v>1606</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -51298,7 +51298,7 @@
         <v>1786</v>
       </c>
       <c r="P279" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -51312,7 +51312,7 @@
         <v>1787</v>
       </c>
       <c r="P280" t="s">
-        <v>1593</v>
+        <v>1569</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -51326,7 +51326,7 @@
         <v>1788</v>
       </c>
       <c r="P281" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -51340,7 +51340,7 @@
         <v>1789</v>
       </c>
       <c r="P282" t="s">
-        <v>1590</v>
+        <v>1569</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -51352,7 +51352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD82B02-CDC8-4E79-A74A-416FDD5EAA5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0730A3F-F4CD-4D06-AB9D-5E2BFEC7FC4B}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6AA809-8049-42EA-B3E7-F9ED9AD5ACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E65846D-BC84-4379-B239-E72CAC8CB30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,15 +4969,18 @@
     <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4987,523 +4990,520 @@
     <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6310,7 +6310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2957C43-6129-4450-BEC8-C319C4F7AB33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227AC0FC-CAA5-4E05-B8B4-A9A5FC20355D}">
   <dimension ref="B2:AG1155"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32208,7 +32208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC707BF1-7D2C-4B44-B8A8-70138F4D15E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D53F73-C4A8-45FA-BF1E-CB84B4349D26}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46685,7 +46685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F34788-4B98-4D6C-9943-809C806CF78B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{701D2331-9B80-40AC-9D05-04D982AA8103}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48848,7 +48848,7 @@
         <v>1611</v>
       </c>
       <c r="P104" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -48862,7 +48862,7 @@
         <v>1612</v>
       </c>
       <c r="P105" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -48890,7 +48890,7 @@
         <v>1614</v>
       </c>
       <c r="P107" t="s">
-        <v>1605</v>
+        <v>1585</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -48904,7 +48904,7 @@
         <v>1615</v>
       </c>
       <c r="P108" t="s">
-        <v>1580</v>
+        <v>1605</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -48932,7 +48932,7 @@
         <v>1617</v>
       </c>
       <c r="P110" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -48974,7 +48974,7 @@
         <v>1620</v>
       </c>
       <c r="P113" t="s">
-        <v>1580</v>
+        <v>1565</v>
       </c>
       <c r="Q113">
         <v>0.95</v>
@@ -48988,7 +48988,7 @@
         <v>1621</v>
       </c>
       <c r="P114" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="Q114">
         <v>0.95</v>
@@ -49002,7 +49002,7 @@
         <v>1622</v>
       </c>
       <c r="P115" t="s">
-        <v>1606</v>
+        <v>1569</v>
       </c>
       <c r="Q115">
         <v>0.95</v>
@@ -49016,7 +49016,7 @@
         <v>1623</v>
       </c>
       <c r="P116" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -49030,7 +49030,7 @@
         <v>1624</v>
       </c>
       <c r="P117" t="s">
-        <v>1559</v>
+        <v>1605</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -49044,7 +49044,7 @@
         <v>1625</v>
       </c>
       <c r="P118" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -49058,7 +49058,7 @@
         <v>1626</v>
       </c>
       <c r="P119" t="s">
-        <v>1580</v>
+        <v>1598</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -49072,7 +49072,7 @@
         <v>1627</v>
       </c>
       <c r="P120" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -49086,7 +49086,7 @@
         <v>1628</v>
       </c>
       <c r="P121" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q121">
         <v>0.85</v>
@@ -49100,10 +49100,10 @@
         <v>1629</v>
       </c>
       <c r="P122" t="s">
-        <v>1559</v>
+        <v>1599</v>
       </c>
       <c r="Q122">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="123" spans="14:17" x14ac:dyDescent="0.45">
@@ -49114,7 +49114,7 @@
         <v>1630</v>
       </c>
       <c r="P123" t="s">
-        <v>1603</v>
+        <v>1575</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -49128,7 +49128,7 @@
         <v>1631</v>
       </c>
       <c r="P124" t="s">
-        <v>1587</v>
+        <v>1560</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -49142,7 +49142,7 @@
         <v>1632</v>
       </c>
       <c r="P125" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -49156,7 +49156,7 @@
         <v>1633</v>
       </c>
       <c r="P126" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -49170,7 +49170,7 @@
         <v>1634</v>
       </c>
       <c r="P127" t="s">
-        <v>1606</v>
+        <v>1575</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -49184,10 +49184,10 @@
         <v>1635</v>
       </c>
       <c r="P128" t="s">
-        <v>1598</v>
+        <v>1563</v>
       </c>
       <c r="Q128">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="129" spans="14:17" x14ac:dyDescent="0.45">
@@ -49198,10 +49198,10 @@
         <v>1636</v>
       </c>
       <c r="P129" t="s">
-        <v>1575</v>
+        <v>1603</v>
       </c>
       <c r="Q129">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -49212,10 +49212,10 @@
         <v>1637</v>
       </c>
       <c r="P130" t="s">
-        <v>1590</v>
+        <v>1565</v>
       </c>
       <c r="Q130">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -49226,7 +49226,7 @@
         <v>1638</v>
       </c>
       <c r="P131" t="s">
-        <v>1571</v>
+        <v>1605</v>
       </c>
       <c r="Q131">
         <v>0.95</v>
@@ -49240,10 +49240,10 @@
         <v>1639</v>
       </c>
       <c r="P132" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q132">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="133" spans="14:17" x14ac:dyDescent="0.45">
@@ -49254,7 +49254,7 @@
         <v>1640</v>
       </c>
       <c r="P133" t="s">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -49282,7 +49282,7 @@
         <v>1642</v>
       </c>
       <c r="P135" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -49296,7 +49296,7 @@
         <v>1643</v>
       </c>
       <c r="P136" t="s">
-        <v>1585</v>
+        <v>1596</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -49310,7 +49310,7 @@
         <v>1644</v>
       </c>
       <c r="P137" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -49338,7 +49338,7 @@
         <v>1646</v>
       </c>
       <c r="P139" t="s">
-        <v>1580</v>
+        <v>1602</v>
       </c>
       <c r="Q139">
         <v>0.95</v>
@@ -49352,7 +49352,7 @@
         <v>1647</v>
       </c>
       <c r="P140" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="Q140">
         <v>0.95</v>
@@ -49366,7 +49366,7 @@
         <v>1648</v>
       </c>
       <c r="P141" t="s">
-        <v>1569</v>
+        <v>1580</v>
       </c>
       <c r="Q141">
         <v>0.95</v>
@@ -49380,10 +49380,10 @@
         <v>1649</v>
       </c>
       <c r="P142" t="s">
-        <v>1603</v>
+        <v>1579</v>
       </c>
       <c r="Q142">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="143" spans="14:17" x14ac:dyDescent="0.45">
@@ -49394,10 +49394,10 @@
         <v>1650</v>
       </c>
       <c r="P143" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="Q143">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="144" spans="14:17" x14ac:dyDescent="0.45">
@@ -49408,10 +49408,10 @@
         <v>1651</v>
       </c>
       <c r="P144" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q144">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="145" spans="14:17" x14ac:dyDescent="0.45">
@@ -49422,7 +49422,7 @@
         <v>1652</v>
       </c>
       <c r="P145" t="s">
-        <v>1599</v>
+        <v>1590</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -49436,7 +49436,7 @@
         <v>1653</v>
       </c>
       <c r="P146" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -49450,10 +49450,10 @@
         <v>1654</v>
       </c>
       <c r="P147" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="Q147">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="148" spans="14:17" x14ac:dyDescent="0.45">
@@ -49464,7 +49464,7 @@
         <v>1655</v>
       </c>
       <c r="P148" t="s">
-        <v>1565</v>
+        <v>1572</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -49478,7 +49478,7 @@
         <v>1656</v>
       </c>
       <c r="P149" t="s">
-        <v>1605</v>
+        <v>1568</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -49492,7 +49492,7 @@
         <v>1657</v>
       </c>
       <c r="P150" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q150">
         <v>0.85</v>
@@ -49506,7 +49506,7 @@
         <v>1658</v>
       </c>
       <c r="P151" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -49520,7 +49520,7 @@
         <v>1659</v>
       </c>
       <c r="P152" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -49534,7 +49534,7 @@
         <v>1660</v>
       </c>
       <c r="P153" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -49548,7 +49548,7 @@
         <v>1661</v>
       </c>
       <c r="P154" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -49562,7 +49562,7 @@
         <v>1662</v>
       </c>
       <c r="P155" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -49576,10 +49576,10 @@
         <v>1663</v>
       </c>
       <c r="P156" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="Q156">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -49590,10 +49590,10 @@
         <v>1664</v>
       </c>
       <c r="P157" t="s">
-        <v>1590</v>
+        <v>1570</v>
       </c>
       <c r="Q157">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -49604,7 +49604,7 @@
         <v>1665</v>
       </c>
       <c r="P158" t="s">
-        <v>1606</v>
+        <v>1560</v>
       </c>
       <c r="Q158">
         <v>0.95</v>
@@ -49618,10 +49618,10 @@
         <v>1666</v>
       </c>
       <c r="P159" t="s">
-        <v>1586</v>
+        <v>1575</v>
       </c>
       <c r="Q159">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="160" spans="14:17" x14ac:dyDescent="0.45">
@@ -49632,7 +49632,7 @@
         <v>1667</v>
       </c>
       <c r="P160" t="s">
-        <v>1559</v>
+        <v>1575</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -49646,7 +49646,7 @@
         <v>1668</v>
       </c>
       <c r="P161" t="s">
-        <v>1606</v>
+        <v>1572</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -49660,7 +49660,7 @@
         <v>1669</v>
       </c>
       <c r="P162" t="s">
-        <v>1575</v>
+        <v>1559</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -49674,7 +49674,7 @@
         <v>1670</v>
       </c>
       <c r="P163" t="s">
-        <v>1598</v>
+        <v>1575</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -49688,7 +49688,7 @@
         <v>1671</v>
       </c>
       <c r="P164" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -49702,10 +49702,10 @@
         <v>1672</v>
       </c>
       <c r="P165" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q165">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="166" spans="14:17" x14ac:dyDescent="0.45">
@@ -49716,10 +49716,10 @@
         <v>1673</v>
       </c>
       <c r="P166" t="s">
-        <v>1603</v>
+        <v>1585</v>
       </c>
       <c r="Q166">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="167" spans="14:17" x14ac:dyDescent="0.45">
@@ -49730,10 +49730,10 @@
         <v>1674</v>
       </c>
       <c r="P167" t="s">
-        <v>1563</v>
+        <v>1594</v>
       </c>
       <c r="Q167">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="168" spans="14:17" x14ac:dyDescent="0.45">
@@ -49744,10 +49744,10 @@
         <v>1675</v>
       </c>
       <c r="P168" t="s">
-        <v>1605</v>
+        <v>1575</v>
       </c>
       <c r="Q168">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="169" spans="14:17" x14ac:dyDescent="0.45">
@@ -49758,10 +49758,10 @@
         <v>1676</v>
       </c>
       <c r="P169" t="s">
-        <v>1603</v>
+        <v>1559</v>
       </c>
       <c r="Q169">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="170" spans="14:17" x14ac:dyDescent="0.45">
@@ -49772,7 +49772,7 @@
         <v>1677</v>
       </c>
       <c r="P170" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="Q170">
         <v>0.85</v>
@@ -49786,7 +49786,7 @@
         <v>1678</v>
       </c>
       <c r="P171" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -49800,7 +49800,7 @@
         <v>1679</v>
       </c>
       <c r="P172" t="s">
-        <v>1569</v>
+        <v>1606</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -49814,7 +49814,7 @@
         <v>1680</v>
       </c>
       <c r="P173" t="s">
-        <v>1559</v>
+        <v>1587</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -49828,7 +49828,7 @@
         <v>1681</v>
       </c>
       <c r="P174" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -49842,7 +49842,7 @@
         <v>1682</v>
       </c>
       <c r="P175" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -49856,10 +49856,10 @@
         <v>1683</v>
       </c>
       <c r="P176" t="s">
-        <v>1605</v>
+        <v>1590</v>
       </c>
       <c r="Q176">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="177" spans="14:17" x14ac:dyDescent="0.45">
@@ -49870,10 +49870,10 @@
         <v>1684</v>
       </c>
       <c r="P177" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="Q177">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="178" spans="14:17" x14ac:dyDescent="0.45">
@@ -49884,10 +49884,10 @@
         <v>1685</v>
       </c>
       <c r="P178" t="s">
-        <v>1606</v>
+        <v>1588</v>
       </c>
       <c r="Q178">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -49898,10 +49898,10 @@
         <v>1686</v>
       </c>
       <c r="P179" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q179">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -49912,7 +49912,7 @@
         <v>1687</v>
       </c>
       <c r="P180" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="Q180">
         <v>0.85</v>
@@ -49926,7 +49926,7 @@
         <v>1688</v>
       </c>
       <c r="P181" t="s">
-        <v>1606</v>
+        <v>1569</v>
       </c>
       <c r="Q181">
         <v>0.85</v>
@@ -49940,7 +49940,7 @@
         <v>1689</v>
       </c>
       <c r="P182" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -49954,7 +49954,7 @@
         <v>1690</v>
       </c>
       <c r="P183" t="s">
-        <v>1606</v>
+        <v>1580</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -49968,7 +49968,7 @@
         <v>1691</v>
       </c>
       <c r="P184" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -49982,7 +49982,7 @@
         <v>1692</v>
       </c>
       <c r="P185" t="s">
-        <v>1569</v>
+        <v>1606</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -49996,7 +49996,7 @@
         <v>1693</v>
       </c>
       <c r="P186" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -50010,7 +50010,7 @@
         <v>1694</v>
       </c>
       <c r="P187" t="s">
-        <v>1603</v>
+        <v>1583</v>
       </c>
       <c r="Q187">
         <v>0.95</v>
@@ -50024,7 +50024,7 @@
         <v>1695</v>
       </c>
       <c r="P188" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="Q188">
         <v>0.95</v>
@@ -50038,7 +50038,7 @@
         <v>1696</v>
       </c>
       <c r="P189" t="s">
-        <v>1591</v>
+        <v>1606</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -50052,7 +50052,7 @@
         <v>1697</v>
       </c>
       <c r="P190" t="s">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -50066,7 +50066,7 @@
         <v>1698</v>
       </c>
       <c r="P191" t="s">
-        <v>1593</v>
+        <v>1561</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -50080,7 +50080,7 @@
         <v>1699</v>
       </c>
       <c r="P192" t="s">
-        <v>1569</v>
+        <v>1591</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -50094,7 +50094,7 @@
         <v>1700</v>
       </c>
       <c r="P193" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="Q193">
         <v>0.85</v>
@@ -50108,7 +50108,7 @@
         <v>1701</v>
       </c>
       <c r="P194" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
       <c r="Q194">
         <v>0.85</v>
@@ -50122,7 +50122,7 @@
         <v>1702</v>
       </c>
       <c r="P195" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="Q195">
         <v>0.85</v>
@@ -50136,7 +50136,7 @@
         <v>1703</v>
       </c>
       <c r="P196" t="s">
-        <v>1580</v>
+        <v>1596</v>
       </c>
       <c r="Q196">
         <v>0.85</v>
@@ -50150,7 +50150,7 @@
         <v>1704</v>
       </c>
       <c r="P197" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q197">
         <v>0.85</v>
@@ -50164,7 +50164,7 @@
         <v>1705</v>
       </c>
       <c r="P198" t="s">
-        <v>1596</v>
+        <v>1570</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -50178,7 +50178,7 @@
         <v>1706</v>
       </c>
       <c r="P199" t="s">
-        <v>1594</v>
+        <v>1605</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -50192,10 +50192,10 @@
         <v>1707</v>
       </c>
       <c r="P200" t="s">
-        <v>1565</v>
+        <v>1585</v>
       </c>
       <c r="Q200">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="201" spans="14:17" x14ac:dyDescent="0.45">
@@ -50206,10 +50206,10 @@
         <v>1708</v>
       </c>
       <c r="P201" t="s">
-        <v>1586</v>
+        <v>1560</v>
       </c>
       <c r="Q201">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="202" spans="14:17" x14ac:dyDescent="0.45">
@@ -50220,10 +50220,10 @@
         <v>1709</v>
       </c>
       <c r="P202" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="Q202">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="203" spans="14:17" x14ac:dyDescent="0.45">
@@ -50234,7 +50234,7 @@
         <v>1710</v>
       </c>
       <c r="P203" t="s">
-        <v>1605</v>
+        <v>1590</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -50248,10 +50248,10 @@
         <v>1711</v>
       </c>
       <c r="P204" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="Q204">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="205" spans="14:17" x14ac:dyDescent="0.45">
@@ -50262,7 +50262,7 @@
         <v>1712</v>
       </c>
       <c r="P205" t="s">
-        <v>1572</v>
+        <v>1605</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -50276,7 +50276,7 @@
         <v>1713</v>
       </c>
       <c r="P206" t="s">
-        <v>1603</v>
+        <v>1593</v>
       </c>
       <c r="Q206">
         <v>0.85</v>
@@ -50290,7 +50290,7 @@
         <v>1714</v>
       </c>
       <c r="P207" t="s">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="Q207">
         <v>0.85</v>
@@ -50304,7 +50304,7 @@
         <v>1715</v>
       </c>
       <c r="P208" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q208">
         <v>0.85</v>
@@ -50318,7 +50318,7 @@
         <v>1716</v>
       </c>
       <c r="P209" t="s">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -50332,7 +50332,7 @@
         <v>1717</v>
       </c>
       <c r="P210" t="s">
-        <v>1560</v>
+        <v>1606</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -50346,7 +50346,7 @@
         <v>1718</v>
       </c>
       <c r="P211" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -50360,7 +50360,7 @@
         <v>1719</v>
       </c>
       <c r="P212" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -50374,7 +50374,7 @@
         <v>1720</v>
       </c>
       <c r="P213" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -50416,7 +50416,7 @@
         <v>1723</v>
       </c>
       <c r="P216" t="s">
-        <v>1588</v>
+        <v>1603</v>
       </c>
       <c r="Q216">
         <v>0.95</v>
@@ -50430,7 +50430,7 @@
         <v>1724</v>
       </c>
       <c r="P217" t="s">
-        <v>1569</v>
+        <v>1591</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -50444,7 +50444,7 @@
         <v>1725</v>
       </c>
       <c r="P218" t="s">
-        <v>1580</v>
+        <v>1603</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -50458,7 +50458,7 @@
         <v>1726</v>
       </c>
       <c r="P219" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -50472,7 +50472,7 @@
         <v>1727</v>
       </c>
       <c r="P220" t="s">
-        <v>1580</v>
+        <v>1596</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -50486,7 +50486,7 @@
         <v>1728</v>
       </c>
       <c r="P221" t="s">
-        <v>1580</v>
+        <v>1600</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -50500,7 +50500,7 @@
         <v>1729</v>
       </c>
       <c r="P222" t="s">
-        <v>1593</v>
+        <v>1565</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -50514,7 +50514,7 @@
         <v>1730</v>
       </c>
       <c r="P223" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -50528,10 +50528,10 @@
         <v>1731</v>
       </c>
       <c r="P224" t="s">
-        <v>1591</v>
+        <v>1606</v>
       </c>
       <c r="Q224">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="225" spans="14:17" x14ac:dyDescent="0.45">
@@ -50542,10 +50542,10 @@
         <v>1732</v>
       </c>
       <c r="P225" t="s">
-        <v>1570</v>
+        <v>1594</v>
       </c>
       <c r="Q225">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="226" spans="14:17" x14ac:dyDescent="0.45">
@@ -50556,10 +50556,10 @@
         <v>1733</v>
       </c>
       <c r="P226" t="s">
-        <v>1560</v>
+        <v>1585</v>
       </c>
       <c r="Q226">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="227" spans="14:17" x14ac:dyDescent="0.45">
@@ -50570,7 +50570,7 @@
         <v>1734</v>
       </c>
       <c r="P227" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -50584,10 +50584,10 @@
         <v>1735</v>
       </c>
       <c r="P228" t="s">
-        <v>1559</v>
+        <v>1605</v>
       </c>
       <c r="Q228">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="229" spans="14:17" x14ac:dyDescent="0.45">
@@ -50598,10 +50598,10 @@
         <v>1736</v>
       </c>
       <c r="P229" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="Q229">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -50612,7 +50612,7 @@
         <v>1737</v>
       </c>
       <c r="P230" t="s">
-        <v>1572</v>
+        <v>1606</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -50626,7 +50626,7 @@
         <v>1738</v>
       </c>
       <c r="P231" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -50640,7 +50640,7 @@
         <v>1739</v>
       </c>
       <c r="P232" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -50654,7 +50654,7 @@
         <v>1740</v>
       </c>
       <c r="P233" t="s">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -50668,7 +50668,7 @@
         <v>1741</v>
       </c>
       <c r="P234" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -50682,7 +50682,7 @@
         <v>1742</v>
       </c>
       <c r="P235" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -50696,7 +50696,7 @@
         <v>1743</v>
       </c>
       <c r="P236" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -50710,10 +50710,10 @@
         <v>1744</v>
       </c>
       <c r="P237" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="Q237">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="238" spans="14:17" x14ac:dyDescent="0.45">
@@ -50724,10 +50724,10 @@
         <v>1745</v>
       </c>
       <c r="P238" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="Q238">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -50738,10 +50738,10 @@
         <v>1746</v>
       </c>
       <c r="P239" t="s">
-        <v>1606</v>
+        <v>1571</v>
       </c>
       <c r="Q239">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="240" spans="14:17" x14ac:dyDescent="0.45">
@@ -50752,10 +50752,10 @@
         <v>1747</v>
       </c>
       <c r="P240" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="Q240">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -50766,7 +50766,7 @@
         <v>1748</v>
       </c>
       <c r="P241" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -50780,7 +50780,7 @@
         <v>1749</v>
       </c>
       <c r="P242" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -50794,7 +50794,7 @@
         <v>1750</v>
       </c>
       <c r="P243" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -50808,7 +50808,7 @@
         <v>1751</v>
       </c>
       <c r="P244" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -50822,7 +50822,7 @@
         <v>1752</v>
       </c>
       <c r="P245" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -50836,7 +50836,7 @@
         <v>1753</v>
       </c>
       <c r="P246" t="s">
-        <v>1596</v>
+        <v>1575</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -50853,7 +50853,7 @@
         <v>1599</v>
       </c>
       <c r="Q247">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -50864,7 +50864,7 @@
         <v>1755</v>
       </c>
       <c r="P248" t="s">
-        <v>1560</v>
+        <v>1591</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -50878,7 +50878,7 @@
         <v>1756</v>
       </c>
       <c r="P249" t="s">
-        <v>1605</v>
+        <v>1570</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -50892,7 +50892,7 @@
         <v>1757</v>
       </c>
       <c r="P250" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -50906,7 +50906,7 @@
         <v>1758</v>
       </c>
       <c r="P251" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -50920,7 +50920,7 @@
         <v>1759</v>
       </c>
       <c r="P252" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -50934,7 +50934,7 @@
         <v>1760</v>
       </c>
       <c r="P253" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -50948,10 +50948,10 @@
         <v>1761</v>
       </c>
       <c r="P254" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
       <c r="Q254">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="255" spans="14:17" x14ac:dyDescent="0.45">
@@ -50962,10 +50962,10 @@
         <v>1762</v>
       </c>
       <c r="P255" t="s">
-        <v>1596</v>
+        <v>1570</v>
       </c>
       <c r="Q255">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="256" spans="14:17" x14ac:dyDescent="0.45">
@@ -50976,10 +50976,10 @@
         <v>1763</v>
       </c>
       <c r="P256" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
       <c r="Q256">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="257" spans="14:17" x14ac:dyDescent="0.45">
@@ -50990,10 +50990,10 @@
         <v>1764</v>
       </c>
       <c r="P257" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="Q257">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="258" spans="14:17" x14ac:dyDescent="0.45">
@@ -51004,10 +51004,10 @@
         <v>1765</v>
       </c>
       <c r="P258" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="Q258">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -51018,7 +51018,7 @@
         <v>1766</v>
       </c>
       <c r="P259" t="s">
-        <v>1579</v>
+        <v>1606</v>
       </c>
       <c r="Q259">
         <v>0.95</v>
@@ -51032,10 +51032,10 @@
         <v>1767</v>
       </c>
       <c r="P260" t="s">
-        <v>1590</v>
+        <v>1586</v>
       </c>
       <c r="Q260">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -51046,7 +51046,7 @@
         <v>1768</v>
       </c>
       <c r="P261" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -51074,7 +51074,7 @@
         <v>1770</v>
       </c>
       <c r="P263" t="s">
-        <v>1568</v>
+        <v>1559</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -51088,7 +51088,7 @@
         <v>1771</v>
       </c>
       <c r="P264" t="s">
-        <v>1591</v>
+        <v>1598</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -51102,7 +51102,7 @@
         <v>1772</v>
       </c>
       <c r="P265" t="s">
-        <v>1568</v>
+        <v>1593</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -51116,10 +51116,10 @@
         <v>1773</v>
       </c>
       <c r="P266" t="s">
-        <v>1572</v>
+        <v>1593</v>
       </c>
       <c r="Q266">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -51130,10 +51130,10 @@
         <v>1774</v>
       </c>
       <c r="P267" t="s">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="Q267">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -51144,10 +51144,10 @@
         <v>1775</v>
       </c>
       <c r="P268" t="s">
-        <v>1598</v>
+        <v>1569</v>
       </c>
       <c r="Q268">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -51158,7 +51158,7 @@
         <v>1776</v>
       </c>
       <c r="P269" t="s">
-        <v>1580</v>
+        <v>1603</v>
       </c>
       <c r="Q269">
         <v>0.85</v>
@@ -51172,7 +51172,7 @@
         <v>1777</v>
       </c>
       <c r="P270" t="s">
-        <v>1590</v>
+        <v>1606</v>
       </c>
       <c r="Q270">
         <v>0.85</v>
@@ -51189,7 +51189,7 @@
         <v>1599</v>
       </c>
       <c r="Q271">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -51200,7 +51200,7 @@
         <v>1779</v>
       </c>
       <c r="P272" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -51214,7 +51214,7 @@
         <v>1780</v>
       </c>
       <c r="P273" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -51228,10 +51228,10 @@
         <v>1781</v>
       </c>
       <c r="P274" t="s">
-        <v>1570</v>
+        <v>1598</v>
       </c>
       <c r="Q274">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="275" spans="14:17" x14ac:dyDescent="0.45">
@@ -51242,10 +51242,10 @@
         <v>1782</v>
       </c>
       <c r="P275" t="s">
-        <v>1591</v>
+        <v>1580</v>
       </c>
       <c r="Q275">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="276" spans="14:17" x14ac:dyDescent="0.45">
@@ -51256,10 +51256,10 @@
         <v>1783</v>
       </c>
       <c r="P276" t="s">
-        <v>1570</v>
+        <v>1606</v>
       </c>
       <c r="Q276">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="277" spans="14:17" x14ac:dyDescent="0.45">
@@ -51270,7 +51270,7 @@
         <v>1784</v>
       </c>
       <c r="P277" t="s">
-        <v>1580</v>
+        <v>1568</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -51284,7 +51284,7 @@
         <v>1785</v>
       </c>
       <c r="P278" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -51298,7 +51298,7 @@
         <v>1786</v>
       </c>
       <c r="P279" t="s">
-        <v>1606</v>
+        <v>1580</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -51312,7 +51312,7 @@
         <v>1787</v>
       </c>
       <c r="P280" t="s">
-        <v>1569</v>
+        <v>1580</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -51326,7 +51326,7 @@
         <v>1788</v>
       </c>
       <c r="P281" t="s">
-        <v>1585</v>
+        <v>1559</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -51340,7 +51340,7 @@
         <v>1789</v>
       </c>
       <c r="P282" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -51352,7 +51352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0730A3F-F4CD-4D06-AB9D-5E2BFEC7FC4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649EF64D-69A6-452E-AC4A-A95CAA3B67A3}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E65846D-BC84-4379-B239-E72CAC8CB30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38DB7BF-E4D0-43E2-B9D5-0CF80C31A74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4957,12 +4957,252 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
   </si>
   <si>
@@ -4972,381 +5212,273 @@
     <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
   </si>
   <si>
@@ -5359,12 +5491,12 @@
     <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
   </si>
   <si>
@@ -5372,138 +5504,6 @@
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6310,7 +6310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227AC0FC-CAA5-4E05-B8B4-A9A5FC20355D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6334AA-6DEB-4110-AC6E-AD77E8657528}">
   <dimension ref="B2:AG1155"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32208,7 +32208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D53F73-C4A8-45FA-BF1E-CB84B4349D26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81F4206-0F1C-4FFF-9913-3AAEA0FBE9E8}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46685,7 +46685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{701D2331-9B80-40AC-9D05-04D982AA8103}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FB3C1E-E9C9-436F-9858-3585D0A8FDE9}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48792,7 +48792,7 @@
         <v>1607</v>
       </c>
       <c r="P100" t="s">
-        <v>1598</v>
+        <v>1569</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -48806,7 +48806,7 @@
         <v>1608</v>
       </c>
       <c r="P101" t="s">
-        <v>1561</v>
+        <v>1586</v>
       </c>
       <c r="Q101">
         <v>0.95</v>
@@ -48820,10 +48820,10 @@
         <v>1609</v>
       </c>
       <c r="P102" t="s">
-        <v>1590</v>
+        <v>1565</v>
       </c>
       <c r="Q102">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="103" spans="14:17" x14ac:dyDescent="0.45">
@@ -48834,7 +48834,7 @@
         <v>1610</v>
       </c>
       <c r="P103" t="s">
-        <v>1568</v>
+        <v>1605</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -48848,7 +48848,7 @@
         <v>1611</v>
       </c>
       <c r="P104" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -48862,7 +48862,7 @@
         <v>1612</v>
       </c>
       <c r="P105" t="s">
-        <v>1575</v>
+        <v>1605</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -48876,7 +48876,7 @@
         <v>1613</v>
       </c>
       <c r="P106" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -48890,7 +48890,7 @@
         <v>1614</v>
       </c>
       <c r="P107" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -48904,7 +48904,7 @@
         <v>1615</v>
       </c>
       <c r="P108" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -48918,7 +48918,7 @@
         <v>1616</v>
       </c>
       <c r="P109" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="Q109">
         <v>0.85</v>
@@ -48932,7 +48932,7 @@
         <v>1617</v>
       </c>
       <c r="P110" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -48946,7 +48946,7 @@
         <v>1618</v>
       </c>
       <c r="P111" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -48960,7 +48960,7 @@
         <v>1619</v>
       </c>
       <c r="P112" t="s">
-        <v>1575</v>
+        <v>1598</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -48974,10 +48974,10 @@
         <v>1620</v>
       </c>
       <c r="P113" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q113">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="114" spans="14:17" x14ac:dyDescent="0.45">
@@ -48988,10 +48988,10 @@
         <v>1621</v>
       </c>
       <c r="P114" t="s">
-        <v>1586</v>
+        <v>1575</v>
       </c>
       <c r="Q114">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="115" spans="14:17" x14ac:dyDescent="0.45">
@@ -49002,7 +49002,7 @@
         <v>1622</v>
       </c>
       <c r="P115" t="s">
-        <v>1569</v>
+        <v>1601</v>
       </c>
       <c r="Q115">
         <v>0.95</v>
@@ -49016,7 +49016,7 @@
         <v>1623</v>
       </c>
       <c r="P116" t="s">
-        <v>1572</v>
+        <v>1605</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -49030,7 +49030,7 @@
         <v>1624</v>
       </c>
       <c r="P117" t="s">
-        <v>1605</v>
+        <v>1565</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -49044,7 +49044,7 @@
         <v>1625</v>
       </c>
       <c r="P118" t="s">
-        <v>1605</v>
+        <v>1593</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -49058,7 +49058,7 @@
         <v>1626</v>
       </c>
       <c r="P119" t="s">
-        <v>1598</v>
+        <v>1580</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -49072,7 +49072,7 @@
         <v>1627</v>
       </c>
       <c r="P120" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -49100,7 +49100,7 @@
         <v>1629</v>
       </c>
       <c r="P122" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q122">
         <v>0.85</v>
@@ -49114,7 +49114,7 @@
         <v>1630</v>
       </c>
       <c r="P123" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -49128,7 +49128,7 @@
         <v>1631</v>
       </c>
       <c r="P124" t="s">
-        <v>1560</v>
+        <v>1590</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -49142,7 +49142,7 @@
         <v>1632</v>
       </c>
       <c r="P125" t="s">
-        <v>1603</v>
+        <v>1575</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -49159,7 +49159,7 @@
         <v>1599</v>
       </c>
       <c r="Q126">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="127" spans="14:17" x14ac:dyDescent="0.45">
@@ -49170,7 +49170,7 @@
         <v>1634</v>
       </c>
       <c r="P127" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -49184,10 +49184,10 @@
         <v>1635</v>
       </c>
       <c r="P128" t="s">
-        <v>1563</v>
+        <v>1575</v>
       </c>
       <c r="Q128">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="129" spans="14:17" x14ac:dyDescent="0.45">
@@ -49198,10 +49198,10 @@
         <v>1636</v>
       </c>
       <c r="P129" t="s">
-        <v>1603</v>
+        <v>1568</v>
       </c>
       <c r="Q129">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -49212,10 +49212,10 @@
         <v>1637</v>
       </c>
       <c r="P130" t="s">
-        <v>1565</v>
+        <v>1591</v>
       </c>
       <c r="Q130">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -49226,10 +49226,10 @@
         <v>1638</v>
       </c>
       <c r="P131" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="Q131">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -49240,7 +49240,7 @@
         <v>1639</v>
       </c>
       <c r="P132" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -49254,7 +49254,7 @@
         <v>1640</v>
       </c>
       <c r="P133" t="s">
-        <v>1559</v>
+        <v>1585</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -49268,7 +49268,7 @@
         <v>1641</v>
       </c>
       <c r="P134" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -49282,7 +49282,7 @@
         <v>1642</v>
       </c>
       <c r="P135" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -49296,7 +49296,7 @@
         <v>1643</v>
       </c>
       <c r="P136" t="s">
-        <v>1596</v>
+        <v>1580</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -49310,7 +49310,7 @@
         <v>1644</v>
       </c>
       <c r="P137" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -49324,10 +49324,10 @@
         <v>1645</v>
       </c>
       <c r="P138" t="s">
-        <v>1575</v>
+        <v>1561</v>
       </c>
       <c r="Q138">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="139" spans="14:17" x14ac:dyDescent="0.45">
@@ -49338,7 +49338,7 @@
         <v>1646</v>
       </c>
       <c r="P139" t="s">
-        <v>1602</v>
+        <v>1588</v>
       </c>
       <c r="Q139">
         <v>0.95</v>
@@ -49352,10 +49352,10 @@
         <v>1647</v>
       </c>
       <c r="P140" t="s">
-        <v>1596</v>
+        <v>1585</v>
       </c>
       <c r="Q140">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="141" spans="14:17" x14ac:dyDescent="0.45">
@@ -49369,7 +49369,7 @@
         <v>1580</v>
       </c>
       <c r="Q141">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="142" spans="14:17" x14ac:dyDescent="0.45">
@@ -49380,10 +49380,10 @@
         <v>1649</v>
       </c>
       <c r="P142" t="s">
-        <v>1579</v>
+        <v>1569</v>
       </c>
       <c r="Q142">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="143" spans="14:17" x14ac:dyDescent="0.45">
@@ -49397,7 +49397,7 @@
         <v>1580</v>
       </c>
       <c r="Q143">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="144" spans="14:17" x14ac:dyDescent="0.45">
@@ -49408,10 +49408,10 @@
         <v>1651</v>
       </c>
       <c r="P144" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="Q144">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="145" spans="14:17" x14ac:dyDescent="0.45">
@@ -49422,7 +49422,7 @@
         <v>1652</v>
       </c>
       <c r="P145" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -49436,7 +49436,7 @@
         <v>1653</v>
       </c>
       <c r="P146" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -49450,10 +49450,10 @@
         <v>1654</v>
       </c>
       <c r="P147" t="s">
-        <v>1606</v>
+        <v>1583</v>
       </c>
       <c r="Q147">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="148" spans="14:17" x14ac:dyDescent="0.45">
@@ -49464,10 +49464,10 @@
         <v>1655</v>
       </c>
       <c r="P148" t="s">
-        <v>1572</v>
+        <v>1583</v>
       </c>
       <c r="Q148">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="149" spans="14:17" x14ac:dyDescent="0.45">
@@ -49478,7 +49478,7 @@
         <v>1656</v>
       </c>
       <c r="P149" t="s">
-        <v>1568</v>
+        <v>1606</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -49492,7 +49492,7 @@
         <v>1657</v>
       </c>
       <c r="P150" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q150">
         <v>0.85</v>
@@ -49506,7 +49506,7 @@
         <v>1658</v>
       </c>
       <c r="P151" t="s">
-        <v>1568</v>
+        <v>1591</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -49520,7 +49520,7 @@
         <v>1659</v>
       </c>
       <c r="P152" t="s">
-        <v>1580</v>
+        <v>1605</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -49548,7 +49548,7 @@
         <v>1661</v>
       </c>
       <c r="P154" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -49562,7 +49562,7 @@
         <v>1662</v>
       </c>
       <c r="P155" t="s">
-        <v>1590</v>
+        <v>1570</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -49576,10 +49576,10 @@
         <v>1663</v>
       </c>
       <c r="P156" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q156">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -49590,10 +49590,10 @@
         <v>1664</v>
       </c>
       <c r="P157" t="s">
-        <v>1570</v>
+        <v>1599</v>
       </c>
       <c r="Q157">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -49604,10 +49604,10 @@
         <v>1665</v>
       </c>
       <c r="P158" t="s">
-        <v>1560</v>
+        <v>1585</v>
       </c>
       <c r="Q158">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="159" spans="14:17" x14ac:dyDescent="0.45">
@@ -49618,7 +49618,7 @@
         <v>1666</v>
       </c>
       <c r="P159" t="s">
-        <v>1575</v>
+        <v>1596</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -49632,7 +49632,7 @@
         <v>1667</v>
       </c>
       <c r="P160" t="s">
-        <v>1575</v>
+        <v>1560</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -49646,7 +49646,7 @@
         <v>1668</v>
       </c>
       <c r="P161" t="s">
-        <v>1572</v>
+        <v>1605</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -49660,7 +49660,7 @@
         <v>1669</v>
       </c>
       <c r="P162" t="s">
-        <v>1559</v>
+        <v>1590</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -49688,10 +49688,10 @@
         <v>1671</v>
       </c>
       <c r="P164" t="s">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="Q164">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="165" spans="14:17" x14ac:dyDescent="0.45">
@@ -49702,7 +49702,7 @@
         <v>1672</v>
       </c>
       <c r="P165" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q165">
         <v>0.85</v>
@@ -49716,7 +49716,7 @@
         <v>1673</v>
       </c>
       <c r="P166" t="s">
-        <v>1585</v>
+        <v>1598</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -49730,7 +49730,7 @@
         <v>1674</v>
       </c>
       <c r="P167" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="Q167">
         <v>0.85</v>
@@ -49744,7 +49744,7 @@
         <v>1675</v>
       </c>
       <c r="P168" t="s">
-        <v>1575</v>
+        <v>1593</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -49758,10 +49758,10 @@
         <v>1676</v>
       </c>
       <c r="P169" t="s">
-        <v>1559</v>
+        <v>1606</v>
       </c>
       <c r="Q169">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="170" spans="14:17" x14ac:dyDescent="0.45">
@@ -49772,7 +49772,7 @@
         <v>1677</v>
       </c>
       <c r="P170" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="Q170">
         <v>0.85</v>
@@ -49786,7 +49786,7 @@
         <v>1678</v>
       </c>
       <c r="P171" t="s">
-        <v>1598</v>
+        <v>1575</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -49800,7 +49800,7 @@
         <v>1679</v>
       </c>
       <c r="P172" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -49814,10 +49814,10 @@
         <v>1680</v>
       </c>
       <c r="P173" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="Q173">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="174" spans="14:17" x14ac:dyDescent="0.45">
@@ -49828,10 +49828,10 @@
         <v>1681</v>
       </c>
       <c r="P174" t="s">
-        <v>1593</v>
+        <v>1606</v>
       </c>
       <c r="Q174">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="175" spans="14:17" x14ac:dyDescent="0.45">
@@ -49842,7 +49842,7 @@
         <v>1682</v>
       </c>
       <c r="P175" t="s">
-        <v>1606</v>
+        <v>1575</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -49856,7 +49856,7 @@
         <v>1683</v>
       </c>
       <c r="P176" t="s">
-        <v>1590</v>
+        <v>1559</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -49870,7 +49870,7 @@
         <v>1684</v>
       </c>
       <c r="P177" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="Q177">
         <v>0.85</v>
@@ -49884,10 +49884,10 @@
         <v>1685</v>
       </c>
       <c r="P178" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="Q178">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -49898,10 +49898,10 @@
         <v>1686</v>
       </c>
       <c r="P179" t="s">
-        <v>1561</v>
+        <v>1598</v>
       </c>
       <c r="Q179">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -49912,10 +49912,10 @@
         <v>1687</v>
       </c>
       <c r="P180" t="s">
-        <v>1593</v>
+        <v>1561</v>
       </c>
       <c r="Q180">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -49926,10 +49926,10 @@
         <v>1688</v>
       </c>
       <c r="P181" t="s">
-        <v>1569</v>
+        <v>1598</v>
       </c>
       <c r="Q181">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -49940,7 +49940,7 @@
         <v>1689</v>
       </c>
       <c r="P182" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -49954,7 +49954,7 @@
         <v>1690</v>
       </c>
       <c r="P183" t="s">
-        <v>1580</v>
+        <v>1568</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -49968,7 +49968,7 @@
         <v>1691</v>
       </c>
       <c r="P184" t="s">
-        <v>1585</v>
+        <v>1568</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -49982,7 +49982,7 @@
         <v>1692</v>
       </c>
       <c r="P185" t="s">
-        <v>1606</v>
+        <v>1568</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -49996,7 +49996,7 @@
         <v>1693</v>
       </c>
       <c r="P186" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -50010,10 +50010,10 @@
         <v>1694</v>
       </c>
       <c r="P187" t="s">
-        <v>1583</v>
+        <v>1600</v>
       </c>
       <c r="Q187">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -50024,10 +50024,10 @@
         <v>1695</v>
       </c>
       <c r="P188" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="Q188">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="189" spans="14:17" x14ac:dyDescent="0.45">
@@ -50038,7 +50038,7 @@
         <v>1696</v>
       </c>
       <c r="P189" t="s">
-        <v>1606</v>
+        <v>1580</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -50052,7 +50052,7 @@
         <v>1697</v>
       </c>
       <c r="P190" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -50066,7 +50066,7 @@
         <v>1698</v>
       </c>
       <c r="P191" t="s">
-        <v>1561</v>
+        <v>1580</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -50080,7 +50080,7 @@
         <v>1699</v>
       </c>
       <c r="P192" t="s">
-        <v>1591</v>
+        <v>1575</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -50094,10 +50094,10 @@
         <v>1700</v>
       </c>
       <c r="P193" t="s">
-        <v>1605</v>
+        <v>1561</v>
       </c>
       <c r="Q193">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="194" spans="14:17" x14ac:dyDescent="0.45">
@@ -50108,10 +50108,10 @@
         <v>1701</v>
       </c>
       <c r="P194" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="Q194">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="195" spans="14:17" x14ac:dyDescent="0.45">
@@ -50122,7 +50122,7 @@
         <v>1702</v>
       </c>
       <c r="P195" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q195">
         <v>0.85</v>
@@ -50136,7 +50136,7 @@
         <v>1703</v>
       </c>
       <c r="P196" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="Q196">
         <v>0.85</v>
@@ -50150,7 +50150,7 @@
         <v>1704</v>
       </c>
       <c r="P197" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q197">
         <v>0.85</v>
@@ -50164,7 +50164,7 @@
         <v>1705</v>
       </c>
       <c r="P198" t="s">
-        <v>1570</v>
+        <v>1585</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -50178,7 +50178,7 @@
         <v>1706</v>
       </c>
       <c r="P199" t="s">
-        <v>1605</v>
+        <v>1594</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -50192,7 +50192,7 @@
         <v>1707</v>
       </c>
       <c r="P200" t="s">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="Q200">
         <v>0.85</v>
@@ -50206,7 +50206,7 @@
         <v>1708</v>
       </c>
       <c r="P201" t="s">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -50220,7 +50220,7 @@
         <v>1709</v>
       </c>
       <c r="P202" t="s">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -50234,7 +50234,7 @@
         <v>1710</v>
       </c>
       <c r="P203" t="s">
-        <v>1590</v>
+        <v>1596</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -50248,10 +50248,10 @@
         <v>1711</v>
       </c>
       <c r="P204" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="Q204">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="205" spans="14:17" x14ac:dyDescent="0.45">
@@ -50262,7 +50262,7 @@
         <v>1712</v>
       </c>
       <c r="P205" t="s">
-        <v>1605</v>
+        <v>1580</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -50276,10 +50276,10 @@
         <v>1713</v>
       </c>
       <c r="P206" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="Q206">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="207" spans="14:17" x14ac:dyDescent="0.45">
@@ -50290,10 +50290,10 @@
         <v>1714</v>
       </c>
       <c r="P207" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q207">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="208" spans="14:17" x14ac:dyDescent="0.45">
@@ -50304,10 +50304,10 @@
         <v>1715</v>
       </c>
       <c r="P208" t="s">
-        <v>1603</v>
+        <v>1580</v>
       </c>
       <c r="Q208">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="209" spans="14:17" x14ac:dyDescent="0.45">
@@ -50318,10 +50318,10 @@
         <v>1716</v>
       </c>
       <c r="P209" t="s">
-        <v>1565</v>
+        <v>1579</v>
       </c>
       <c r="Q209">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="210" spans="14:17" x14ac:dyDescent="0.45">
@@ -50332,10 +50332,10 @@
         <v>1717</v>
       </c>
       <c r="P210" t="s">
-        <v>1606</v>
+        <v>1580</v>
       </c>
       <c r="Q210">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="211" spans="14:17" x14ac:dyDescent="0.45">
@@ -50346,10 +50346,10 @@
         <v>1718</v>
       </c>
       <c r="P211" t="s">
-        <v>1580</v>
+        <v>1602</v>
       </c>
       <c r="Q211">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="212" spans="14:17" x14ac:dyDescent="0.45">
@@ -50388,7 +50388,7 @@
         <v>1721</v>
       </c>
       <c r="P214" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="Q214">
         <v>0.85</v>
@@ -50402,10 +50402,10 @@
         <v>1722</v>
       </c>
       <c r="P215" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="Q215">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -50416,10 +50416,10 @@
         <v>1723</v>
       </c>
       <c r="P216" t="s">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="Q216">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -50430,7 +50430,7 @@
         <v>1724</v>
       </c>
       <c r="P217" t="s">
-        <v>1591</v>
+        <v>1568</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -50444,7 +50444,7 @@
         <v>1725</v>
       </c>
       <c r="P218" t="s">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -50458,7 +50458,7 @@
         <v>1726</v>
       </c>
       <c r="P219" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -50472,7 +50472,7 @@
         <v>1727</v>
       </c>
       <c r="P220" t="s">
-        <v>1596</v>
+        <v>1580</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -50486,7 +50486,7 @@
         <v>1728</v>
       </c>
       <c r="P221" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -50500,7 +50500,7 @@
         <v>1729</v>
       </c>
       <c r="P222" t="s">
-        <v>1565</v>
+        <v>1590</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -50514,10 +50514,10 @@
         <v>1730</v>
       </c>
       <c r="P223" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="Q223">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="224" spans="14:17" x14ac:dyDescent="0.45">
@@ -50528,10 +50528,10 @@
         <v>1731</v>
       </c>
       <c r="P224" t="s">
-        <v>1606</v>
+        <v>1580</v>
       </c>
       <c r="Q224">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="225" spans="14:17" x14ac:dyDescent="0.45">
@@ -50542,10 +50542,10 @@
         <v>1732</v>
       </c>
       <c r="P225" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="Q225">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="226" spans="14:17" x14ac:dyDescent="0.45">
@@ -50556,7 +50556,7 @@
         <v>1733</v>
       </c>
       <c r="P226" t="s">
-        <v>1585</v>
+        <v>1568</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -50570,7 +50570,7 @@
         <v>1734</v>
       </c>
       <c r="P227" t="s">
-        <v>1569</v>
+        <v>1580</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -50584,10 +50584,10 @@
         <v>1735</v>
       </c>
       <c r="P228" t="s">
-        <v>1605</v>
+        <v>1580</v>
       </c>
       <c r="Q228">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="229" spans="14:17" x14ac:dyDescent="0.45">
@@ -50598,10 +50598,10 @@
         <v>1736</v>
       </c>
       <c r="P229" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="Q229">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -50612,7 +50612,7 @@
         <v>1737</v>
       </c>
       <c r="P230" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -50626,7 +50626,7 @@
         <v>1738</v>
       </c>
       <c r="P231" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -50640,10 +50640,10 @@
         <v>1739</v>
       </c>
       <c r="P232" t="s">
-        <v>1606</v>
+        <v>1563</v>
       </c>
       <c r="Q232">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="233" spans="14:17" x14ac:dyDescent="0.45">
@@ -50654,10 +50654,10 @@
         <v>1740</v>
       </c>
       <c r="P233" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="Q233">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -50668,10 +50668,10 @@
         <v>1741</v>
       </c>
       <c r="P234" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="Q234">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -50682,10 +50682,10 @@
         <v>1742</v>
       </c>
       <c r="P235" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="Q235">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="236" spans="14:17" x14ac:dyDescent="0.45">
@@ -50696,7 +50696,7 @@
         <v>1743</v>
       </c>
       <c r="P236" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -50724,7 +50724,7 @@
         <v>1745</v>
       </c>
       <c r="P238" t="s">
-        <v>1575</v>
+        <v>1559</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -50738,10 +50738,10 @@
         <v>1746</v>
       </c>
       <c r="P239" t="s">
-        <v>1571</v>
+        <v>1599</v>
       </c>
       <c r="Q239">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="240" spans="14:17" x14ac:dyDescent="0.45">
@@ -50752,10 +50752,10 @@
         <v>1747</v>
       </c>
       <c r="P240" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="Q240">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -50766,7 +50766,7 @@
         <v>1748</v>
       </c>
       <c r="P241" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -50780,7 +50780,7 @@
         <v>1749</v>
       </c>
       <c r="P242" t="s">
-        <v>1593</v>
+        <v>1575</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -50794,10 +50794,10 @@
         <v>1750</v>
       </c>
       <c r="P243" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="Q243">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -50808,10 +50808,10 @@
         <v>1751</v>
       </c>
       <c r="P244" t="s">
-        <v>1599</v>
+        <v>1571</v>
       </c>
       <c r="Q244">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -50822,7 +50822,7 @@
         <v>1752</v>
       </c>
       <c r="P245" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -50836,7 +50836,7 @@
         <v>1753</v>
       </c>
       <c r="P246" t="s">
-        <v>1575</v>
+        <v>1599</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -50850,10 +50850,10 @@
         <v>1754</v>
       </c>
       <c r="P247" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="Q247">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -50864,7 +50864,7 @@
         <v>1755</v>
       </c>
       <c r="P248" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -50878,7 +50878,7 @@
         <v>1756</v>
       </c>
       <c r="P249" t="s">
-        <v>1570</v>
+        <v>1599</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -50906,10 +50906,10 @@
         <v>1758</v>
       </c>
       <c r="P251" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="Q251">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="252" spans="14:17" x14ac:dyDescent="0.45">
@@ -50920,10 +50920,10 @@
         <v>1759</v>
       </c>
       <c r="P252" t="s">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="Q252">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="253" spans="14:17" x14ac:dyDescent="0.45">
@@ -50934,10 +50934,10 @@
         <v>1760</v>
       </c>
       <c r="P253" t="s">
-        <v>1585</v>
+        <v>1591</v>
       </c>
       <c r="Q253">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="254" spans="14:17" x14ac:dyDescent="0.45">
@@ -50948,7 +50948,7 @@
         <v>1761</v>
       </c>
       <c r="P254" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -50962,7 +50962,7 @@
         <v>1762</v>
       </c>
       <c r="P255" t="s">
-        <v>1570</v>
+        <v>1559</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -50976,7 +50976,7 @@
         <v>1763</v>
       </c>
       <c r="P256" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -50990,7 +50990,7 @@
         <v>1764</v>
       </c>
       <c r="P257" t="s">
-        <v>1606</v>
+        <v>1572</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -51004,7 +51004,7 @@
         <v>1765</v>
       </c>
       <c r="P258" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q258">
         <v>0.85</v>
@@ -51018,10 +51018,10 @@
         <v>1766</v>
       </c>
       <c r="P259" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="Q259">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="260" spans="14:17" x14ac:dyDescent="0.45">
@@ -51032,10 +51032,10 @@
         <v>1767</v>
       </c>
       <c r="P260" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="Q260">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -51060,7 +51060,7 @@
         <v>1769</v>
       </c>
       <c r="P262" t="s">
-        <v>1606</v>
+        <v>1594</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -51074,7 +51074,7 @@
         <v>1770</v>
       </c>
       <c r="P263" t="s">
-        <v>1559</v>
+        <v>1575</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -51088,10 +51088,10 @@
         <v>1771</v>
       </c>
       <c r="P264" t="s">
-        <v>1598</v>
+        <v>1569</v>
       </c>
       <c r="Q264">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="265" spans="14:17" x14ac:dyDescent="0.45">
@@ -51105,7 +51105,7 @@
         <v>1593</v>
       </c>
       <c r="Q265">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="266" spans="14:17" x14ac:dyDescent="0.45">
@@ -51116,7 +51116,7 @@
         <v>1773</v>
       </c>
       <c r="P266" t="s">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="Q266">
         <v>0.95</v>
@@ -51130,10 +51130,10 @@
         <v>1774</v>
       </c>
       <c r="P267" t="s">
-        <v>1580</v>
+        <v>1603</v>
       </c>
       <c r="Q267">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -51144,10 +51144,10 @@
         <v>1775</v>
       </c>
       <c r="P268" t="s">
-        <v>1569</v>
+        <v>1606</v>
       </c>
       <c r="Q268">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -51158,7 +51158,7 @@
         <v>1776</v>
       </c>
       <c r="P269" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="Q269">
         <v>0.85</v>
@@ -51172,7 +51172,7 @@
         <v>1777</v>
       </c>
       <c r="P270" t="s">
-        <v>1606</v>
+        <v>1570</v>
       </c>
       <c r="Q270">
         <v>0.85</v>
@@ -51186,7 +51186,7 @@
         <v>1778</v>
       </c>
       <c r="P271" t="s">
-        <v>1599</v>
+        <v>1575</v>
       </c>
       <c r="Q271">
         <v>0.85</v>
@@ -51200,10 +51200,10 @@
         <v>1779</v>
       </c>
       <c r="P272" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="Q272">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="273" spans="14:17" x14ac:dyDescent="0.45">
@@ -51214,10 +51214,10 @@
         <v>1780</v>
       </c>
       <c r="P273" t="s">
-        <v>1575</v>
+        <v>1605</v>
       </c>
       <c r="Q273">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="274" spans="14:17" x14ac:dyDescent="0.45">
@@ -51228,10 +51228,10 @@
         <v>1781</v>
       </c>
       <c r="P274" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="Q274">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="275" spans="14:17" x14ac:dyDescent="0.45">
@@ -51242,10 +51242,10 @@
         <v>1782</v>
       </c>
       <c r="P275" t="s">
-        <v>1580</v>
+        <v>1599</v>
       </c>
       <c r="Q275">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="276" spans="14:17" x14ac:dyDescent="0.45">
@@ -51259,7 +51259,7 @@
         <v>1606</v>
       </c>
       <c r="Q276">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="277" spans="14:17" x14ac:dyDescent="0.45">
@@ -51270,7 +51270,7 @@
         <v>1784</v>
       </c>
       <c r="P277" t="s">
-        <v>1568</v>
+        <v>1606</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -51284,7 +51284,7 @@
         <v>1785</v>
       </c>
       <c r="P278" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -51298,7 +51298,7 @@
         <v>1786</v>
       </c>
       <c r="P279" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -51312,7 +51312,7 @@
         <v>1787</v>
       </c>
       <c r="P280" t="s">
-        <v>1580</v>
+        <v>1599</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -51326,7 +51326,7 @@
         <v>1788</v>
       </c>
       <c r="P281" t="s">
-        <v>1559</v>
+        <v>1599</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -51352,7 +51352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649EF64D-69A6-452E-AC4A-A95CAA3B67A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA5939E-BE1C-4713-8488-AE699EBA0304}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E4E673-8111-44EE-A6C9-979E3296C138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F8A534-937E-4D89-B758-E1F73C45A494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4885,10 +4885,43 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
@@ -4897,130 +4930,427 @@
     <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
@@ -5032,292 +5362,34 @@
     <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
@@ -5329,109 +5401,37 @@
     <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6384,7 +6384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2F5E9D-6D5D-4AB4-976A-C3D8952AFE44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0872980-9B2C-4AD1-BD2E-1DD37C883FBE}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37571,7 +37571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A220FE72-B626-4B23-A197-0FD16673BB37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F28A15-493B-40B8-9341-E710AC6D6220}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51830,7 +51830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB99CB9-A901-4738-93FF-11B732CD0B02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19012F33-A961-49DF-AEEA-C774816E1DEE}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53937,7 +53937,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1581</v>
+        <v>1552</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53951,10 +53951,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1554</v>
+        <v>1596</v>
       </c>
       <c r="Q101">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53965,7 +53965,7 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1562</v>
+        <v>1591</v>
       </c>
       <c r="Q102">
         <v>0.85</v>
@@ -53979,7 +53979,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1573</v>
+        <v>1580</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53993,7 +53993,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54007,7 +54007,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54021,7 +54021,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54035,7 +54035,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54049,7 +54049,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54077,7 +54077,7 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1591</v>
+        <v>1581</v>
       </c>
       <c r="Q110">
         <v>0.95</v>
@@ -54091,7 +54091,7 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -54105,7 +54105,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1561</v>
+        <v>1586</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54119,7 +54119,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54133,7 +54133,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54147,7 +54147,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54161,7 +54161,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54175,7 +54175,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54189,10 +54189,10 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="Q118">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="119" spans="14:17" x14ac:dyDescent="0.45">
@@ -54203,10 +54203,10 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="Q119">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="120" spans="14:17" x14ac:dyDescent="0.45">
@@ -54217,10 +54217,10 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1573</v>
+        <v>1553</v>
       </c>
       <c r="Q120">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="121" spans="14:17" x14ac:dyDescent="0.45">
@@ -54245,10 +54245,10 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q122">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="123" spans="14:17" x14ac:dyDescent="0.45">
@@ -54259,10 +54259,10 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1591</v>
+        <v>1565</v>
       </c>
       <c r="Q123">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="124" spans="14:17" x14ac:dyDescent="0.45">
@@ -54273,10 +54273,10 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1573</v>
+        <v>1552</v>
       </c>
       <c r="Q124">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="125" spans="14:17" x14ac:dyDescent="0.45">
@@ -54287,7 +54287,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54301,7 +54301,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54315,7 +54315,7 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1552</v>
+        <v>1592</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -54329,7 +54329,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54343,7 +54343,7 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q129">
         <v>0.85</v>
@@ -54371,7 +54371,7 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="Q131">
         <v>0.95</v>
@@ -54385,10 +54385,10 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1599</v>
+        <v>1563</v>
       </c>
       <c r="Q132">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="133" spans="14:17" x14ac:dyDescent="0.45">
@@ -54399,7 +54399,7 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -54413,7 +54413,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54427,7 +54427,7 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -54441,7 +54441,7 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1591</v>
+        <v>1562</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -54455,7 +54455,7 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -54469,10 +54469,10 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q138">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="139" spans="14:17" x14ac:dyDescent="0.45">
@@ -54483,10 +54483,10 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1586</v>
+        <v>1563</v>
       </c>
       <c r="Q139">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="140" spans="14:17" x14ac:dyDescent="0.45">
@@ -54497,10 +54497,10 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="Q140">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="141" spans="14:17" x14ac:dyDescent="0.45">
@@ -54511,7 +54511,7 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="Q141">
         <v>0.85</v>
@@ -54539,10 +54539,10 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="Q143">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="144" spans="14:17" x14ac:dyDescent="0.45">
@@ -54553,10 +54553,10 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q144">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="145" spans="14:17" x14ac:dyDescent="0.45">
@@ -54567,10 +54567,10 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q145">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="146" spans="14:17" x14ac:dyDescent="0.45">
@@ -54595,7 +54595,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54623,7 +54623,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1599</v>
+        <v>1562</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54637,7 +54637,7 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q150">
         <v>0.85</v>
@@ -54651,7 +54651,7 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -54665,7 +54665,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1599</v>
+        <v>1589</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54679,7 +54679,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54693,10 +54693,10 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1592</v>
+        <v>1554</v>
       </c>
       <c r="Q154">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="155" spans="14:17" x14ac:dyDescent="0.45">
@@ -54707,10 +54707,10 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1568</v>
+        <v>1596</v>
       </c>
       <c r="Q155">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="156" spans="14:17" x14ac:dyDescent="0.45">
@@ -54721,10 +54721,10 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="Q156">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -54735,10 +54735,10 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1596</v>
+        <v>1586</v>
       </c>
       <c r="Q157">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -54749,7 +54749,7 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="Q158">
         <v>0.85</v>
@@ -54763,7 +54763,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -54777,7 +54777,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54791,7 +54791,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54805,7 +54805,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1578</v>
+        <v>1589</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54833,7 +54833,7 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1589</v>
+        <v>1578</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -54847,7 +54847,7 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1587</v>
+        <v>1593</v>
       </c>
       <c r="Q165">
         <v>0.85</v>
@@ -54861,7 +54861,7 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1593</v>
+        <v>1562</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -54875,10 +54875,10 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="Q167">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="168" spans="14:17" x14ac:dyDescent="0.45">
@@ -54889,10 +54889,10 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q168">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="169" spans="14:17" x14ac:dyDescent="0.45">
@@ -54903,10 +54903,10 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1554</v>
+        <v>1578</v>
       </c>
       <c r="Q169">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="170" spans="14:17" x14ac:dyDescent="0.45">
@@ -54917,10 +54917,10 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q170">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="171" spans="14:17" x14ac:dyDescent="0.45">
@@ -54931,10 +54931,10 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q171">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="172" spans="14:17" x14ac:dyDescent="0.45">
@@ -54945,7 +54945,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54959,7 +54959,7 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -54973,7 +54973,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -54987,10 +54987,10 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q175">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="176" spans="14:17" x14ac:dyDescent="0.45">
@@ -55001,7 +55001,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -55015,7 +55015,7 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
       <c r="Q177">
         <v>0.85</v>
@@ -55029,7 +55029,7 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1563</v>
+        <v>1552</v>
       </c>
       <c r="Q178">
         <v>0.85</v>
@@ -55043,7 +55043,7 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q179">
         <v>0.85</v>
@@ -55057,7 +55057,7 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="Q180">
         <v>0.85</v>
@@ -55071,10 +55071,10 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="Q181">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -55085,10 +55085,10 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="Q182">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="183" spans="14:17" x14ac:dyDescent="0.45">
@@ -55099,10 +55099,10 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="Q183">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="184" spans="14:17" x14ac:dyDescent="0.45">
@@ -55113,7 +55113,7 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -55127,7 +55127,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1583</v>
+        <v>1561</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55141,7 +55141,7 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -55155,10 +55155,10 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q187">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -55169,7 +55169,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55183,7 +55183,7 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -55197,7 +55197,7 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -55211,7 +55211,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1561</v>
+        <v>1578</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55225,7 +55225,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55239,7 +55239,7 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="Q193">
         <v>0.85</v>
@@ -55253,7 +55253,7 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q194">
         <v>0.85</v>
@@ -55267,10 +55267,10 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1563</v>
+        <v>1594</v>
       </c>
       <c r="Q195">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="196" spans="14:17" x14ac:dyDescent="0.45">
@@ -55281,7 +55281,7 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q196">
         <v>0.85</v>
@@ -55295,7 +55295,7 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="Q197">
         <v>0.85</v>
@@ -55309,7 +55309,7 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1562</v>
+        <v>1586</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -55323,10 +55323,10 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="Q199">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="200" spans="14:17" x14ac:dyDescent="0.45">
@@ -55351,7 +55351,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1591</v>
+        <v>1558</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55365,7 +55365,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1580</v>
+        <v>1599</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55379,7 +55379,7 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -55393,7 +55393,7 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -55407,7 +55407,7 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -55421,10 +55421,10 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1583</v>
+        <v>1562</v>
       </c>
       <c r="Q206">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="207" spans="14:17" x14ac:dyDescent="0.45">
@@ -55435,10 +55435,10 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q207">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="208" spans="14:17" x14ac:dyDescent="0.45">
@@ -55449,7 +55449,7 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="Q208">
         <v>0.95</v>
@@ -55463,7 +55463,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55477,7 +55477,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55491,7 +55491,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55505,7 +55505,7 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1599</v>
+        <v>1563</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -55519,7 +55519,7 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -55533,10 +55533,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1596</v>
+        <v>1558</v>
       </c>
       <c r="Q214">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55547,10 +55547,10 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1592</v>
+        <v>1579</v>
       </c>
       <c r="Q215">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -55561,10 +55561,10 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="Q216">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -55575,7 +55575,7 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -55589,7 +55589,7 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -55603,10 +55603,10 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1598</v>
+        <v>1565</v>
       </c>
       <c r="Q219">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -55617,10 +55617,10 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q220">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -55631,10 +55631,10 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="Q221">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -55645,10 +55645,10 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="Q222">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="223" spans="14:17" x14ac:dyDescent="0.45">
@@ -55659,7 +55659,7 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -55673,7 +55673,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55687,7 +55687,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1552</v>
+        <v>1591</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -55701,7 +55701,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1592</v>
+        <v>1553</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55715,7 +55715,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -55729,7 +55729,7 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -55743,10 +55743,10 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="Q229">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -55757,7 +55757,7 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1558</v>
+        <v>1576</v>
       </c>
       <c r="Q230">
         <v>0.95</v>
@@ -55771,10 +55771,10 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1562</v>
+        <v>1599</v>
       </c>
       <c r="Q231">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="232" spans="14:17" x14ac:dyDescent="0.45">
@@ -55785,10 +55785,10 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1579</v>
+        <v>1554</v>
       </c>
       <c r="Q232">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="233" spans="14:17" x14ac:dyDescent="0.45">
@@ -55799,7 +55799,7 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -55813,7 +55813,7 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1565</v>
+        <v>1584</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -55841,7 +55841,7 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -55855,7 +55855,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1553</v>
+        <v>1592</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -55869,7 +55869,7 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1591</v>
+        <v>1563</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -55883,7 +55883,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55897,7 +55897,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55925,7 +55925,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1596</v>
+        <v>1553</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55939,7 +55939,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -55953,7 +55953,7 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -55967,10 +55967,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q245">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -55981,7 +55981,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="Q246">
         <v>0.95</v>
@@ -55995,7 +55995,7 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="Q247">
         <v>0.95</v>
@@ -56009,7 +56009,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="Q248">
         <v>0.95</v>
@@ -56023,10 +56023,10 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1573</v>
+        <v>1561</v>
       </c>
       <c r="Q249">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="250" spans="14:17" x14ac:dyDescent="0.45">
@@ -56037,10 +56037,10 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="Q250">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="251" spans="14:17" x14ac:dyDescent="0.45">
@@ -56051,7 +56051,7 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -56079,7 +56079,7 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -56093,7 +56093,7 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -56107,10 +56107,10 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="Q255">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="256" spans="14:17" x14ac:dyDescent="0.45">
@@ -56121,10 +56121,10 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
       <c r="Q256">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="257" spans="14:17" x14ac:dyDescent="0.45">
@@ -56135,7 +56135,7 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -56149,7 +56149,7 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q258">
         <v>0.85</v>
@@ -56163,7 +56163,7 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q259">
         <v>0.85</v>
@@ -56177,7 +56177,7 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q260">
         <v>0.85</v>
@@ -56191,7 +56191,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1583</v>
+        <v>1562</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56208,7 +56208,7 @@
         <v>1592</v>
       </c>
       <c r="Q262">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="263" spans="14:17" x14ac:dyDescent="0.45">
@@ -56219,10 +56219,10 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1564</v>
+        <v>1599</v>
       </c>
       <c r="Q263">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="264" spans="14:17" x14ac:dyDescent="0.45">
@@ -56233,7 +56233,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56247,7 +56247,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56261,10 +56261,10 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1586</v>
+        <v>1595</v>
       </c>
       <c r="Q266">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -56275,10 +56275,10 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q267">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -56289,10 +56289,10 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q268">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -56303,10 +56303,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q269">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56317,7 +56317,7 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1553</v>
+        <v>1592</v>
       </c>
       <c r="Q270">
         <v>0.95</v>
@@ -56331,7 +56331,7 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1563</v>
+        <v>1572</v>
       </c>
       <c r="Q271">
         <v>0.95</v>
@@ -56345,10 +56345,10 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q272">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="273" spans="14:17" x14ac:dyDescent="0.45">
@@ -56359,7 +56359,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56373,7 +56373,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56401,7 +56401,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56415,7 +56415,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56429,7 +56429,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56443,7 +56443,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56457,7 +56457,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56471,7 +56471,7 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1578</v>
+        <v>1591</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -56485,7 +56485,7 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -56497,7 +56497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF0B556-557F-477A-ABCD-8EE883AADC6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2B13E0-A9E3-423B-8DC0-FBC3C0AEF338}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F8A534-937E-4D89-B758-E1F73C45A494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3203C0-3BC2-4492-8D53-0DA5B208C224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4141,292 +4141,292 @@
     <t>en_hp_air_10mw_Pulawy_POL</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Legnica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Legnica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Lomza_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Lomza_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Police_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Police_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Krosno_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Krosno_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Lubin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Lubin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Chelm_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Chelm_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Debica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Debica_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Kielce_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Kielce_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Mielec_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Mielec_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Opole_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Opole_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Konin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Konin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Ustka_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Ustka_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Elk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Elk_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Poznan_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Poznan_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Katowice_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Katowice_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Plock_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Plock_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Krakow_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Krakow_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Pulawy_POL</t>
+    <t>en_battery_4h_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Legnica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Legnica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Lomza_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Lomza_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Police_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Police_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Krosno_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Krosno_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Lubin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Lubin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Chelm_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Chelm_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Debica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Debica_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Kielce_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Kielce_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Mielec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Mielec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Opole_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Opole_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Konin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Konin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Ustka_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Ustka_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Elk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Elk_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Poznan_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Poznan_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Katowice_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Katowice_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Plock_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Plock_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Krakow_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Krakow_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Pulawy_POL</t>
   </si>
   <si>
     <t>~tfm_ins-at</t>
@@ -4885,33 +4885,411 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4921,15 +5299,15 @@
     <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4939,157 +5317,49 @@
     <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
@@ -5098,340 +5368,70 @@
     <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6384,7 +6384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0872980-9B2C-4AD1-BD2E-1DD37C883FBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDCEFE9-D258-4BB3-B5C1-043D8D7EAAC1}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37571,7 +37571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F28A15-493B-40B8-9341-E710AC6D6220}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B781A279-F35B-4260-9430-39AF57BAAC81}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51830,7 +51830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19012F33-A961-49DF-AEEA-C774816E1DEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8964ED7A-3039-4152-9446-985C468332E8}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53937,7 +53937,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1552</v>
+        <v>1558</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53951,10 +53951,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1596</v>
+        <v>1562</v>
       </c>
       <c r="Q101">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53965,10 +53965,10 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="Q102">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="103" spans="14:17" x14ac:dyDescent="0.45">
@@ -53979,7 +53979,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1580</v>
+        <v>1565</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53993,7 +53993,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54007,7 +54007,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54021,7 +54021,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54035,7 +54035,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54049,7 +54049,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1568</v>
+        <v>1553</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54063,10 +54063,10 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1554</v>
+        <v>1591</v>
       </c>
       <c r="Q109">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="110" spans="14:17" x14ac:dyDescent="0.45">
@@ -54077,10 +54077,10 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1581</v>
+        <v>1568</v>
       </c>
       <c r="Q110">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="111" spans="14:17" x14ac:dyDescent="0.45">
@@ -54091,7 +54091,7 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -54105,7 +54105,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54119,7 +54119,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54133,7 +54133,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54147,10 +54147,10 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1573</v>
+        <v>1594</v>
       </c>
       <c r="Q115">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="116" spans="14:17" x14ac:dyDescent="0.45">
@@ -54161,7 +54161,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54175,7 +54175,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54189,10 +54189,10 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1584</v>
+        <v>1558</v>
       </c>
       <c r="Q118">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="119" spans="14:17" x14ac:dyDescent="0.45">
@@ -54203,10 +54203,10 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="Q119">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="120" spans="14:17" x14ac:dyDescent="0.45">
@@ -54217,10 +54217,10 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="Q120">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="121" spans="14:17" x14ac:dyDescent="0.45">
@@ -54231,7 +54231,7 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1568</v>
+        <v>1596</v>
       </c>
       <c r="Q121">
         <v>0.85</v>
@@ -54245,7 +54245,7 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q122">
         <v>0.85</v>
@@ -54259,7 +54259,7 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -54273,7 +54273,7 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1552</v>
+        <v>1583</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -54287,7 +54287,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54301,10 +54301,10 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="Q126">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="127" spans="14:17" x14ac:dyDescent="0.45">
@@ -54315,10 +54315,10 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1592</v>
+        <v>1576</v>
       </c>
       <c r="Q127">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="128" spans="14:17" x14ac:dyDescent="0.45">
@@ -54329,7 +54329,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54343,7 +54343,7 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="Q129">
         <v>0.85</v>
@@ -54357,7 +54357,7 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q130">
         <v>0.85</v>
@@ -54371,10 +54371,10 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Q131">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -54385,7 +54385,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1563</v>
+        <v>1586</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54413,7 +54413,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54427,7 +54427,7 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -54441,7 +54441,7 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -54469,7 +54469,7 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1573</v>
+        <v>1589</v>
       </c>
       <c r="Q138">
         <v>0.85</v>
@@ -54483,7 +54483,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1563</v>
+        <v>1592</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54497,7 +54497,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1562</v>
+        <v>1553</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54511,7 +54511,7 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q141">
         <v>0.85</v>
@@ -54525,7 +54525,7 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q142">
         <v>0.85</v>
@@ -54539,7 +54539,7 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1556</v>
+        <v>1592</v>
       </c>
       <c r="Q143">
         <v>0.95</v>
@@ -54553,10 +54553,10 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="Q144">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="145" spans="14:17" x14ac:dyDescent="0.45">
@@ -54567,10 +54567,10 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="Q145">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="146" spans="14:17" x14ac:dyDescent="0.45">
@@ -54581,10 +54581,10 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q146">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="147" spans="14:17" x14ac:dyDescent="0.45">
@@ -54595,7 +54595,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1596</v>
+        <v>1561</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54609,7 +54609,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54623,7 +54623,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1562</v>
+        <v>1599</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54637,7 +54637,7 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="Q150">
         <v>0.85</v>
@@ -54651,7 +54651,7 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -54665,7 +54665,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1589</v>
+        <v>1562</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54679,7 +54679,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54693,10 +54693,10 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1554</v>
+        <v>1573</v>
       </c>
       <c r="Q154">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="155" spans="14:17" x14ac:dyDescent="0.45">
@@ -54707,7 +54707,7 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1596</v>
+        <v>1552</v>
       </c>
       <c r="Q155">
         <v>0.95</v>
@@ -54721,7 +54721,7 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="Q156">
         <v>0.85</v>
@@ -54735,7 +54735,7 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q157">
         <v>0.85</v>
@@ -54749,7 +54749,7 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="Q158">
         <v>0.85</v>
@@ -54763,7 +54763,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -54777,7 +54777,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1558</v>
+        <v>1586</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54791,7 +54791,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54805,7 +54805,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54819,7 +54819,7 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -54833,10 +54833,10 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1578</v>
+        <v>1554</v>
       </c>
       <c r="Q164">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="165" spans="14:17" x14ac:dyDescent="0.45">
@@ -54847,10 +54847,10 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="Q165">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="166" spans="14:17" x14ac:dyDescent="0.45">
@@ -54861,7 +54861,7 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -54875,10 +54875,10 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1564</v>
+        <v>1586</v>
       </c>
       <c r="Q167">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="168" spans="14:17" x14ac:dyDescent="0.45">
@@ -54889,10 +54889,10 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q168">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="169" spans="14:17" x14ac:dyDescent="0.45">
@@ -54917,7 +54917,7 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="Q170">
         <v>0.85</v>
@@ -54931,7 +54931,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -54945,7 +54945,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54959,7 +54959,7 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -54973,7 +54973,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1568</v>
+        <v>1593</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -54987,10 +54987,10 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1599</v>
+        <v>1562</v>
       </c>
       <c r="Q175">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="176" spans="14:17" x14ac:dyDescent="0.45">
@@ -55001,7 +55001,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -55015,10 +55015,10 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1599</v>
+        <v>1572</v>
       </c>
       <c r="Q177">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="178" spans="14:17" x14ac:dyDescent="0.45">
@@ -55029,10 +55029,10 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="Q178">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -55043,10 +55043,10 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="Q179">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -55057,10 +55057,10 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q180">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -55071,7 +55071,7 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1579</v>
+        <v>1595</v>
       </c>
       <c r="Q181">
         <v>0.95</v>
@@ -55085,7 +55085,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1591</v>
+        <v>1573</v>
       </c>
       <c r="Q182">
         <v>0.95</v>
@@ -55099,10 +55099,10 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1554</v>
+        <v>1592</v>
       </c>
       <c r="Q183">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="184" spans="14:17" x14ac:dyDescent="0.45">
@@ -55127,7 +55127,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55155,7 +55155,7 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="Q187">
         <v>0.85</v>
@@ -55169,7 +55169,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55183,7 +55183,7 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -55197,7 +55197,7 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -55211,7 +55211,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55225,7 +55225,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55239,7 +55239,7 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1593</v>
+        <v>1583</v>
       </c>
       <c r="Q193">
         <v>0.85</v>
@@ -55253,10 +55253,10 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="Q194">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="195" spans="14:17" x14ac:dyDescent="0.45">
@@ -55267,7 +55267,7 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1594</v>
+        <v>1556</v>
       </c>
       <c r="Q195">
         <v>0.95</v>
@@ -55281,10 +55281,10 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q196">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="197" spans="14:17" x14ac:dyDescent="0.45">
@@ -55298,7 +55298,7 @@
         <v>1558</v>
       </c>
       <c r="Q197">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="198" spans="14:17" x14ac:dyDescent="0.45">
@@ -55309,7 +55309,7 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -55323,7 +55323,7 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1573</v>
+        <v>1552</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -55337,7 +55337,7 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q200">
         <v>0.85</v>
@@ -55351,7 +55351,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55365,7 +55365,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55379,7 +55379,7 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -55393,7 +55393,7 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -55407,10 +55407,10 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1568</v>
+        <v>1553</v>
       </c>
       <c r="Q205">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="206" spans="14:17" x14ac:dyDescent="0.45">
@@ -55421,7 +55421,7 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="Q206">
         <v>0.95</v>
@@ -55435,7 +55435,7 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q207">
         <v>0.95</v>
@@ -55449,10 +55449,10 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q208">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="209" spans="14:17" x14ac:dyDescent="0.45">
@@ -55463,7 +55463,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1596</v>
+        <v>1552</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55477,7 +55477,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55491,7 +55491,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55505,7 +55505,7 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1563</v>
+        <v>1592</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -55519,7 +55519,7 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -55533,10 +55533,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="Q214">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55547,10 +55547,10 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1579</v>
+        <v>1568</v>
       </c>
       <c r="Q215">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -55561,10 +55561,10 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1562</v>
+        <v>1587</v>
       </c>
       <c r="Q216">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -55575,7 +55575,7 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -55589,10 +55589,10 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q218">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -55603,10 +55603,10 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1565</v>
+        <v>1591</v>
       </c>
       <c r="Q219">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -55617,10 +55617,10 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q220">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -55631,7 +55631,7 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -55645,7 +55645,7 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -55659,7 +55659,7 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -55687,7 +55687,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1591</v>
+        <v>1552</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -55701,7 +55701,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1553</v>
+        <v>1568</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55715,10 +55715,10 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1596</v>
+        <v>1573</v>
       </c>
       <c r="Q227">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="228" spans="14:17" x14ac:dyDescent="0.45">
@@ -55729,10 +55729,10 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q228">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="229" spans="14:17" x14ac:dyDescent="0.45">
@@ -55743,7 +55743,7 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1576</v>
+        <v>1562</v>
       </c>
       <c r="Q229">
         <v>0.95</v>
@@ -55757,10 +55757,10 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1576</v>
+        <v>1596</v>
       </c>
       <c r="Q230">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="231" spans="14:17" x14ac:dyDescent="0.45">
@@ -55785,7 +55785,7 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1554</v>
+        <v>1592</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -55799,7 +55799,7 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1584</v>
+        <v>1563</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -55813,7 +55813,7 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -55827,10 +55827,10 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1598</v>
+        <v>1554</v>
       </c>
       <c r="Q235">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="236" spans="14:17" x14ac:dyDescent="0.45">
@@ -55841,10 +55841,10 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="Q236">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="237" spans="14:17" x14ac:dyDescent="0.45">
@@ -55855,7 +55855,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -55869,7 +55869,7 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -55883,7 +55883,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55897,7 +55897,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55911,7 +55911,7 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -55925,7 +55925,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1553</v>
+        <v>1599</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55939,7 +55939,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1598</v>
+        <v>1573</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -55953,10 +55953,10 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="Q244">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -55967,10 +55967,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="Q245">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -55981,10 +55981,10 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q246">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="247" spans="14:17" x14ac:dyDescent="0.45">
@@ -55995,10 +55995,10 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q247">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -56012,7 +56012,7 @@
         <v>1599</v>
       </c>
       <c r="Q248">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="249" spans="14:17" x14ac:dyDescent="0.45">
@@ -56023,7 +56023,7 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -56037,7 +56037,7 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -56051,7 +56051,7 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -56065,7 +56065,7 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -56079,7 +56079,7 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1552</v>
+        <v>1592</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -56107,7 +56107,7 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q255">
         <v>0.95</v>
@@ -56121,7 +56121,7 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1598</v>
+        <v>1564</v>
       </c>
       <c r="Q256">
         <v>0.95</v>
@@ -56135,7 +56135,7 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -56163,7 +56163,7 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q259">
         <v>0.85</v>
@@ -56177,7 +56177,7 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q260">
         <v>0.85</v>
@@ -56191,7 +56191,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56205,7 +56205,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56219,10 +56219,10 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q263">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="264" spans="14:17" x14ac:dyDescent="0.45">
@@ -56233,10 +56233,10 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1592</v>
+        <v>1554</v>
       </c>
       <c r="Q264">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="265" spans="14:17" x14ac:dyDescent="0.45">
@@ -56247,7 +56247,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56261,10 +56261,10 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1595</v>
+        <v>1561</v>
       </c>
       <c r="Q266">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -56275,10 +56275,10 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1589</v>
+        <v>1561</v>
       </c>
       <c r="Q267">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -56289,10 +56289,10 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1573</v>
+        <v>1561</v>
       </c>
       <c r="Q268">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -56303,10 +56303,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q269">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56317,10 +56317,10 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="Q270">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="271" spans="14:17" x14ac:dyDescent="0.45">
@@ -56331,10 +56331,10 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1572</v>
+        <v>1598</v>
       </c>
       <c r="Q271">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -56345,7 +56345,7 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -56359,7 +56359,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56373,7 +56373,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56387,7 +56387,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56401,10 +56401,10 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q276">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="277" spans="14:17" x14ac:dyDescent="0.45">
@@ -56415,10 +56415,10 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="Q277">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="278" spans="14:17" x14ac:dyDescent="0.45">
@@ -56429,7 +56429,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56443,7 +56443,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1573</v>
+        <v>1552</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56457,7 +56457,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56471,7 +56471,7 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -56485,7 +56485,7 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -56497,7 +56497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2B13E0-A9E3-423B-8DC0-FBC3C0AEF338}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9F07FF4-A6DF-4AB7-9887-643E731B6A77}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3203C0-3BC2-4492-8D53-0DA5B208C224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC63730C-4E66-4E47-9248-E318ED1AF7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4885,13 +4885,109 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
@@ -4900,7 +4996,22 @@
     <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
@@ -4909,529 +5020,418 @@
     <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6384,7 +6384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDCEFE9-D258-4BB3-B5C1-043D8D7EAAC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AECA9E1F-F4B0-4970-9B9F-3696D2AF7994}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37571,7 +37571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B781A279-F35B-4260-9430-39AF57BAAC81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64190062-692F-4F4B-AC60-9AC31A969E39}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51830,7 +51830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8964ED7A-3039-4152-9446-985C468332E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3911617C-206E-4FC1-8B07-8CF83B489D19}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53937,7 +53937,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53951,7 +53951,7 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q101">
         <v>0.95</v>
@@ -53965,10 +53965,10 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1579</v>
+        <v>1596</v>
       </c>
       <c r="Q102">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="103" spans="14:17" x14ac:dyDescent="0.45">
@@ -53979,7 +53979,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1565</v>
+        <v>1592</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53993,7 +53993,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1598</v>
+        <v>1552</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54007,7 +54007,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54021,7 +54021,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54035,7 +54035,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54049,7 +54049,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1553</v>
+        <v>1568</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54063,10 +54063,10 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="Q109">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="110" spans="14:17" x14ac:dyDescent="0.45">
@@ -54077,10 +54077,10 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q110">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="111" spans="14:17" x14ac:dyDescent="0.45">
@@ -54091,7 +54091,7 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -54105,7 +54105,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54119,7 +54119,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54133,7 +54133,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54147,10 +54147,10 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q115">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="116" spans="14:17" x14ac:dyDescent="0.45">
@@ -54161,7 +54161,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54175,7 +54175,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54189,7 +54189,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54203,7 +54203,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54217,10 +54217,10 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1558</v>
+        <v>1598</v>
       </c>
       <c r="Q120">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="121" spans="14:17" x14ac:dyDescent="0.45">
@@ -54231,10 +54231,10 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1596</v>
+        <v>1562</v>
       </c>
       <c r="Q121">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="122" spans="14:17" x14ac:dyDescent="0.45">
@@ -54245,7 +54245,7 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q122">
         <v>0.85</v>
@@ -54259,7 +54259,7 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -54273,7 +54273,7 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -54287,7 +54287,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54301,10 +54301,10 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="Q126">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="127" spans="14:17" x14ac:dyDescent="0.45">
@@ -54315,10 +54315,10 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="Q127">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="128" spans="14:17" x14ac:dyDescent="0.45">
@@ -54329,7 +54329,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54343,10 +54343,10 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1554</v>
+        <v>1581</v>
       </c>
       <c r="Q129">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -54357,10 +54357,10 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1584</v>
+        <v>1554</v>
       </c>
       <c r="Q130">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -54371,10 +54371,10 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1598</v>
+        <v>1579</v>
       </c>
       <c r="Q131">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -54385,10 +54385,10 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1586</v>
+        <v>1562</v>
       </c>
       <c r="Q132">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="133" spans="14:17" x14ac:dyDescent="0.45">
@@ -54399,10 +54399,10 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1584</v>
+        <v>1558</v>
       </c>
       <c r="Q133">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="134" spans="14:17" x14ac:dyDescent="0.45">
@@ -54427,7 +54427,7 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1592</v>
+        <v>1565</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -54441,7 +54441,7 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1563</v>
+        <v>1598</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -54455,7 +54455,7 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -54469,7 +54469,7 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="Q138">
         <v>0.85</v>
@@ -54483,7 +54483,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1592</v>
+        <v>1553</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54497,7 +54497,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1553</v>
+        <v>1591</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54511,7 +54511,7 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q141">
         <v>0.85</v>
@@ -54525,7 +54525,7 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1568</v>
+        <v>1596</v>
       </c>
       <c r="Q142">
         <v>0.85</v>
@@ -54542,7 +54542,7 @@
         <v>1592</v>
       </c>
       <c r="Q143">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="144" spans="14:17" x14ac:dyDescent="0.45">
@@ -54553,7 +54553,7 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q144">
         <v>0.85</v>
@@ -54567,7 +54567,7 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -54581,10 +54581,10 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="Q146">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="147" spans="14:17" x14ac:dyDescent="0.45">
@@ -54595,7 +54595,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54609,7 +54609,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54623,7 +54623,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54637,7 +54637,7 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q150">
         <v>0.85</v>
@@ -54651,7 +54651,7 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -54665,7 +54665,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54679,7 +54679,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54707,10 +54707,10 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1552</v>
+        <v>1578</v>
       </c>
       <c r="Q155">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="156" spans="14:17" x14ac:dyDescent="0.45">
@@ -54721,7 +54721,7 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="Q156">
         <v>0.85</v>
@@ -54735,7 +54735,7 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q157">
         <v>0.85</v>
@@ -54752,7 +54752,7 @@
         <v>1591</v>
       </c>
       <c r="Q158">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="159" spans="14:17" x14ac:dyDescent="0.45">
@@ -54763,7 +54763,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1580</v>
+        <v>1563</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -54777,7 +54777,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54791,7 +54791,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54805,7 +54805,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1583</v>
+        <v>1561</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54819,7 +54819,7 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -54833,10 +54833,10 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1554</v>
+        <v>1573</v>
       </c>
       <c r="Q164">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="165" spans="14:17" x14ac:dyDescent="0.45">
@@ -54847,10 +54847,10 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="Q165">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="166" spans="14:17" x14ac:dyDescent="0.45">
@@ -54861,7 +54861,7 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -54875,7 +54875,7 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1586</v>
+        <v>1562</v>
       </c>
       <c r="Q167">
         <v>0.85</v>
@@ -54889,7 +54889,7 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1596</v>
+        <v>1578</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -54903,7 +54903,7 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="Q169">
         <v>0.85</v>
@@ -54917,10 +54917,10 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="Q170">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="171" spans="14:17" x14ac:dyDescent="0.45">
@@ -54931,7 +54931,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1589</v>
+        <v>1561</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -54945,7 +54945,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54959,7 +54959,7 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -54973,7 +54973,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1593</v>
+        <v>1573</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -54987,7 +54987,7 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -55001,7 +55001,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -55015,7 +55015,7 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1572</v>
+        <v>1599</v>
       </c>
       <c r="Q177">
         <v>0.95</v>
@@ -55029,7 +55029,7 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="Q178">
         <v>0.95</v>
@@ -55043,7 +55043,7 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q179">
         <v>0.95</v>
@@ -55057,7 +55057,7 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1589</v>
+        <v>1552</v>
       </c>
       <c r="Q180">
         <v>0.95</v>
@@ -55071,10 +55071,10 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="Q181">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -55085,10 +55085,10 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="Q182">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="183" spans="14:17" x14ac:dyDescent="0.45">
@@ -55099,7 +55099,7 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -55113,7 +55113,7 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -55141,7 +55141,7 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1561</v>
+        <v>1586</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -55155,7 +55155,7 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q187">
         <v>0.85</v>
@@ -55169,7 +55169,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55183,7 +55183,7 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -55197,7 +55197,7 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -55211,7 +55211,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55225,7 +55225,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55239,7 +55239,7 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q193">
         <v>0.85</v>
@@ -55253,10 +55253,10 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q194">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="195" spans="14:17" x14ac:dyDescent="0.45">
@@ -55267,7 +55267,7 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1556</v>
+        <v>1592</v>
       </c>
       <c r="Q195">
         <v>0.95</v>
@@ -55281,7 +55281,7 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1596</v>
+        <v>1564</v>
       </c>
       <c r="Q196">
         <v>0.95</v>
@@ -55295,7 +55295,7 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="Q197">
         <v>0.95</v>
@@ -55323,7 +55323,7 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1552</v>
+        <v>1563</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -55337,7 +55337,7 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q200">
         <v>0.85</v>
@@ -55351,7 +55351,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55365,7 +55365,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55379,10 +55379,10 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="Q203">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="204" spans="14:17" x14ac:dyDescent="0.45">
@@ -55393,10 +55393,10 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q204">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="205" spans="14:17" x14ac:dyDescent="0.45">
@@ -55407,10 +55407,10 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="Q205">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="206" spans="14:17" x14ac:dyDescent="0.45">
@@ -55421,10 +55421,10 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1563</v>
+        <v>1598</v>
       </c>
       <c r="Q206">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="207" spans="14:17" x14ac:dyDescent="0.45">
@@ -55435,10 +55435,10 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="Q207">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="208" spans="14:17" x14ac:dyDescent="0.45">
@@ -55449,7 +55449,7 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q208">
         <v>0.85</v>
@@ -55463,7 +55463,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1552</v>
+        <v>1596</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55477,7 +55477,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55491,7 +55491,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1565</v>
+        <v>1592</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55505,7 +55505,7 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -55519,7 +55519,7 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -55533,7 +55533,7 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q214">
         <v>0.85</v>
@@ -55547,10 +55547,10 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1568</v>
+        <v>1594</v>
       </c>
       <c r="Q215">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -55561,10 +55561,10 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="Q216">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -55589,10 +55589,10 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q218">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -55603,10 +55603,10 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q219">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -55617,10 +55617,10 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="Q220">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -55631,7 +55631,7 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1561</v>
+        <v>1586</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -55645,10 +55645,10 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="Q222">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="223" spans="14:17" x14ac:dyDescent="0.45">
@@ -55659,7 +55659,7 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -55673,7 +55673,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55687,7 +55687,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1552</v>
+        <v>1586</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -55701,7 +55701,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1568</v>
+        <v>1587</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55715,10 +55715,10 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1573</v>
+        <v>1558</v>
       </c>
       <c r="Q227">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="228" spans="14:17" x14ac:dyDescent="0.45">
@@ -55729,10 +55729,10 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="Q228">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="229" spans="14:17" x14ac:dyDescent="0.45">
@@ -55743,10 +55743,10 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
       <c r="Q229">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -55757,7 +55757,7 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -55771,7 +55771,7 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -55785,7 +55785,7 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -55799,7 +55799,7 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1563</v>
+        <v>1599</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -55813,10 +55813,10 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="Q234">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -55827,7 +55827,7 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1554</v>
+        <v>1596</v>
       </c>
       <c r="Q235">
         <v>0.95</v>
@@ -55841,7 +55841,7 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="Q236">
         <v>0.95</v>
@@ -55855,7 +55855,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1578</v>
+        <v>1599</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -55869,7 +55869,7 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -55883,7 +55883,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55897,7 +55897,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1586</v>
+        <v>1598</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55911,7 +55911,7 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -55925,7 +55925,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55939,7 +55939,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -55953,10 +55953,10 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1598</v>
+        <v>1553</v>
       </c>
       <c r="Q244">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -55967,10 +55967,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
       <c r="Q245">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -55981,7 +55981,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1599</v>
+        <v>1589</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -56009,7 +56009,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -56023,7 +56023,7 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1599</v>
+        <v>1563</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -56037,7 +56037,7 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -56051,7 +56051,7 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1592</v>
+        <v>1583</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -56065,10 +56065,10 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1599</v>
+        <v>1576</v>
       </c>
       <c r="Q252">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="253" spans="14:17" x14ac:dyDescent="0.45">
@@ -56079,10 +56079,10 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q253">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="254" spans="14:17" x14ac:dyDescent="0.45">
@@ -56093,10 +56093,10 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="Q254">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="255" spans="14:17" x14ac:dyDescent="0.45">
@@ -56107,7 +56107,7 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="Q255">
         <v>0.95</v>
@@ -56121,10 +56121,10 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1564</v>
+        <v>1592</v>
       </c>
       <c r="Q256">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="257" spans="14:17" x14ac:dyDescent="0.45">
@@ -56135,7 +56135,7 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -56149,7 +56149,7 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q258">
         <v>0.85</v>
@@ -56163,7 +56163,7 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="Q259">
         <v>0.85</v>
@@ -56177,7 +56177,7 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q260">
         <v>0.85</v>
@@ -56191,7 +56191,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1592</v>
+        <v>1565</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56205,7 +56205,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56219,10 +56219,10 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="Q263">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="264" spans="14:17" x14ac:dyDescent="0.45">
@@ -56233,10 +56233,10 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1554</v>
+        <v>1591</v>
       </c>
       <c r="Q264">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="265" spans="14:17" x14ac:dyDescent="0.45">
@@ -56247,7 +56247,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56261,7 +56261,7 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="Q266">
         <v>0.85</v>
@@ -56275,10 +56275,10 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q267">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -56289,10 +56289,10 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q268">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -56303,10 +56303,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q269">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56317,10 +56317,10 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1593</v>
+        <v>1553</v>
       </c>
       <c r="Q270">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="271" spans="14:17" x14ac:dyDescent="0.45">
@@ -56331,7 +56331,7 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q271">
         <v>0.85</v>
@@ -56345,7 +56345,7 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1573</v>
+        <v>1552</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -56359,7 +56359,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56373,7 +56373,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56387,7 +56387,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56401,10 +56401,10 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="Q276">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="277" spans="14:17" x14ac:dyDescent="0.45">
@@ -56415,10 +56415,10 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1579</v>
+        <v>1568</v>
       </c>
       <c r="Q277">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="278" spans="14:17" x14ac:dyDescent="0.45">
@@ -56429,7 +56429,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56443,7 +56443,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1552</v>
+        <v>1578</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56457,7 +56457,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56471,10 +56471,10 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1586</v>
+        <v>1563</v>
       </c>
       <c r="Q281">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="282" spans="14:17" x14ac:dyDescent="0.45">
@@ -56485,10 +56485,10 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="Q282">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -56497,7 +56497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9F07FF4-A6DF-4AB7-9887-643E731B6A77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A30D4F2-D2DB-4346-93AE-C08B22AB584B}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC63730C-4E66-4E47-9248-E318ED1AF7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E6A71C-6AC6-4834-86B1-F7B0E76CDBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4885,6 +4885,255 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4894,6 +5143,9 @@
     <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4906,532 +5158,280 @@
     <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6384,7 +6384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AECA9E1F-F4B0-4970-9B9F-3696D2AF7994}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A3380E-0252-4CC7-8176-0F4A49B5D513}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37571,7 +37571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64190062-692F-4F4B-AC60-9AC31A969E39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB0ECD7-33DE-4181-BBB7-BC34872F6417}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51830,7 +51830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3911617C-206E-4FC1-8B07-8CF83B489D19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3267CB-1A88-4F31-BDD7-5307151F1367}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53937,7 +53937,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1556</v>
+        <v>1599</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53951,10 +53951,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q101">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53965,7 +53965,7 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q102">
         <v>0.85</v>
@@ -53979,7 +53979,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1592</v>
+        <v>1552</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53993,7 +53993,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1552</v>
+        <v>1591</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54007,7 +54007,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54021,10 +54021,10 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1562</v>
+        <v>1579</v>
       </c>
       <c r="Q106">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="107" spans="14:17" x14ac:dyDescent="0.45">
@@ -54035,7 +54035,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54049,7 +54049,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54063,10 +54063,10 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1596</v>
+        <v>1562</v>
       </c>
       <c r="Q109">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="110" spans="14:17" x14ac:dyDescent="0.45">
@@ -54077,10 +54077,10 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="Q110">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="111" spans="14:17" x14ac:dyDescent="0.45">
@@ -54105,7 +54105,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54119,7 +54119,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54133,10 +54133,10 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1599</v>
+        <v>1581</v>
       </c>
       <c r="Q114">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="115" spans="14:17" x14ac:dyDescent="0.45">
@@ -54147,10 +54147,10 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1592</v>
+        <v>1554</v>
       </c>
       <c r="Q115">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="116" spans="14:17" x14ac:dyDescent="0.45">
@@ -54161,10 +54161,10 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="Q116">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="117" spans="14:17" x14ac:dyDescent="0.45">
@@ -54175,7 +54175,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1599</v>
+        <v>1558</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54189,7 +54189,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54203,7 +54203,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54217,10 +54217,10 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q120">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="121" spans="14:17" x14ac:dyDescent="0.45">
@@ -54231,10 +54231,10 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q121">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="122" spans="14:17" x14ac:dyDescent="0.45">
@@ -54245,7 +54245,7 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="Q122">
         <v>0.85</v>
@@ -54259,7 +54259,7 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -54273,7 +54273,7 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1573</v>
+        <v>1596</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -54287,7 +54287,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54301,7 +54301,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54315,7 +54315,7 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -54329,7 +54329,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54343,10 +54343,10 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1581</v>
+        <v>1599</v>
       </c>
       <c r="Q129">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -54357,10 +54357,10 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1554</v>
+        <v>1599</v>
       </c>
       <c r="Q130">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -54371,10 +54371,10 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1579</v>
+        <v>1599</v>
       </c>
       <c r="Q131">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -54388,7 +54388,7 @@
         <v>1562</v>
       </c>
       <c r="Q132">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="133" spans="14:17" x14ac:dyDescent="0.45">
@@ -54399,10 +54399,10 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="Q133">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="134" spans="14:17" x14ac:dyDescent="0.45">
@@ -54413,7 +54413,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54427,7 +54427,7 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -54444,7 +54444,7 @@
         <v>1598</v>
       </c>
       <c r="Q136">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="137" spans="14:17" x14ac:dyDescent="0.45">
@@ -54455,10 +54455,10 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="Q137">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="138" spans="14:17" x14ac:dyDescent="0.45">
@@ -54472,7 +54472,7 @@
         <v>1592</v>
       </c>
       <c r="Q138">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="139" spans="14:17" x14ac:dyDescent="0.45">
@@ -54483,7 +54483,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1553</v>
+        <v>1584</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54497,7 +54497,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1591</v>
+        <v>1563</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54525,7 +54525,7 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1596</v>
+        <v>1561</v>
       </c>
       <c r="Q142">
         <v>0.85</v>
@@ -54539,7 +54539,7 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q143">
         <v>0.85</v>
@@ -54553,7 +54553,7 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q144">
         <v>0.85</v>
@@ -54567,7 +54567,7 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -54581,10 +54581,10 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1554</v>
+        <v>1578</v>
       </c>
       <c r="Q146">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="147" spans="14:17" x14ac:dyDescent="0.45">
@@ -54595,7 +54595,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1583</v>
+        <v>1562</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54609,7 +54609,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54623,7 +54623,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54637,10 +54637,10 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1561</v>
+        <v>1576</v>
       </c>
       <c r="Q150">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="151" spans="14:17" x14ac:dyDescent="0.45">
@@ -54651,10 +54651,10 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="Q151">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="152" spans="14:17" x14ac:dyDescent="0.45">
@@ -54665,7 +54665,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54679,7 +54679,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54693,7 +54693,7 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1573</v>
+        <v>1554</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -54707,7 +54707,7 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -54721,7 +54721,7 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="Q156">
         <v>0.85</v>
@@ -54735,7 +54735,7 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q157">
         <v>0.85</v>
@@ -54749,10 +54749,10 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q158">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="159" spans="14:17" x14ac:dyDescent="0.45">
@@ -54763,7 +54763,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1563</v>
+        <v>1598</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -54777,7 +54777,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54791,7 +54791,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54805,7 +54805,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54819,7 +54819,7 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1563</v>
+        <v>1578</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -54833,7 +54833,7 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1573</v>
+        <v>1589</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -54847,7 +54847,7 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q165">
         <v>0.85</v>
@@ -54861,7 +54861,7 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -54875,7 +54875,7 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q167">
         <v>0.85</v>
@@ -54889,7 +54889,7 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -54903,7 +54903,7 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q169">
         <v>0.85</v>
@@ -54917,10 +54917,10 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q170">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="171" spans="14:17" x14ac:dyDescent="0.45">
@@ -54931,7 +54931,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -54945,7 +54945,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54959,10 +54959,10 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1573</v>
+        <v>1564</v>
       </c>
       <c r="Q173">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="174" spans="14:17" x14ac:dyDescent="0.45">
@@ -54973,10 +54973,10 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q174">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="175" spans="14:17" x14ac:dyDescent="0.45">
@@ -54987,10 +54987,10 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="Q175">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="176" spans="14:17" x14ac:dyDescent="0.45">
@@ -55001,10 +55001,10 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q176">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="177" spans="14:17" x14ac:dyDescent="0.45">
@@ -55015,7 +55015,7 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1599</v>
+        <v>1562</v>
       </c>
       <c r="Q177">
         <v>0.95</v>
@@ -55029,10 +55029,10 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="Q178">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -55043,10 +55043,10 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q179">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -55057,10 +55057,10 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1552</v>
+        <v>1563</v>
       </c>
       <c r="Q180">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -55071,7 +55071,7 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q181">
         <v>0.85</v>
@@ -55085,7 +55085,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1591</v>
+        <v>1568</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -55099,10 +55099,10 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1599</v>
+        <v>1556</v>
       </c>
       <c r="Q183">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="184" spans="14:17" x14ac:dyDescent="0.45">
@@ -55113,10 +55113,10 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1580</v>
+        <v>1598</v>
       </c>
       <c r="Q184">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="185" spans="14:17" x14ac:dyDescent="0.45">
@@ -55127,7 +55127,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55141,7 +55141,7 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -55155,7 +55155,7 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q187">
         <v>0.85</v>
@@ -55169,7 +55169,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1583</v>
+        <v>1552</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55197,7 +55197,7 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1586</v>
+        <v>1562</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -55211,7 +55211,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55225,10 +55225,10 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1578</v>
+        <v>1558</v>
       </c>
       <c r="Q192">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="193" spans="14:17" x14ac:dyDescent="0.45">
@@ -55239,10 +55239,10 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q193">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="194" spans="14:17" x14ac:dyDescent="0.45">
@@ -55253,7 +55253,7 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q194">
         <v>0.85</v>
@@ -55267,10 +55267,10 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q195">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="196" spans="14:17" x14ac:dyDescent="0.45">
@@ -55281,10 +55281,10 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="Q196">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="197" spans="14:17" x14ac:dyDescent="0.45">
@@ -55295,10 +55295,10 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q197">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="198" spans="14:17" x14ac:dyDescent="0.45">
@@ -55309,7 +55309,7 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1596</v>
+        <v>1561</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -55323,7 +55323,7 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -55337,7 +55337,7 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q200">
         <v>0.85</v>
@@ -55351,7 +55351,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55365,7 +55365,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55379,10 +55379,10 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q203">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="204" spans="14:17" x14ac:dyDescent="0.45">
@@ -55393,10 +55393,10 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q204">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="205" spans="14:17" x14ac:dyDescent="0.45">
@@ -55407,10 +55407,10 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1558</v>
+        <v>1591</v>
       </c>
       <c r="Q205">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="206" spans="14:17" x14ac:dyDescent="0.45">
@@ -55421,10 +55421,10 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1598</v>
+        <v>1554</v>
       </c>
       <c r="Q206">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="207" spans="14:17" x14ac:dyDescent="0.45">
@@ -55435,7 +55435,7 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="Q207">
         <v>0.85</v>
@@ -55449,7 +55449,7 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="Q208">
         <v>0.85</v>
@@ -55463,7 +55463,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55477,7 +55477,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55491,7 +55491,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55505,7 +55505,7 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -55519,7 +55519,7 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -55533,7 +55533,7 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q214">
         <v>0.85</v>
@@ -55547,7 +55547,7 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1594</v>
+        <v>1552</v>
       </c>
       <c r="Q215">
         <v>0.95</v>
@@ -55561,7 +55561,7 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="Q216">
         <v>0.95</v>
@@ -55575,10 +55575,10 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1568</v>
+        <v>1553</v>
       </c>
       <c r="Q217">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -55589,7 +55589,7 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1552</v>
+        <v>1568</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -55603,7 +55603,7 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -55617,7 +55617,7 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1591</v>
+        <v>1565</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -55631,7 +55631,7 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1586</v>
+        <v>1552</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -55645,10 +55645,10 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="Q222">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="223" spans="14:17" x14ac:dyDescent="0.45">
@@ -55659,7 +55659,7 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -55673,7 +55673,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55687,7 +55687,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -55715,7 +55715,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -55729,10 +55729,10 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1593</v>
+        <v>1563</v>
       </c>
       <c r="Q228">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="229" spans="14:17" x14ac:dyDescent="0.45">
@@ -55743,10 +55743,10 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="Q229">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -55757,10 +55757,10 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1589</v>
+        <v>1579</v>
       </c>
       <c r="Q230">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="231" spans="14:17" x14ac:dyDescent="0.45">
@@ -55771,7 +55771,7 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -55785,7 +55785,7 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -55799,7 +55799,7 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -55813,10 +55813,10 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1554</v>
+        <v>1592</v>
       </c>
       <c r="Q234">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -55827,10 +55827,10 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q235">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="236" spans="14:17" x14ac:dyDescent="0.45">
@@ -55841,10 +55841,10 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1576</v>
+        <v>1553</v>
       </c>
       <c r="Q236">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="237" spans="14:17" x14ac:dyDescent="0.45">
@@ -55855,7 +55855,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -55869,7 +55869,7 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -55883,7 +55883,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55897,7 +55897,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55911,7 +55911,7 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -55925,7 +55925,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55939,10 +55939,10 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="Q243">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -55953,10 +55953,10 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="Q244">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -55967,10 +55967,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1578</v>
+        <v>1596</v>
       </c>
       <c r="Q245">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -55981,7 +55981,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -55995,7 +55995,7 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -56009,7 +56009,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -56023,7 +56023,7 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1563</v>
+        <v>1599</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -56037,7 +56037,7 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -56051,7 +56051,7 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -56065,10 +56065,10 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1576</v>
+        <v>1589</v>
       </c>
       <c r="Q252">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="253" spans="14:17" x14ac:dyDescent="0.45">
@@ -56079,10 +56079,10 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="Q253">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="254" spans="14:17" x14ac:dyDescent="0.45">
@@ -56093,10 +56093,10 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="Q254">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="255" spans="14:17" x14ac:dyDescent="0.45">
@@ -56107,10 +56107,10 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q255">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="256" spans="14:17" x14ac:dyDescent="0.45">
@@ -56121,7 +56121,7 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -56135,10 +56135,10 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="Q257">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="258" spans="14:17" x14ac:dyDescent="0.45">
@@ -56149,10 +56149,10 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q258">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -56163,10 +56163,10 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1561</v>
+        <v>1591</v>
       </c>
       <c r="Q259">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="260" spans="14:17" x14ac:dyDescent="0.45">
@@ -56191,7 +56191,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56205,7 +56205,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1584</v>
+        <v>1573</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56219,7 +56219,7 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1586</v>
+        <v>1552</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -56233,7 +56233,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56247,7 +56247,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56261,10 +56261,10 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="Q266">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -56275,7 +56275,7 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q267">
         <v>0.95</v>
@@ -56303,7 +56303,7 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1592</v>
+        <v>1572</v>
       </c>
       <c r="Q269">
         <v>0.95</v>
@@ -56317,7 +56317,7 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1553</v>
+        <v>1573</v>
       </c>
       <c r="Q270">
         <v>0.95</v>
@@ -56331,7 +56331,7 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q271">
         <v>0.85</v>
@@ -56345,7 +56345,7 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1552</v>
+        <v>1592</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -56359,7 +56359,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56373,7 +56373,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1565</v>
+        <v>1584</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56387,7 +56387,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56401,7 +56401,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1587</v>
+        <v>1565</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56415,7 +56415,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56429,7 +56429,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56443,7 +56443,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1578</v>
+        <v>1591</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56457,7 +56457,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56471,10 +56471,10 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1563</v>
+        <v>1583</v>
       </c>
       <c r="Q281">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="282" spans="14:17" x14ac:dyDescent="0.45">
@@ -56485,7 +56485,7 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1584</v>
+        <v>1595</v>
       </c>
       <c r="Q282">
         <v>0.95</v>
@@ -56497,7 +56497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A30D4F2-D2DB-4346-93AE-C08B22AB584B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9467A496-49A7-4DF7-8539-6EF29522DB67}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E6A71C-6AC6-4834-86B1-F7B0E76CDBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F01961-1DA8-4EDD-B1DB-E2A8A5F42E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4885,15 +4885,471 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4903,535 +5359,79 @@
     <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6384,7 +6384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A3380E-0252-4CC7-8176-0F4A49B5D513}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8535437-6039-4270-B7DD-1BE859C09308}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6460,7 +6460,7 @@
         <v>119</v>
       </c>
       <c r="C4">
-        <v>1.4746679999999999</v>
+        <v>1.0322676</v>
       </c>
       <c r="D4">
         <v>53.900000000000006</v>
@@ -6531,7 +6531,7 @@
         <v>120</v>
       </c>
       <c r="C5">
-        <v>5.0496210000000001</v>
+        <v>3.5347347</v>
       </c>
       <c r="D5">
         <v>107.80000000000001</v>
@@ -6599,7 +6599,7 @@
         <v>121</v>
       </c>
       <c r="C6">
-        <v>0.98311199999999999</v>
+        <v>0.68817839999999997</v>
       </c>
       <c r="D6">
         <v>97.9</v>
@@ -6664,7 +6664,7 @@
         <v>122</v>
       </c>
       <c r="C7">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D7">
         <v>117.7</v>
@@ -6714,7 +6714,7 @@
         <v>123</v>
       </c>
       <c r="C8">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D8">
         <v>116.60000000000001</v>
@@ -6764,7 +6764,7 @@
         <v>124</v>
       </c>
       <c r="C9">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D9">
         <v>81.400000000000006</v>
@@ -6814,7 +6814,7 @@
         <v>125</v>
       </c>
       <c r="C10">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D10">
         <v>77</v>
@@ -6864,7 +6864,7 @@
         <v>126</v>
       </c>
       <c r="C11">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D11">
         <v>91.300000000000011</v>
@@ -6914,7 +6914,7 @@
         <v>127</v>
       </c>
       <c r="C12">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D12">
         <v>90.2</v>
@@ -6964,7 +6964,7 @@
         <v>128</v>
       </c>
       <c r="C13">
-        <v>2.7705880000000001</v>
+        <v>1.9394115999999999</v>
       </c>
       <c r="D13">
         <v>85.800000000000011</v>
@@ -7014,7 +7014,7 @@
         <v>129</v>
       </c>
       <c r="C14">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D14">
         <v>58.300000000000004</v>
@@ -7064,7 +7064,7 @@
         <v>130</v>
       </c>
       <c r="C15">
-        <v>5.3624289999999997</v>
+        <v>3.7537002999999993</v>
       </c>
       <c r="D15">
         <v>99.000000000000014</v>
@@ -7114,7 +7114,7 @@
         <v>131</v>
       </c>
       <c r="C16">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D16">
         <v>150.70000000000002</v>
@@ -7164,7 +7164,7 @@
         <v>132</v>
       </c>
       <c r="C17">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D17">
         <v>37.400000000000006</v>
@@ -7214,7 +7214,7 @@
         <v>133</v>
       </c>
       <c r="C18">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D18">
         <v>100.10000000000001</v>
@@ -7264,7 +7264,7 @@
         <v>134</v>
       </c>
       <c r="C19">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D19">
         <v>132</v>
@@ -7314,7 +7314,7 @@
         <v>135</v>
       </c>
       <c r="C20">
-        <v>4.558065</v>
+        <v>3.1906455</v>
       </c>
       <c r="D20">
         <v>47.300000000000004</v>
@@ -7364,7 +7364,7 @@
         <v>136</v>
       </c>
       <c r="C21">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D21">
         <v>101.2</v>
@@ -7414,7 +7414,7 @@
         <v>137</v>
       </c>
       <c r="C22">
-        <v>5.5411759999999992</v>
+        <v>3.8788231999999994</v>
       </c>
       <c r="D22">
         <v>93.500000000000014</v>
@@ -7464,7 +7464,7 @@
         <v>138</v>
       </c>
       <c r="C23">
-        <v>0.98311199999999999</v>
+        <v>0.68817839999999997</v>
       </c>
       <c r="D23">
         <v>16.5</v>
@@ -7514,7 +7514,7 @@
         <v>139</v>
       </c>
       <c r="C24">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D24">
         <v>53.900000000000006</v>
@@ -7564,7 +7564,7 @@
         <v>140</v>
       </c>
       <c r="C25">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D25">
         <v>121.00000000000001</v>
@@ -7614,7 +7614,7 @@
         <v>141</v>
       </c>
       <c r="C26">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D26">
         <v>79.2</v>
@@ -7664,7 +7664,7 @@
         <v>142</v>
       </c>
       <c r="C27">
-        <v>4.558065</v>
+        <v>3.1906455</v>
       </c>
       <c r="D27">
         <v>103.4</v>
@@ -7714,7 +7714,7 @@
         <v>143</v>
       </c>
       <c r="C28">
-        <v>0.98311199999999999</v>
+        <v>0.68817839999999997</v>
       </c>
       <c r="D28">
         <v>85.800000000000011</v>
@@ -7764,7 +7764,7 @@
         <v>144</v>
       </c>
       <c r="C29">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D29">
         <v>118.80000000000001</v>
@@ -7814,7 +7814,7 @@
         <v>145</v>
       </c>
       <c r="C30">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D30">
         <v>160.60000000000002</v>
@@ -7864,7 +7864,7 @@
         <v>146</v>
       </c>
       <c r="C31">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D31">
         <v>89.100000000000009</v>
@@ -7914,7 +7914,7 @@
         <v>147</v>
       </c>
       <c r="C32">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D32">
         <v>134.20000000000002</v>
@@ -7964,7 +7964,7 @@
         <v>148</v>
       </c>
       <c r="C33">
-        <v>5.3624289999999997</v>
+        <v>3.7537002999999993</v>
       </c>
       <c r="D33">
         <v>71.5</v>
@@ -8014,7 +8014,7 @@
         <v>149</v>
       </c>
       <c r="C34">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D34">
         <v>206.8</v>
@@ -8064,7 +8064,7 @@
         <v>150</v>
       </c>
       <c r="C35">
-        <v>3.2621440000000002</v>
+        <v>2.2835008000000001</v>
       </c>
       <c r="D35">
         <v>108.9</v>
@@ -8114,7 +8114,7 @@
         <v>151</v>
       </c>
       <c r="C36">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D36">
         <v>64.900000000000006</v>
@@ -8164,7 +8164,7 @@
         <v>152</v>
       </c>
       <c r="C37">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D37">
         <v>4.4000000000000004</v>
@@ -8214,7 +8214,7 @@
         <v>153</v>
       </c>
       <c r="C38">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D38">
         <v>70.400000000000006</v>
@@ -8264,7 +8264,7 @@
         <v>154</v>
       </c>
       <c r="C39">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D39">
         <v>25.3</v>
@@ -8314,7 +8314,7 @@
         <v>155</v>
       </c>
       <c r="C40">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D40">
         <v>47.300000000000004</v>
@@ -8364,7 +8364,7 @@
         <v>156</v>
       </c>
       <c r="C41">
-        <v>5.3624289999999997</v>
+        <v>3.7537002999999993</v>
       </c>
       <c r="D41">
         <v>53.900000000000006</v>
@@ -8414,7 +8414,7 @@
         <v>157</v>
       </c>
       <c r="C42">
-        <v>3.5749520000000001</v>
+        <v>2.5024663999999999</v>
       </c>
       <c r="D42">
         <v>99.000000000000014</v>
@@ -8464,7 +8464,7 @@
         <v>158</v>
       </c>
       <c r="C43">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D43">
         <v>91.300000000000011</v>
@@ -8514,7 +8514,7 @@
         <v>159</v>
       </c>
       <c r="C44">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D44">
         <v>101.2</v>
@@ -8564,7 +8564,7 @@
         <v>160</v>
       </c>
       <c r="C45">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D45">
         <v>146.30000000000001</v>
@@ -8614,7 +8614,7 @@
         <v>161</v>
       </c>
       <c r="C46">
-        <v>5.8539850000000007</v>
+        <v>4.0977895000000002</v>
       </c>
       <c r="D46">
         <v>38.5</v>
@@ -8664,7 +8664,7 @@
         <v>162</v>
       </c>
       <c r="C47">
-        <v>0.98311199999999999</v>
+        <v>0.68817839999999997</v>
       </c>
       <c r="D47">
         <v>99.000000000000014</v>
@@ -8714,7 +8714,7 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D48">
         <v>74.800000000000011</v>
@@ -8764,7 +8764,7 @@
         <v>164</v>
       </c>
       <c r="C49">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D49">
         <v>67.100000000000009</v>
@@ -8814,7 +8814,7 @@
         <v>165</v>
       </c>
       <c r="C50">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D50">
         <v>103.4</v>
@@ -8864,7 +8864,7 @@
         <v>166</v>
       </c>
       <c r="C51">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D51">
         <v>137.5</v>
@@ -8914,7 +8914,7 @@
         <v>167</v>
       </c>
       <c r="C52">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D52">
         <v>143</v>
@@ -8964,7 +8964,7 @@
         <v>168</v>
       </c>
       <c r="C53">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D53">
         <v>59.400000000000006</v>
@@ -9014,7 +9014,7 @@
         <v>169</v>
       </c>
       <c r="C54">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D54">
         <v>133.10000000000002</v>
@@ -9064,7 +9064,7 @@
         <v>170</v>
       </c>
       <c r="C55">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D55">
         <v>85.800000000000011</v>
@@ -9114,7 +9114,7 @@
         <v>171</v>
       </c>
       <c r="C56">
-        <v>3.2621439999999997</v>
+        <v>2.2835007999999997</v>
       </c>
       <c r="D56">
         <v>85.800000000000011</v>
@@ -9164,7 +9164,7 @@
         <v>172</v>
       </c>
       <c r="C57">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D57">
         <v>224.4</v>
@@ -9214,7 +9214,7 @@
         <v>173</v>
       </c>
       <c r="C58">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D58">
         <v>198.00000000000003</v>
@@ -9264,7 +9264,7 @@
         <v>174</v>
       </c>
       <c r="C59">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D59">
         <v>103.4</v>
@@ -9314,7 +9314,7 @@
         <v>175</v>
       </c>
       <c r="C60">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D60">
         <v>140.80000000000001</v>
@@ -9364,7 +9364,7 @@
         <v>176</v>
       </c>
       <c r="C61">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D61">
         <v>154</v>
@@ -9414,7 +9414,7 @@
         <v>177</v>
       </c>
       <c r="C62">
-        <v>4.0665089999999999</v>
+        <v>2.8465562999999996</v>
       </c>
       <c r="D62">
         <v>89.100000000000009</v>
@@ -9464,7 +9464,7 @@
         <v>178</v>
       </c>
       <c r="C63">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D63">
         <v>124.30000000000001</v>
@@ -9514,7 +9514,7 @@
         <v>179</v>
       </c>
       <c r="C64">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D64">
         <v>124.30000000000001</v>
@@ -9564,7 +9564,7 @@
         <v>180</v>
       </c>
       <c r="C65">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D65">
         <v>72.600000000000009</v>
@@ -9614,7 +9614,7 @@
         <v>181</v>
       </c>
       <c r="C66">
-        <v>3.5749529999999998</v>
+        <v>2.5024670999999996</v>
       </c>
       <c r="D66">
         <v>14.3</v>
@@ -9664,7 +9664,7 @@
         <v>182</v>
       </c>
       <c r="C67">
-        <v>6.345540999999999</v>
+        <v>4.4418786999999993</v>
       </c>
       <c r="D67">
         <v>41.800000000000004</v>
@@ -9714,7 +9714,7 @@
         <v>183</v>
       </c>
       <c r="C68">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D68">
         <v>86.9</v>
@@ -9764,7 +9764,7 @@
         <v>184</v>
       </c>
       <c r="C69">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D69">
         <v>29.700000000000003</v>
@@ -9814,7 +9814,7 @@
         <v>185</v>
       </c>
       <c r="C70">
-        <v>3.5749520000000001</v>
+        <v>2.5024663999999999</v>
       </c>
       <c r="D70">
         <v>48.400000000000006</v>
@@ -9864,7 +9864,7 @@
         <v>186</v>
       </c>
       <c r="C71">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D71">
         <v>57.2</v>
@@ -9914,7 +9914,7 @@
         <v>187</v>
       </c>
       <c r="C72">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D72">
         <v>94.600000000000009</v>
@@ -9964,7 +9964,7 @@
         <v>188</v>
       </c>
       <c r="C73">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D73">
         <v>96.800000000000011</v>
@@ -10064,7 +10064,7 @@
         <v>190</v>
       </c>
       <c r="C75">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D75">
         <v>52.800000000000004</v>
@@ -10114,7 +10114,7 @@
         <v>191</v>
       </c>
       <c r="C76">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D76">
         <v>57.2</v>
@@ -10164,7 +10164,7 @@
         <v>192</v>
       </c>
       <c r="C77">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D77">
         <v>72.600000000000009</v>
@@ -10214,7 +10214,7 @@
         <v>193</v>
       </c>
       <c r="C78">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D78">
         <v>102.30000000000001</v>
@@ -10264,7 +10264,7 @@
         <v>194</v>
       </c>
       <c r="C79">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D79">
         <v>101.2</v>
@@ -10314,7 +10314,7 @@
         <v>195</v>
       </c>
       <c r="C80">
-        <v>2.7705880000000001</v>
+        <v>1.9394115999999999</v>
       </c>
       <c r="D80">
         <v>49.500000000000007</v>
@@ -10364,7 +10364,7 @@
         <v>196</v>
       </c>
       <c r="C81">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D81">
         <v>228.8</v>
@@ -10414,7 +10414,7 @@
         <v>197</v>
       </c>
       <c r="C82">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D82">
         <v>90.2</v>
@@ -10464,7 +10464,7 @@
         <v>198</v>
       </c>
       <c r="C83">
-        <v>2.2790319999999999</v>
+        <v>1.5953223999999999</v>
       </c>
       <c r="D83">
         <v>105.60000000000001</v>
@@ -10514,7 +10514,7 @@
         <v>199</v>
       </c>
       <c r="C84">
-        <v>1.7874760000000001</v>
+        <v>1.2512331999999999</v>
       </c>
       <c r="D84">
         <v>94.600000000000009</v>
@@ -10564,7 +10564,7 @@
         <v>200</v>
       </c>
       <c r="C85">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D85">
         <v>200.20000000000002</v>
@@ -10614,7 +10614,7 @@
         <v>201</v>
       </c>
       <c r="C86">
-        <v>3.5749520000000001</v>
+        <v>2.5024663999999999</v>
       </c>
       <c r="D86">
         <v>67.100000000000009</v>
@@ -10664,7 +10664,7 @@
         <v>202</v>
       </c>
       <c r="C87">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D87">
         <v>66</v>
@@ -10714,7 +10714,7 @@
         <v>203</v>
       </c>
       <c r="C88">
-        <v>0.49155599999999999</v>
+        <v>0.34408919999999998</v>
       </c>
       <c r="D88">
         <v>72.600000000000009</v>
@@ -37571,7 +37571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB0ECD7-33DE-4181-BBB7-BC34872F6417}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C9D8A3-8458-4EC3-90B7-A2421AC6AABF}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51830,7 +51830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3267CB-1A88-4F31-BDD7-5307151F1367}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD371BF-C88B-47F8-8E26-290C16AAF9F5}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53937,7 +53937,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1599</v>
+        <v>1576</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53951,10 +53951,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1599</v>
+        <v>1576</v>
       </c>
       <c r="Q101">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53965,7 +53965,7 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q102">
         <v>0.85</v>
@@ -53979,7 +53979,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1552</v>
+        <v>1584</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53993,7 +53993,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54007,7 +54007,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1586</v>
+        <v>1554</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54021,10 +54021,10 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1579</v>
+        <v>1598</v>
       </c>
       <c r="Q106">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="107" spans="14:17" x14ac:dyDescent="0.45">
@@ -54035,7 +54035,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54049,7 +54049,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54063,7 +54063,7 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q109">
         <v>0.85</v>
@@ -54077,7 +54077,7 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1573</v>
+        <v>1553</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -54091,7 +54091,7 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -54105,7 +54105,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54119,7 +54119,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1586</v>
+        <v>1563</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54133,10 +54133,10 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
       <c r="Q114">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="115" spans="14:17" x14ac:dyDescent="0.45">
@@ -54147,10 +54147,10 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="Q115">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="116" spans="14:17" x14ac:dyDescent="0.45">
@@ -54161,10 +54161,10 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1594</v>
+        <v>1583</v>
       </c>
       <c r="Q116">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="117" spans="14:17" x14ac:dyDescent="0.45">
@@ -54175,10 +54175,10 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1558</v>
+        <v>1594</v>
       </c>
       <c r="Q117">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="118" spans="14:17" x14ac:dyDescent="0.45">
@@ -54189,7 +54189,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1598</v>
+        <v>1558</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54217,7 +54217,7 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -54259,7 +54259,7 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -54287,7 +54287,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54301,7 +54301,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54315,7 +54315,7 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -54329,10 +54329,10 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q128">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="129" spans="14:17" x14ac:dyDescent="0.45">
@@ -54343,10 +54343,10 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1599</v>
+        <v>1554</v>
       </c>
       <c r="Q129">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -54357,7 +54357,7 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="Q130">
         <v>0.85</v>
@@ -54371,7 +54371,7 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q131">
         <v>0.85</v>
@@ -54385,7 +54385,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1562</v>
+        <v>1596</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54399,7 +54399,7 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -54413,7 +54413,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54427,7 +54427,7 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -54441,10 +54441,10 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="Q136">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="137" spans="14:17" x14ac:dyDescent="0.45">
@@ -54455,10 +54455,10 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1562</v>
+        <v>1589</v>
       </c>
       <c r="Q137">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="138" spans="14:17" x14ac:dyDescent="0.45">
@@ -54469,10 +54469,10 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q138">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="139" spans="14:17" x14ac:dyDescent="0.45">
@@ -54483,7 +54483,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54497,7 +54497,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54511,10 +54511,10 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q141">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="142" spans="14:17" x14ac:dyDescent="0.45">
@@ -54525,10 +54525,10 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="Q142">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="143" spans="14:17" x14ac:dyDescent="0.45">
@@ -54539,10 +54539,10 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="Q143">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="144" spans="14:17" x14ac:dyDescent="0.45">
@@ -54553,7 +54553,7 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="Q144">
         <v>0.85</v>
@@ -54567,7 +54567,7 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -54581,7 +54581,7 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1578</v>
+        <v>1598</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -54595,7 +54595,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54609,7 +54609,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1563</v>
+        <v>1553</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54623,7 +54623,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54637,10 +54637,10 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q150">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="151" spans="14:17" x14ac:dyDescent="0.45">
@@ -54651,10 +54651,10 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q151">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="152" spans="14:17" x14ac:dyDescent="0.45">
@@ -54665,7 +54665,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54679,7 +54679,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54693,7 +54693,7 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1554</v>
+        <v>1596</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -54707,7 +54707,7 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -54721,10 +54721,10 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1598</v>
+        <v>1564</v>
       </c>
       <c r="Q156">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -54735,10 +54735,10 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="Q157">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -54763,7 +54763,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -54791,7 +54791,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1563</v>
+        <v>1578</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54805,7 +54805,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1553</v>
+        <v>1592</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54819,7 +54819,7 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -54833,10 +54833,10 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="Q164">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="165" spans="14:17" x14ac:dyDescent="0.45">
@@ -54847,10 +54847,10 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="Q165">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="166" spans="14:17" x14ac:dyDescent="0.45">
@@ -54875,7 +54875,7 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q167">
         <v>0.85</v>
@@ -54889,7 +54889,7 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1586</v>
+        <v>1561</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -54903,7 +54903,7 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q169">
         <v>0.85</v>
@@ -54917,7 +54917,7 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="Q170">
         <v>0.85</v>
@@ -54931,7 +54931,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -54945,7 +54945,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54959,10 +54959,10 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="Q173">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="174" spans="14:17" x14ac:dyDescent="0.45">
@@ -54973,10 +54973,10 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Q174">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="175" spans="14:17" x14ac:dyDescent="0.45">
@@ -54990,7 +54990,7 @@
         <v>1573</v>
       </c>
       <c r="Q175">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="176" spans="14:17" x14ac:dyDescent="0.45">
@@ -55001,10 +55001,10 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q176">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="177" spans="14:17" x14ac:dyDescent="0.45">
@@ -55015,7 +55015,7 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1562</v>
+        <v>1591</v>
       </c>
       <c r="Q177">
         <v>0.95</v>
@@ -55029,10 +55029,10 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1596</v>
+        <v>1573</v>
       </c>
       <c r="Q178">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -55046,7 +55046,7 @@
         <v>1599</v>
       </c>
       <c r="Q179">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -55057,7 +55057,7 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="Q180">
         <v>0.85</v>
@@ -55071,7 +55071,7 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q181">
         <v>0.85</v>
@@ -55085,7 +55085,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -55099,10 +55099,10 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1556</v>
+        <v>1592</v>
       </c>
       <c r="Q183">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="184" spans="14:17" x14ac:dyDescent="0.45">
@@ -55113,10 +55113,10 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1598</v>
+        <v>1552</v>
       </c>
       <c r="Q184">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="185" spans="14:17" x14ac:dyDescent="0.45">
@@ -55127,7 +55127,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55141,10 +55141,10 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1589</v>
+        <v>1554</v>
       </c>
       <c r="Q186">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="187" spans="14:17" x14ac:dyDescent="0.45">
@@ -55155,10 +55155,10 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1592</v>
+        <v>1581</v>
       </c>
       <c r="Q187">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -55169,7 +55169,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55183,7 +55183,7 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -55211,7 +55211,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55225,10 +55225,10 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1558</v>
+        <v>1586</v>
       </c>
       <c r="Q192">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="193" spans="14:17" x14ac:dyDescent="0.45">
@@ -55239,10 +55239,10 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="Q193">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="194" spans="14:17" x14ac:dyDescent="0.45">
@@ -55253,7 +55253,7 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="Q194">
         <v>0.85</v>
@@ -55267,10 +55267,10 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q195">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="196" spans="14:17" x14ac:dyDescent="0.45">
@@ -55281,10 +55281,10 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="Q196">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="197" spans="14:17" x14ac:dyDescent="0.45">
@@ -55295,10 +55295,10 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1561</v>
+        <v>1595</v>
       </c>
       <c r="Q197">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="198" spans="14:17" x14ac:dyDescent="0.45">
@@ -55309,10 +55309,10 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1561</v>
+        <v>1589</v>
       </c>
       <c r="Q198">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="199" spans="14:17" x14ac:dyDescent="0.45">
@@ -55323,10 +55323,10 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q199">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="200" spans="14:17" x14ac:dyDescent="0.45">
@@ -55337,10 +55337,10 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="Q200">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="201" spans="14:17" x14ac:dyDescent="0.45">
@@ -55351,7 +55351,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55365,7 +55365,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55379,7 +55379,7 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -55393,7 +55393,7 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -55407,10 +55407,10 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q205">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="206" spans="14:17" x14ac:dyDescent="0.45">
@@ -55421,10 +55421,10 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1554</v>
+        <v>1584</v>
       </c>
       <c r="Q206">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="207" spans="14:17" x14ac:dyDescent="0.45">
@@ -55435,7 +55435,7 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="Q207">
         <v>0.85</v>
@@ -55449,7 +55449,7 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q208">
         <v>0.85</v>
@@ -55463,7 +55463,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55477,7 +55477,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55491,7 +55491,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55505,10 +55505,10 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="Q212">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="213" spans="14:17" x14ac:dyDescent="0.45">
@@ -55519,10 +55519,10 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1568</v>
+        <v>1596</v>
       </c>
       <c r="Q213">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="214" spans="14:17" x14ac:dyDescent="0.45">
@@ -55533,10 +55533,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="Q214">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55547,7 +55547,7 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="Q215">
         <v>0.95</v>
@@ -55561,10 +55561,10 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="Q216">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -55575,10 +55575,10 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1553</v>
+        <v>1562</v>
       </c>
       <c r="Q217">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -55589,7 +55589,7 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -55603,7 +55603,7 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -55617,7 +55617,7 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1565</v>
+        <v>1592</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -55631,7 +55631,7 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1552</v>
+        <v>1589</v>
       </c>
       <c r="Q221">
         <v>0.85</v>
@@ -55645,7 +55645,7 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -55659,10 +55659,10 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1578</v>
+        <v>1552</v>
       </c>
       <c r="Q223">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="224" spans="14:17" x14ac:dyDescent="0.45">
@@ -55673,7 +55673,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55687,7 +55687,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1568</v>
+        <v>1591</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -55701,7 +55701,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55715,7 +55715,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -55729,10 +55729,10 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1563</v>
+        <v>1580</v>
       </c>
       <c r="Q228">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="229" spans="14:17" x14ac:dyDescent="0.45">
@@ -55743,10 +55743,10 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1562</v>
+        <v>1586</v>
       </c>
       <c r="Q229">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -55757,10 +55757,10 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1579</v>
+        <v>1568</v>
       </c>
       <c r="Q230">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="231" spans="14:17" x14ac:dyDescent="0.45">
@@ -55771,7 +55771,7 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -55788,7 +55788,7 @@
         <v>1598</v>
       </c>
       <c r="Q232">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="233" spans="14:17" x14ac:dyDescent="0.45">
@@ -55799,10 +55799,10 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="Q233">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -55813,7 +55813,7 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -55841,7 +55841,7 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1553</v>
+        <v>1599</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -55855,7 +55855,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -55869,7 +55869,7 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -55883,7 +55883,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55897,7 +55897,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55911,7 +55911,7 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1596</v>
+        <v>1562</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -55939,7 +55939,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="Q243">
         <v>0.95</v>
@@ -55953,7 +55953,7 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1554</v>
+        <v>1586</v>
       </c>
       <c r="Q244">
         <v>0.95</v>
@@ -55967,7 +55967,7 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1596</v>
+        <v>1562</v>
       </c>
       <c r="Q245">
         <v>0.95</v>
@@ -55981,7 +55981,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -55995,7 +55995,7 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -56009,7 +56009,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1596</v>
+        <v>1563</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -56037,7 +56037,7 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -56051,10 +56051,10 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="Q251">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="252" spans="14:17" x14ac:dyDescent="0.45">
@@ -56065,10 +56065,10 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1589</v>
+        <v>1579</v>
       </c>
       <c r="Q252">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="253" spans="14:17" x14ac:dyDescent="0.45">
@@ -56079,7 +56079,7 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -56093,7 +56093,7 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -56107,7 +56107,7 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1593</v>
+        <v>1552</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -56121,7 +56121,7 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1562</v>
+        <v>1591</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -56135,10 +56135,10 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q257">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="258" spans="14:17" x14ac:dyDescent="0.45">
@@ -56149,7 +56149,7 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q258">
         <v>0.95</v>
@@ -56163,7 +56163,7 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1591</v>
+        <v>1563</v>
       </c>
       <c r="Q259">
         <v>0.95</v>
@@ -56177,10 +56177,10 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
       <c r="Q260">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -56191,7 +56191,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56205,7 +56205,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56219,7 +56219,7 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1552</v>
+        <v>1565</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -56233,7 +56233,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1592</v>
+        <v>1552</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56247,7 +56247,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56261,10 +56261,10 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1589</v>
+        <v>1578</v>
       </c>
       <c r="Q266">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -56275,10 +56275,10 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q267">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -56289,10 +56289,10 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="Q268">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -56303,10 +56303,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1572</v>
+        <v>1592</v>
       </c>
       <c r="Q269">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56317,10 +56317,10 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q270">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="271" spans="14:17" x14ac:dyDescent="0.45">
@@ -56331,10 +56331,10 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q271">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -56345,7 +56345,7 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1592</v>
+        <v>1563</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -56359,7 +56359,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56373,7 +56373,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56401,7 +56401,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56415,7 +56415,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56429,7 +56429,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56443,7 +56443,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1591</v>
+        <v>1562</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56457,7 +56457,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56471,7 +56471,7 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -56485,10 +56485,10 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1595</v>
+        <v>1573</v>
       </c>
       <c r="Q282">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -56497,7 +56497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9467A496-49A7-4DF7-8539-6EF29522DB67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15CBB587-B57B-400B-B822-24624EA391E7}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F01961-1DA8-4EDD-B1DB-E2A8A5F42E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE2457B-8694-4310-AE33-AAEC7B08AA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4885,6 +4885,246 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
   </si>
   <si>
@@ -4894,46 +5134,79 @@
     <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
@@ -4942,496 +5215,223 @@
     <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6384,7 +6384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8535437-6039-4270-B7DD-1BE859C09308}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F8DE39D-F71A-42B9-8AE7-D9C2B6AE849D}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37571,7 +37571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C9D8A3-8458-4EC3-90B7-A2421AC6AABF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A4537A-0821-4C22-BCD4-5F8DA04BAFAE}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51830,7 +51830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD371BF-C88B-47F8-8E26-290C16AAF9F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52F2B29-4EEC-4306-9AB2-C18C08A7A354}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53937,7 +53937,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53951,7 +53951,7 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="Q101">
         <v>0.95</v>
@@ -53979,7 +53979,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1584</v>
+        <v>1552</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53993,7 +53993,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54007,7 +54007,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1554</v>
+        <v>1591</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54021,7 +54021,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54035,10 +54035,10 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="Q107">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="108" spans="14:17" x14ac:dyDescent="0.45">
@@ -54049,10 +54049,10 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q108">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="109" spans="14:17" x14ac:dyDescent="0.45">
@@ -54063,10 +54063,10 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1598</v>
+        <v>1579</v>
       </c>
       <c r="Q109">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="110" spans="14:17" x14ac:dyDescent="0.45">
@@ -54077,7 +54077,7 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1553</v>
+        <v>1598</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -54091,7 +54091,7 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Q111">
         <v>0.85</v>
@@ -54105,7 +54105,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1578</v>
+        <v>1565</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54119,7 +54119,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1563</v>
+        <v>1596</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54133,7 +54133,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54147,7 +54147,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54161,7 +54161,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1583</v>
+        <v>1553</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54175,10 +54175,10 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="Q117">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="118" spans="14:17" x14ac:dyDescent="0.45">
@@ -54189,7 +54189,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54203,7 +54203,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54217,7 +54217,7 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -54231,7 +54231,7 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q121">
         <v>0.85</v>
@@ -54245,10 +54245,10 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="Q122">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="123" spans="14:17" x14ac:dyDescent="0.45">
@@ -54259,10 +54259,10 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q123">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="124" spans="14:17" x14ac:dyDescent="0.45">
@@ -54273,10 +54273,10 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1596</v>
+        <v>1573</v>
       </c>
       <c r="Q124">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="125" spans="14:17" x14ac:dyDescent="0.45">
@@ -54287,7 +54287,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54301,7 +54301,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54315,7 +54315,7 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -54329,10 +54329,10 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q128">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="129" spans="14:17" x14ac:dyDescent="0.45">
@@ -54343,10 +54343,10 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="Q129">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -54357,10 +54357,10 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1584</v>
+        <v>1554</v>
       </c>
       <c r="Q130">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -54371,10 +54371,10 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="Q131">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -54385,7 +54385,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54399,7 +54399,7 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1558</v>
+        <v>1596</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -54413,7 +54413,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54427,7 +54427,7 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1578</v>
+        <v>1599</v>
       </c>
       <c r="Q135">
         <v>0.85</v>
@@ -54441,7 +54441,7 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1593</v>
+        <v>1562</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -54455,7 +54455,7 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1589</v>
+        <v>1578</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -54469,7 +54469,7 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="Q138">
         <v>0.85</v>
@@ -54483,7 +54483,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54497,7 +54497,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54514,7 +54514,7 @@
         <v>1558</v>
       </c>
       <c r="Q141">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="142" spans="14:17" x14ac:dyDescent="0.45">
@@ -54525,10 +54525,10 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1562</v>
+        <v>1593</v>
       </c>
       <c r="Q142">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="143" spans="14:17" x14ac:dyDescent="0.45">
@@ -54539,7 +54539,7 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="Q143">
         <v>0.95</v>
@@ -54553,10 +54553,10 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q144">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="145" spans="14:17" x14ac:dyDescent="0.45">
@@ -54567,7 +54567,7 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -54581,7 +54581,7 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1598</v>
+        <v>1578</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -54595,7 +54595,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54609,7 +54609,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1553</v>
+        <v>1586</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54623,7 +54623,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54637,7 +54637,7 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q150">
         <v>0.85</v>
@@ -54654,7 +54654,7 @@
         <v>1592</v>
       </c>
       <c r="Q151">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="152" spans="14:17" x14ac:dyDescent="0.45">
@@ -54665,7 +54665,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1591</v>
+        <v>1568</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54679,7 +54679,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54693,7 +54693,7 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -54707,7 +54707,7 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -54721,10 +54721,10 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="Q156">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -54735,10 +54735,10 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q157">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -54749,7 +54749,7 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q158">
         <v>0.85</v>
@@ -54763,7 +54763,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -54777,7 +54777,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54791,7 +54791,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1578</v>
+        <v>1563</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54805,7 +54805,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54819,10 +54819,10 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q163">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="164" spans="14:17" x14ac:dyDescent="0.45">
@@ -54833,7 +54833,7 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1591</v>
+        <v>1573</v>
       </c>
       <c r="Q164">
         <v>0.95</v>
@@ -54847,7 +54847,7 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1554</v>
+        <v>1595</v>
       </c>
       <c r="Q165">
         <v>0.95</v>
@@ -54861,10 +54861,10 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="Q166">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="167" spans="14:17" x14ac:dyDescent="0.45">
@@ -54875,10 +54875,10 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q167">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="168" spans="14:17" x14ac:dyDescent="0.45">
@@ -54889,10 +54889,10 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1561</v>
+        <v>1572</v>
       </c>
       <c r="Q168">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="169" spans="14:17" x14ac:dyDescent="0.45">
@@ -54903,7 +54903,7 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q169">
         <v>0.85</v>
@@ -54917,7 +54917,7 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="Q170">
         <v>0.85</v>
@@ -54931,7 +54931,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="Q171">
         <v>0.85</v>
@@ -54945,7 +54945,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54959,7 +54959,7 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1578</v>
+        <v>1565</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -54973,7 +54973,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1598</v>
+        <v>1561</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -54987,7 +54987,7 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1573</v>
+        <v>1561</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -55001,7 +55001,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -55015,10 +55015,10 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1591</v>
+        <v>1573</v>
       </c>
       <c r="Q177">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="178" spans="14:17" x14ac:dyDescent="0.45">
@@ -55029,10 +55029,10 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="Q178">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -55043,10 +55043,10 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q179">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -55057,10 +55057,10 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1561</v>
+        <v>1576</v>
       </c>
       <c r="Q180">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -55071,10 +55071,10 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="Q181">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -55085,7 +55085,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -55099,7 +55099,7 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -55113,7 +55113,7 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1552</v>
+        <v>1598</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -55127,7 +55127,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55144,7 +55144,7 @@
         <v>1554</v>
       </c>
       <c r="Q186">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="187" spans="14:17" x14ac:dyDescent="0.45">
@@ -55155,10 +55155,10 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="Q187">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -55169,7 +55169,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55183,7 +55183,7 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1578</v>
+        <v>1589</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -55197,7 +55197,7 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -55211,7 +55211,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55225,7 +55225,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1586</v>
+        <v>1553</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55239,7 +55239,7 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q193">
         <v>0.85</v>
@@ -55253,7 +55253,7 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="Q194">
         <v>0.85</v>
@@ -55267,10 +55267,10 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="Q195">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="196" spans="14:17" x14ac:dyDescent="0.45">
@@ -55281,10 +55281,10 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="Q196">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="197" spans="14:17" x14ac:dyDescent="0.45">
@@ -55295,7 +55295,7 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1595</v>
+        <v>1556</v>
       </c>
       <c r="Q197">
         <v>0.95</v>
@@ -55309,7 +55309,7 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1589</v>
+        <v>1558</v>
       </c>
       <c r="Q198">
         <v>0.95</v>
@@ -55323,7 +55323,7 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q199">
         <v>0.95</v>
@@ -55337,7 +55337,7 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q200">
         <v>0.95</v>
@@ -55351,7 +55351,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55365,7 +55365,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55379,7 +55379,7 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1599</v>
+        <v>1589</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -55393,7 +55393,7 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1561</v>
+        <v>1552</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -55407,7 +55407,7 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -55421,7 +55421,7 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1584</v>
+        <v>1562</v>
       </c>
       <c r="Q206">
         <v>0.85</v>
@@ -55435,7 +55435,7 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q207">
         <v>0.85</v>
@@ -55449,10 +55449,10 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="Q208">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="209" spans="14:17" x14ac:dyDescent="0.45">
@@ -55463,7 +55463,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55477,7 +55477,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55491,7 +55491,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55505,10 +55505,10 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="Q212">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="213" spans="14:17" x14ac:dyDescent="0.45">
@@ -55519,10 +55519,10 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q213">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="214" spans="14:17" x14ac:dyDescent="0.45">
@@ -55533,10 +55533,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q214">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55547,10 +55547,10 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="Q215">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -55561,7 +55561,7 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1596</v>
+        <v>1573</v>
       </c>
       <c r="Q216">
         <v>0.85</v>
@@ -55575,7 +55575,7 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1562</v>
+        <v>1583</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -55589,7 +55589,7 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -55603,10 +55603,10 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1552</v>
+        <v>1563</v>
       </c>
       <c r="Q219">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -55617,10 +55617,10 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1592</v>
+        <v>1553</v>
       </c>
       <c r="Q220">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -55631,10 +55631,10 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="Q221">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -55659,10 +55659,10 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1552</v>
+        <v>1568</v>
       </c>
       <c r="Q223">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="224" spans="14:17" x14ac:dyDescent="0.45">
@@ -55673,7 +55673,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55687,7 +55687,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1591</v>
+        <v>1552</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -55701,7 +55701,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55715,7 +55715,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -55729,7 +55729,7 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1580</v>
+        <v>1592</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -55743,7 +55743,7 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -55757,7 +55757,7 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1568</v>
+        <v>1587</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -55771,7 +55771,7 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -55785,7 +55785,7 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1598</v>
+        <v>1552</v>
       </c>
       <c r="Q232">
         <v>0.95</v>
@@ -55799,10 +55799,10 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1562</v>
+        <v>1596</v>
       </c>
       <c r="Q233">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -55813,7 +55813,7 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -55827,7 +55827,7 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -55855,7 +55855,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -55869,7 +55869,7 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -55883,7 +55883,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55897,7 +55897,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1592</v>
+        <v>1583</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55911,10 +55911,10 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1562</v>
+        <v>1581</v>
       </c>
       <c r="Q241">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="242" spans="14:17" x14ac:dyDescent="0.45">
@@ -55925,7 +55925,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55939,10 +55939,10 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q243">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -55953,10 +55953,10 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q244">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -55967,10 +55967,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1562</v>
+        <v>1586</v>
       </c>
       <c r="Q245">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -55981,7 +55981,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1596</v>
+        <v>1578</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -55995,7 +55995,7 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -56009,7 +56009,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -56023,10 +56023,10 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1599</v>
+        <v>1554</v>
       </c>
       <c r="Q249">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="250" spans="14:17" x14ac:dyDescent="0.45">
@@ -56037,10 +56037,10 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q250">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="251" spans="14:17" x14ac:dyDescent="0.45">
@@ -56051,7 +56051,7 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q251">
         <v>0.95</v>
@@ -56065,7 +56065,7 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1579</v>
+        <v>1591</v>
       </c>
       <c r="Q252">
         <v>0.95</v>
@@ -56079,7 +56079,7 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -56093,7 +56093,7 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -56107,7 +56107,7 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1552</v>
+        <v>1592</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -56121,7 +56121,7 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1591</v>
+        <v>1573</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -56135,7 +56135,7 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -56149,10 +56149,10 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q258">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -56163,7 +56163,7 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q259">
         <v>0.95</v>
@@ -56177,10 +56177,10 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1553</v>
+        <v>1599</v>
       </c>
       <c r="Q260">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -56191,7 +56191,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56205,7 +56205,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56219,7 +56219,7 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -56233,7 +56233,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56247,7 +56247,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56261,7 +56261,7 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q266">
         <v>0.85</v>
@@ -56275,7 +56275,7 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q267">
         <v>0.85</v>
@@ -56289,7 +56289,7 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1587</v>
+        <v>1568</v>
       </c>
       <c r="Q268">
         <v>0.85</v>
@@ -56303,10 +56303,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Q269">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56317,7 +56317,7 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q270">
         <v>0.85</v>
@@ -56331,10 +56331,10 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q271">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -56345,7 +56345,7 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -56359,7 +56359,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1584</v>
+        <v>1561</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56373,7 +56373,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56387,7 +56387,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56401,7 +56401,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56415,7 +56415,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56429,7 +56429,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56443,7 +56443,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56457,7 +56457,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56471,10 +56471,10 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1578</v>
+        <v>1591</v>
       </c>
       <c r="Q281">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="282" spans="14:17" x14ac:dyDescent="0.45">
@@ -56485,10 +56485,10 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1573</v>
+        <v>1554</v>
       </c>
       <c r="Q282">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -56497,7 +56497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15CBB587-B57B-400B-B822-24624EA391E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B99F33B6-D8A3-42DB-9F6E-F245DBCFE249}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD53BD40-5A08-4875-8D22-99D5E0E431EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86E40E2-83FC-4FA6-8F37-0968A27D7EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12018" uniqueCount="1888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12013" uniqueCount="1886">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -4885,555 +4885,555 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>~UC_Sets: R_S: Allregions</t>
   </si>
   <si>
@@ -5741,12 +5741,6 @@
   </si>
   <si>
     <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_020</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
   </si>
 </sst>
 </file>
@@ -5761,7 +5755,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5788,7 +5782,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5796,14 +5790,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5812,7 +5806,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5915,39 +5909,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5999,7 +5993,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -6110,6 +6104,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -6118,13 +6119,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -6189,31 +6183,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6384,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296D8679-9053-49A9-A5EC-159A2FA88455}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137989AC-CC96-4608-9039-F52C111DDA64}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37571,7 +37545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C448D6EA-FCA9-4E09-8D65-F2A9F1580401}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4682D185-9BBB-4575-AD4D-FAC86D452D25}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37615,7 +37589,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B11">
         <v>2030</v>
       </c>
@@ -37685,7 +37659,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B13">
         <v>2030</v>
       </c>
@@ -37755,7 +37729,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B15">
         <v>2030</v>
       </c>
@@ -37825,7 +37799,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B17">
         <v>2030</v>
       </c>
@@ -37836,7 +37810,7 @@
         <v>86</v>
       </c>
       <c r="E17">
-        <v>1.1000000000000001</v>
+        <v>1.1180000000000001</v>
       </c>
       <c r="F17" t="s">
         <v>87</v>
@@ -37848,19 +37822,19 @@
         <v>89</v>
       </c>
       <c r="I17" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
-      </c>
-      <c r="K17" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B18">
         <v>2030</v>
       </c>
@@ -37871,7 +37845,7 @@
         <v>86</v>
       </c>
       <c r="E18">
-        <v>1.1180000000000001</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F18" t="s">
         <v>87</v>
@@ -37883,16 +37857,16 @@
         <v>89</v>
       </c>
       <c r="I18" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J18" t="s">
-        <v>93</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K18" t="s">
+        <v>91</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -37927,7 +37901,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B20">
         <v>2030</v>
       </c>
@@ -37997,7 +37971,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B22">
         <v>2030</v>
       </c>
@@ -38067,7 +38041,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B24">
         <v>2030</v>
       </c>
@@ -38090,19 +38064,19 @@
         <v>89</v>
       </c>
       <c r="I24" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K24" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B25">
         <v>2030</v>
       </c>
@@ -38125,19 +38099,19 @@
         <v>89</v>
       </c>
       <c r="I25" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J25" t="s">
-        <v>93</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K25" t="s">
+        <v>91</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B26">
         <v>2030</v>
       </c>
@@ -38207,7 +38181,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B28">
         <v>2030</v>
       </c>
@@ -38277,7 +38251,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B30">
         <v>2030</v>
       </c>
@@ -38288,7 +38262,7 @@
         <v>104</v>
       </c>
       <c r="E30">
-        <v>57.6</v>
+        <v>43.3</v>
       </c>
       <c r="F30" t="s">
         <v>87</v>
@@ -38300,19 +38274,19 @@
         <v>89</v>
       </c>
       <c r="I30" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J30" t="s">
-        <v>93</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K30" t="s">
+        <v>91</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B31">
         <v>2030</v>
       </c>
@@ -38323,7 +38297,7 @@
         <v>104</v>
       </c>
       <c r="E31">
-        <v>43.3</v>
+        <v>57.6</v>
       </c>
       <c r="F31" t="s">
         <v>87</v>
@@ -38335,19 +38309,19 @@
         <v>89</v>
       </c>
       <c r="I31" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J31" t="s">
-        <v>90</v>
-      </c>
-      <c r="K31" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B32">
         <v>2030</v>
       </c>
@@ -38417,7 +38391,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>2030</v>
       </c>
@@ -38519,7 +38493,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B37">
         <v>2030</v>
       </c>
@@ -38589,7 +38563,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B39">
         <v>2030</v>
       </c>
@@ -38600,7 +38574,7 @@
         <v>104</v>
       </c>
       <c r="E39">
-        <v>38.1</v>
+        <v>47.4</v>
       </c>
       <c r="F39" t="s">
         <v>87</v>
@@ -38612,19 +38586,19 @@
         <v>89</v>
       </c>
       <c r="I39" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J39" t="s">
-        <v>93</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K39" t="s">
+        <v>91</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B40">
         <v>2030</v>
       </c>
@@ -38635,7 +38609,7 @@
         <v>104</v>
       </c>
       <c r="E40">
-        <v>47.4</v>
+        <v>38.1</v>
       </c>
       <c r="F40" t="s">
         <v>87</v>
@@ -38647,16 +38621,16 @@
         <v>89</v>
       </c>
       <c r="I40" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J40" t="s">
-        <v>90</v>
-      </c>
-      <c r="K40" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -38694,7 +38668,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B42">
         <v>2030</v>
       </c>
@@ -38729,7 +38703,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B43">
         <v>2030</v>
       </c>
@@ -38799,7 +38773,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B45">
         <v>2030</v>
       </c>
@@ -38904,7 +38878,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B48">
         <v>2030</v>
       </c>
@@ -38939,7 +38913,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B49">
         <v>2030</v>
       </c>
@@ -39009,7 +38983,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B51">
         <v>2030</v>
       </c>
@@ -39111,7 +39085,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B54">
         <v>2030</v>
       </c>
@@ -39122,7 +39096,7 @@
         <v>105</v>
       </c>
       <c r="E54">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="F54" t="s">
         <v>87</v>
@@ -39134,19 +39108,19 @@
         <v>89</v>
       </c>
       <c r="I54" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J54" t="s">
-        <v>93</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K54" t="s">
+        <v>91</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B55">
         <v>2030</v>
       </c>
@@ -39157,7 +39131,7 @@
         <v>105</v>
       </c>
       <c r="E55">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F55" t="s">
         <v>87</v>
@@ -39169,19 +39143,19 @@
         <v>89</v>
       </c>
       <c r="I55" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J55" t="s">
-        <v>90</v>
-      </c>
-      <c r="K55" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B56">
         <v>2030</v>
       </c>
@@ -39192,7 +39166,7 @@
         <v>105</v>
       </c>
       <c r="E56">
-        <v>25.5</v>
+        <v>19.8</v>
       </c>
       <c r="F56" t="s">
         <v>87</v>
@@ -39204,19 +39178,19 @@
         <v>89</v>
       </c>
       <c r="I56" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J56" t="s">
-        <v>90</v>
-      </c>
-      <c r="K56" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B57">
         <v>2030</v>
       </c>
@@ -39227,7 +39201,7 @@
         <v>105</v>
       </c>
       <c r="E57">
-        <v>19.8</v>
+        <v>25.5</v>
       </c>
       <c r="F57" t="s">
         <v>87</v>
@@ -39239,16 +39213,16 @@
         <v>89</v>
       </c>
       <c r="I57" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J57" t="s">
-        <v>93</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K57" t="s">
+        <v>91</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -39286,7 +39260,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B59">
         <v>2030</v>
       </c>
@@ -39321,7 +39295,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B60">
         <v>2030</v>
       </c>
@@ -39332,7 +39306,7 @@
         <v>105</v>
       </c>
       <c r="E60">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F60" t="s">
         <v>87</v>
@@ -39344,19 +39318,19 @@
         <v>89</v>
       </c>
       <c r="I60" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J60" t="s">
-        <v>90</v>
-      </c>
-      <c r="K60" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B61">
         <v>2030</v>
       </c>
@@ -39367,7 +39341,7 @@
         <v>105</v>
       </c>
       <c r="E61">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="F61" t="s">
         <v>87</v>
@@ -39379,16 +39353,16 @@
         <v>89</v>
       </c>
       <c r="I61" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J61" t="s">
-        <v>93</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K61" t="s">
+        <v>91</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
@@ -51832,7 +51806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE6FF9-E0D8-4B93-A22E-24081D89D3ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4BE1B3-6B4F-4632-92B1-28609EFA3C51}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53939,10 +53913,10 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1564</v>
+        <v>1584</v>
       </c>
       <c r="Q100">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="101" spans="14:17" x14ac:dyDescent="0.45">
@@ -53953,10 +53927,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q101">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53967,7 +53941,7 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q102">
         <v>0.85</v>
@@ -53981,7 +53955,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53995,7 +53969,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -54009,7 +53983,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1578</v>
+        <v>1593</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54023,7 +53997,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54037,7 +54011,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54051,10 +54025,10 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q108">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="109" spans="14:17" x14ac:dyDescent="0.45">
@@ -54065,10 +54039,10 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1591</v>
+        <v>1562</v>
       </c>
       <c r="Q109">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="110" spans="14:17" x14ac:dyDescent="0.45">
@@ -54079,10 +54053,10 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q110">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="111" spans="14:17" x14ac:dyDescent="0.45">
@@ -54093,10 +54067,10 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="Q111">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="112" spans="14:17" x14ac:dyDescent="0.45">
@@ -54107,10 +54081,10 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1552</v>
+        <v>1596</v>
       </c>
       <c r="Q112">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="113" spans="14:17" x14ac:dyDescent="0.45">
@@ -54121,10 +54095,10 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q113">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="114" spans="14:17" x14ac:dyDescent="0.45">
@@ -54135,7 +54109,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54149,7 +54123,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54163,7 +54137,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54177,10 +54151,10 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q117">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="118" spans="14:17" x14ac:dyDescent="0.45">
@@ -54191,7 +54165,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54205,7 +54179,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54219,7 +54193,7 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -54247,7 +54221,7 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q122">
         <v>0.85</v>
@@ -54261,10 +54235,10 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1579</v>
+        <v>1586</v>
       </c>
       <c r="Q123">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="124" spans="14:17" x14ac:dyDescent="0.45">
@@ -54275,10 +54249,10 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="Q124">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="125" spans="14:17" x14ac:dyDescent="0.45">
@@ -54289,10 +54263,10 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q125">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="126" spans="14:17" x14ac:dyDescent="0.45">
@@ -54303,10 +54277,10 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q126">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="127" spans="14:17" x14ac:dyDescent="0.45">
@@ -54317,10 +54291,10 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q127">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="128" spans="14:17" x14ac:dyDescent="0.45">
@@ -54331,10 +54305,10 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1599</v>
+        <v>1572</v>
       </c>
       <c r="Q128">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="129" spans="14:17" x14ac:dyDescent="0.45">
@@ -54345,10 +54319,10 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="Q129">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -54359,10 +54333,10 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q130">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -54373,7 +54347,7 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="Q131">
         <v>0.85</v>
@@ -54387,7 +54361,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1592</v>
+        <v>1563</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54415,10 +54389,10 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q134">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="135" spans="14:17" x14ac:dyDescent="0.45">
@@ -54429,10 +54403,10 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="Q135">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="136" spans="14:17" x14ac:dyDescent="0.45">
@@ -54443,7 +54417,7 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1596</v>
+        <v>1563</v>
       </c>
       <c r="Q136">
         <v>0.85</v>
@@ -54471,7 +54445,7 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q138">
         <v>0.85</v>
@@ -54485,7 +54459,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1591</v>
+        <v>1562</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54499,7 +54473,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54513,7 +54487,7 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1580</v>
+        <v>1562</v>
       </c>
       <c r="Q141">
         <v>0.85</v>
@@ -54527,10 +54501,10 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="Q142">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="143" spans="14:17" x14ac:dyDescent="0.45">
@@ -54541,7 +54515,7 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="Q143">
         <v>0.85</v>
@@ -54555,10 +54529,10 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="Q144">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="145" spans="14:17" x14ac:dyDescent="0.45">
@@ -54569,10 +54543,10 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="Q145">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="146" spans="14:17" x14ac:dyDescent="0.45">
@@ -54583,7 +54557,7 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -54597,7 +54571,7 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q147">
         <v>0.85</v>
@@ -54625,7 +54599,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54639,10 +54613,10 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="Q150">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="151" spans="14:17" x14ac:dyDescent="0.45">
@@ -54653,7 +54627,7 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -54667,7 +54641,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54681,10 +54655,10 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q153">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="154" spans="14:17" x14ac:dyDescent="0.45">
@@ -54695,7 +54669,7 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -54709,7 +54683,7 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1561</v>
+        <v>1552</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -54723,7 +54697,7 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q156">
         <v>0.85</v>
@@ -54737,10 +54711,10 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
       <c r="Q157">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -54751,10 +54725,10 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q158">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="159" spans="14:17" x14ac:dyDescent="0.45">
@@ -54768,7 +54742,7 @@
         <v>1599</v>
       </c>
       <c r="Q159">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="160" spans="14:17" x14ac:dyDescent="0.45">
@@ -54779,7 +54753,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54793,7 +54767,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1562</v>
+        <v>1586</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54807,7 +54781,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1578</v>
+        <v>1558</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54821,7 +54795,7 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1562</v>
+        <v>1596</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -54835,7 +54809,7 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -54849,10 +54823,10 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q165">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="166" spans="14:17" x14ac:dyDescent="0.45">
@@ -54863,10 +54837,10 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q166">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="167" spans="14:17" x14ac:dyDescent="0.45">
@@ -54877,10 +54851,10 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q167">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="168" spans="14:17" x14ac:dyDescent="0.45">
@@ -54891,7 +54865,7 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -54905,7 +54879,7 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1563</v>
+        <v>1583</v>
       </c>
       <c r="Q169">
         <v>0.85</v>
@@ -54919,10 +54893,10 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="Q170">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="171" spans="14:17" x14ac:dyDescent="0.45">
@@ -54933,10 +54907,10 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1592</v>
+        <v>1579</v>
       </c>
       <c r="Q171">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="172" spans="14:17" x14ac:dyDescent="0.45">
@@ -54961,10 +54935,10 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="Q173">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="174" spans="14:17" x14ac:dyDescent="0.45">
@@ -54975,7 +54949,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1598</v>
+        <v>1552</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -54989,7 +54963,7 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1558</v>
+        <v>1586</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -55003,7 +54977,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -55017,10 +54991,10 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q177">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="178" spans="14:17" x14ac:dyDescent="0.45">
@@ -55045,7 +55019,7 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1596</v>
+        <v>1554</v>
       </c>
       <c r="Q179">
         <v>0.85</v>
@@ -55059,7 +55033,7 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q180">
         <v>0.85</v>
@@ -55073,7 +55047,7 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1558</v>
+        <v>1584</v>
       </c>
       <c r="Q181">
         <v>0.85</v>
@@ -55087,7 +55061,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -55101,7 +55075,7 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -55115,10 +55089,10 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q184">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="185" spans="14:17" x14ac:dyDescent="0.45">
@@ -55129,10 +55103,10 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="Q185">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="186" spans="14:17" x14ac:dyDescent="0.45">
@@ -55143,10 +55117,10 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="Q186">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="187" spans="14:17" x14ac:dyDescent="0.45">
@@ -55157,10 +55131,10 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1556</v>
+        <v>1578</v>
       </c>
       <c r="Q187">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -55171,7 +55145,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55185,7 +55159,7 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1589</v>
+        <v>1563</v>
       </c>
       <c r="Q189">
         <v>0.85</v>
@@ -55199,7 +55173,7 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Q190">
         <v>0.85</v>
@@ -55213,7 +55187,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55227,7 +55201,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1552</v>
+        <v>1583</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55241,10 +55215,10 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1592</v>
+        <v>1576</v>
       </c>
       <c r="Q193">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="194" spans="14:17" x14ac:dyDescent="0.45">
@@ -55255,10 +55229,10 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="Q194">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="195" spans="14:17" x14ac:dyDescent="0.45">
@@ -55269,10 +55243,10 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1553</v>
+        <v>1596</v>
       </c>
       <c r="Q195">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="196" spans="14:17" x14ac:dyDescent="0.45">
@@ -55283,10 +55257,10 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
       <c r="Q196">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="197" spans="14:17" x14ac:dyDescent="0.45">
@@ -55297,10 +55271,10 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1563</v>
+        <v>1580</v>
       </c>
       <c r="Q197">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="198" spans="14:17" x14ac:dyDescent="0.45">
@@ -55311,7 +55285,7 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1568</v>
+        <v>1591</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -55325,7 +55299,7 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1552</v>
+        <v>1586</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -55339,7 +55313,7 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q200">
         <v>0.85</v>
@@ -55353,7 +55327,7 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1565</v>
+        <v>1583</v>
       </c>
       <c r="Q201">
         <v>0.85</v>
@@ -55367,7 +55341,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1587</v>
+        <v>1568</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55381,10 +55355,10 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1592</v>
+        <v>1552</v>
       </c>
       <c r="Q203">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="204" spans="14:17" x14ac:dyDescent="0.45">
@@ -55395,7 +55369,7 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -55409,7 +55383,7 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -55423,7 +55397,7 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="Q206">
         <v>0.85</v>
@@ -55437,7 +55411,7 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
       <c r="Q207">
         <v>0.85</v>
@@ -55451,10 +55425,10 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q208">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="209" spans="14:17" x14ac:dyDescent="0.45">
@@ -55465,10 +55439,10 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1576</v>
+        <v>1587</v>
       </c>
       <c r="Q209">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="210" spans="14:17" x14ac:dyDescent="0.45">
@@ -55479,7 +55453,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55493,7 +55467,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55507,7 +55481,7 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -55521,7 +55495,7 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -55535,10 +55509,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="Q214">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55552,7 +55526,7 @@
         <v>1584</v>
       </c>
       <c r="Q215">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -55566,7 +55540,7 @@
         <v>1553</v>
       </c>
       <c r="Q216">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -55577,10 +55551,10 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q217">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -55591,10 +55565,10 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q218">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -55605,10 +55579,10 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="Q219">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -55619,7 +55593,7 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -55647,7 +55621,7 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -55661,7 +55635,7 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -55675,7 +55649,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55689,7 +55663,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="Q225">
         <v>0.95</v>
@@ -55703,7 +55677,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55717,7 +55691,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1586</v>
+        <v>1561</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -55731,7 +55705,7 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1596</v>
+        <v>1561</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -55745,7 +55719,7 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -55759,7 +55733,7 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -55773,7 +55747,7 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -55787,7 +55761,7 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1558</v>
+        <v>1598</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -55829,7 +55803,7 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -55843,7 +55817,7 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1589</v>
+        <v>1568</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -55871,10 +55845,10 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="Q238">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -55885,10 +55859,10 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="Q239">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="240" spans="14:17" x14ac:dyDescent="0.45">
@@ -55899,10 +55873,10 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1558</v>
+        <v>1598</v>
       </c>
       <c r="Q240">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -55913,7 +55887,7 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -55927,7 +55901,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55941,7 +55915,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1565</v>
+        <v>1553</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -55955,7 +55929,7 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1553</v>
+        <v>1568</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -55983,7 +55957,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -56011,7 +55985,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -56025,7 +55999,7 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -56039,10 +56013,10 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="Q250">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="251" spans="14:17" x14ac:dyDescent="0.45">
@@ -56053,10 +56027,10 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="Q251">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="252" spans="14:17" x14ac:dyDescent="0.45">
@@ -56067,10 +56041,10 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q252">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="253" spans="14:17" x14ac:dyDescent="0.45">
@@ -56081,7 +56055,7 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1572</v>
+        <v>1598</v>
       </c>
       <c r="Q253">
         <v>0.95</v>
@@ -56095,10 +56069,10 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="Q254">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="255" spans="14:17" x14ac:dyDescent="0.45">
@@ -56109,10 +56083,10 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q255">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="256" spans="14:17" x14ac:dyDescent="0.45">
@@ -56123,10 +56097,10 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q256">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="257" spans="14:17" x14ac:dyDescent="0.45">
@@ -56137,10 +56111,10 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q257">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="258" spans="14:17" x14ac:dyDescent="0.45">
@@ -56151,10 +56125,10 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="Q258">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -56165,7 +56139,7 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q259">
         <v>0.85</v>
@@ -56193,7 +56167,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1599</v>
+        <v>1562</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56207,7 +56181,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56221,10 +56195,10 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1584</v>
+        <v>1562</v>
       </c>
       <c r="Q263">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="264" spans="14:17" x14ac:dyDescent="0.45">
@@ -56235,7 +56209,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1565</v>
+        <v>1586</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56249,7 +56223,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56263,7 +56237,7 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q266">
         <v>0.85</v>
@@ -56277,7 +56251,7 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="Q267">
         <v>0.85</v>
@@ -56291,7 +56265,7 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q268">
         <v>0.85</v>
@@ -56305,7 +56279,7 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q269">
         <v>0.85</v>
@@ -56319,7 +56293,7 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q270">
         <v>0.95</v>
@@ -56333,7 +56307,7 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="Q271">
         <v>0.95</v>
@@ -56347,10 +56321,10 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1583</v>
+        <v>1556</v>
       </c>
       <c r="Q272">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="273" spans="14:17" x14ac:dyDescent="0.45">
@@ -56361,7 +56335,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1561</v>
+        <v>1596</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56375,7 +56349,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56389,7 +56363,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56403,7 +56377,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1561</v>
+        <v>1589</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56417,7 +56391,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1593</v>
+        <v>1562</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56431,7 +56405,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56445,7 +56419,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56459,10 +56433,10 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q280">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="281" spans="14:17" x14ac:dyDescent="0.45">
@@ -56473,10 +56447,10 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1573</v>
+        <v>1558</v>
       </c>
       <c r="Q281">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="282" spans="14:17" x14ac:dyDescent="0.45">
@@ -56487,10 +56461,10 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="Q282">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -56499,8 +56473,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A7D315-6CC1-459D-A8D8-69F4E18FEA08}">
-  <dimension ref="A1:I54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1D30AA-8EB2-468C-AC1D-FAFA65B7D249}">
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -57816,32 +57790,6 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>2</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1886</v>
-      </c>
-      <c r="H54" t="s">
-        <v>1887</v>
-      </c>
-      <c r="I54">
-        <v>-1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86E40E2-83FC-4FA6-8F37-0968A27D7EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA4472C-FB51-49D1-B76B-58936723C25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12013" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12298" uniqueCount="2000">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -4885,48 +4885,522 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
   </si>
   <si>
@@ -4936,18 +5410,18 @@
     <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
   </si>
   <si>
@@ -4960,480 +5434,6 @@
     <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>~UC_Sets: R_S: Allregions</t>
   </si>
   <si>
@@ -5569,6 +5569,174 @@
     <t>elc_spv_POL_020</t>
   </si>
   <si>
+    <t>UCE_elcagg_spv_POL_021</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_022</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_023</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_024</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_025</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_026</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_027</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_028</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_029</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_030</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_031</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_032</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_033</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_034</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_035</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_036</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_037</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_038</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_039</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_040</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_041</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_042</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_043</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_044</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_045</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_046</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_047</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_048</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_048</t>
+  </si>
+  <si>
     <t>UCE_elcagg_wof_POL_001</t>
   </si>
   <si>
@@ -5741,6 +5909,180 @@
   </si>
   <si>
     <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_047</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_048</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
   </si>
 </sst>
 </file>
@@ -5755,7 +6097,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5782,7 +6124,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5790,14 +6132,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5806,7 +6148,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5909,39 +6251,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5993,7 +6335,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -6104,13 +6446,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -6119,6 +6454,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -6183,11 +6525,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6358,7 +6720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137989AC-CC96-4608-9039-F52C111DDA64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122767FA-7A80-4ACA-9C44-5FD5F7FAAAD1}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37545,7 +37907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4682D185-9BBB-4575-AD4D-FAC86D452D25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E2D7C2-BE5C-4348-AA76-9A4C01BD0FC9}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37589,7 +37951,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B11">
         <v>2030</v>
       </c>
@@ -37659,7 +38021,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B13">
         <v>2030</v>
       </c>
@@ -37729,7 +38091,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B15">
         <v>2030</v>
       </c>
@@ -37799,7 +38161,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B17">
         <v>2030</v>
       </c>
@@ -37810,7 +38172,7 @@
         <v>86</v>
       </c>
       <c r="E17">
-        <v>1.1180000000000001</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F17" t="s">
         <v>87</v>
@@ -37822,19 +38184,19 @@
         <v>89</v>
       </c>
       <c r="I17" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J17" t="s">
-        <v>93</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K17" t="s">
+        <v>91</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B18">
         <v>2030</v>
       </c>
@@ -37845,7 +38207,7 @@
         <v>86</v>
       </c>
       <c r="E18">
-        <v>1.1000000000000001</v>
+        <v>1.1180000000000001</v>
       </c>
       <c r="F18" t="s">
         <v>87</v>
@@ -37857,16 +38219,16 @@
         <v>89</v>
       </c>
       <c r="I18" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
-      </c>
-      <c r="K18" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -37901,7 +38263,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B20">
         <v>2030</v>
       </c>
@@ -37971,7 +38333,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B22">
         <v>2030</v>
       </c>
@@ -38041,7 +38403,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B24">
         <v>2030</v>
       </c>
@@ -38064,19 +38426,19 @@
         <v>89</v>
       </c>
       <c r="I24" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K24" t="s">
+        <v>91</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B25">
         <v>2030</v>
       </c>
@@ -38099,19 +38461,19 @@
         <v>89</v>
       </c>
       <c r="I25" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J25" t="s">
-        <v>90</v>
-      </c>
-      <c r="K25" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B26">
         <v>2030</v>
       </c>
@@ -38181,7 +38543,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B28">
         <v>2030</v>
       </c>
@@ -38251,7 +38613,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B30">
         <v>2030</v>
       </c>
@@ -38262,7 +38624,7 @@
         <v>104</v>
       </c>
       <c r="E30">
-        <v>43.3</v>
+        <v>57.6</v>
       </c>
       <c r="F30" t="s">
         <v>87</v>
@@ -38274,19 +38636,19 @@
         <v>89</v>
       </c>
       <c r="I30" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J30" t="s">
-        <v>90</v>
-      </c>
-      <c r="K30" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B31">
         <v>2030</v>
       </c>
@@ -38297,7 +38659,7 @@
         <v>104</v>
       </c>
       <c r="E31">
-        <v>57.6</v>
+        <v>43.3</v>
       </c>
       <c r="F31" t="s">
         <v>87</v>
@@ -38309,19 +38671,19 @@
         <v>89</v>
       </c>
       <c r="I31" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J31" t="s">
-        <v>93</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K31" t="s">
+        <v>91</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B32">
         <v>2030</v>
       </c>
@@ -38391,7 +38753,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>2030</v>
       </c>
@@ -38493,7 +38855,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B37">
         <v>2030</v>
       </c>
@@ -38563,7 +38925,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B39">
         <v>2030</v>
       </c>
@@ -38574,7 +38936,7 @@
         <v>104</v>
       </c>
       <c r="E39">
-        <v>47.4</v>
+        <v>38.1</v>
       </c>
       <c r="F39" t="s">
         <v>87</v>
@@ -38586,19 +38948,19 @@
         <v>89</v>
       </c>
       <c r="I39" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J39" t="s">
-        <v>90</v>
-      </c>
-      <c r="K39" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B40">
         <v>2030</v>
       </c>
@@ -38609,7 +38971,7 @@
         <v>104</v>
       </c>
       <c r="E40">
-        <v>38.1</v>
+        <v>47.4</v>
       </c>
       <c r="F40" t="s">
         <v>87</v>
@@ -38621,16 +38983,16 @@
         <v>89</v>
       </c>
       <c r="I40" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J40" t="s">
-        <v>93</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K40" t="s">
+        <v>91</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -38668,7 +39030,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B42">
         <v>2030</v>
       </c>
@@ -38703,7 +39065,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B43">
         <v>2030</v>
       </c>
@@ -38773,7 +39135,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B45">
         <v>2030</v>
       </c>
@@ -38878,7 +39240,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B48">
         <v>2030</v>
       </c>
@@ -38913,7 +39275,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B49">
         <v>2030</v>
       </c>
@@ -38983,7 +39345,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B51">
         <v>2030</v>
       </c>
@@ -39085,7 +39447,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B54">
         <v>2030</v>
       </c>
@@ -39096,7 +39458,7 @@
         <v>105</v>
       </c>
       <c r="E54">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F54" t="s">
         <v>87</v>
@@ -39108,19 +39470,19 @@
         <v>89</v>
       </c>
       <c r="I54" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J54" t="s">
-        <v>90</v>
-      </c>
-      <c r="K54" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B55">
         <v>2030</v>
       </c>
@@ -39131,7 +39493,7 @@
         <v>105</v>
       </c>
       <c r="E55">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="F55" t="s">
         <v>87</v>
@@ -39143,19 +39505,19 @@
         <v>89</v>
       </c>
       <c r="I55" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J55" t="s">
-        <v>93</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K55" t="s">
+        <v>91</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B56">
         <v>2030</v>
       </c>
@@ -39166,7 +39528,7 @@
         <v>105</v>
       </c>
       <c r="E56">
-        <v>19.8</v>
+        <v>25.5</v>
       </c>
       <c r="F56" t="s">
         <v>87</v>
@@ -39178,19 +39540,19 @@
         <v>89</v>
       </c>
       <c r="I56" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J56" t="s">
-        <v>93</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K56" t="s">
+        <v>91</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B57">
         <v>2030</v>
       </c>
@@ -39201,7 +39563,7 @@
         <v>105</v>
       </c>
       <c r="E57">
-        <v>25.5</v>
+        <v>19.8</v>
       </c>
       <c r="F57" t="s">
         <v>87</v>
@@ -39213,16 +39575,16 @@
         <v>89</v>
       </c>
       <c r="I57" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J57" t="s">
-        <v>90</v>
-      </c>
-      <c r="K57" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -39260,7 +39622,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B59">
         <v>2030</v>
       </c>
@@ -39295,7 +39657,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B60">
         <v>2030</v>
       </c>
@@ -39306,7 +39668,7 @@
         <v>105</v>
       </c>
       <c r="E60">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="F60" t="s">
         <v>87</v>
@@ -39318,19 +39680,19 @@
         <v>89</v>
       </c>
       <c r="I60" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J60" t="s">
-        <v>93</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K60" t="s">
+        <v>91</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B61">
         <v>2030</v>
       </c>
@@ -39341,7 +39703,7 @@
         <v>105</v>
       </c>
       <c r="E61">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F61" t="s">
         <v>87</v>
@@ -39353,16 +39715,16 @@
         <v>89</v>
       </c>
       <c r="I61" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J61" t="s">
-        <v>90</v>
-      </c>
-      <c r="K61" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
@@ -51806,7 +52168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4BE1B3-6B4F-4632-92B1-28609EFA3C51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14155DC-10BE-4C72-AA97-A2EFEDF24626}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53913,10 +54275,10 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1584</v>
+        <v>1554</v>
       </c>
       <c r="Q100">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="101" spans="14:17" x14ac:dyDescent="0.45">
@@ -53927,10 +54289,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1596</v>
+        <v>1581</v>
       </c>
       <c r="Q101">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53941,7 +54303,7 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="Q102">
         <v>0.85</v>
@@ -53955,7 +54317,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53969,7 +54331,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -53983,7 +54345,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -53997,7 +54359,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54011,7 +54373,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54025,7 +54387,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54039,10 +54401,10 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="Q109">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="110" spans="14:17" x14ac:dyDescent="0.45">
@@ -54053,10 +54415,10 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1573</v>
+        <v>1553</v>
       </c>
       <c r="Q110">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="111" spans="14:17" x14ac:dyDescent="0.45">
@@ -54067,7 +54429,7 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="Q111">
         <v>0.95</v>
@@ -54081,10 +54443,10 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q112">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="113" spans="14:17" x14ac:dyDescent="0.45">
@@ -54095,10 +54457,10 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1589</v>
+        <v>1552</v>
       </c>
       <c r="Q113">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="114" spans="14:17" x14ac:dyDescent="0.45">
@@ -54109,7 +54471,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54123,7 +54485,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1592</v>
+        <v>1565</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54137,7 +54499,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54151,7 +54513,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1561</v>
+        <v>1578</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54165,7 +54527,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54179,7 +54541,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54193,7 +54555,7 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1565</v>
+        <v>1592</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -54207,7 +54569,7 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1591</v>
+        <v>1568</v>
       </c>
       <c r="Q121">
         <v>0.85</v>
@@ -54221,7 +54583,7 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="Q122">
         <v>0.85</v>
@@ -54235,7 +54597,7 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1586</v>
+        <v>1598</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -54249,7 +54611,7 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="Q124">
         <v>0.85</v>
@@ -54263,10 +54625,10 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q125">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="126" spans="14:17" x14ac:dyDescent="0.45">
@@ -54277,10 +54639,10 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q126">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="127" spans="14:17" x14ac:dyDescent="0.45">
@@ -54291,10 +54653,10 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1592</v>
+        <v>1553</v>
       </c>
       <c r="Q127">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="128" spans="14:17" x14ac:dyDescent="0.45">
@@ -54305,10 +54667,10 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1572</v>
+        <v>1596</v>
       </c>
       <c r="Q128">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="129" spans="14:17" x14ac:dyDescent="0.45">
@@ -54319,10 +54681,10 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1595</v>
+        <v>1568</v>
       </c>
       <c r="Q129">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="130" spans="14:17" x14ac:dyDescent="0.45">
@@ -54333,10 +54695,10 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="Q130">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -54347,7 +54709,7 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q131">
         <v>0.85</v>
@@ -54361,7 +54723,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54389,10 +54751,10 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="Q134">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="135" spans="14:17" x14ac:dyDescent="0.45">
@@ -54403,10 +54765,10 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="Q135">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="136" spans="14:17" x14ac:dyDescent="0.45">
@@ -54417,10 +54779,10 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="Q136">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="137" spans="14:17" x14ac:dyDescent="0.45">
@@ -54431,7 +54793,7 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q137">
         <v>0.85</v>
@@ -54445,7 +54807,7 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="Q138">
         <v>0.85</v>
@@ -54459,7 +54821,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54473,7 +54835,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54487,7 +54849,7 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q141">
         <v>0.85</v>
@@ -54501,10 +54863,10 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1554</v>
+        <v>1599</v>
       </c>
       <c r="Q142">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="143" spans="14:17" x14ac:dyDescent="0.45">
@@ -54515,7 +54877,7 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="Q143">
         <v>0.85</v>
@@ -54529,7 +54891,7 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="Q144">
         <v>0.85</v>
@@ -54543,7 +54905,7 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -54557,7 +54919,7 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -54571,10 +54933,10 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="Q147">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="148" spans="14:17" x14ac:dyDescent="0.45">
@@ -54585,7 +54947,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1573</v>
+        <v>1596</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54599,7 +54961,7 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="Q149">
         <v>0.85</v>
@@ -54613,10 +54975,10 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="Q150">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="151" spans="14:17" x14ac:dyDescent="0.45">
@@ -54627,7 +54989,7 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -54641,7 +55003,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -54655,7 +55017,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -54669,7 +55031,7 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -54683,7 +55045,7 @@
         <v>1655</v>
       </c>
       <c r="P155" t="s">
-        <v>1552</v>
+        <v>1568</v>
       </c>
       <c r="Q155">
         <v>0.85</v>
@@ -54697,10 +55059,10 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
       <c r="Q156">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -54711,7 +55073,7 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q157">
         <v>0.95</v>
@@ -54725,10 +55087,10 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q158">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="159" spans="14:17" x14ac:dyDescent="0.45">
@@ -54739,10 +55101,10 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q159">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="160" spans="14:17" x14ac:dyDescent="0.45">
@@ -54753,7 +55115,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -54767,7 +55129,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1586</v>
+        <v>1563</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -54781,7 +55143,7 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="Q162">
         <v>0.85</v>
@@ -54795,7 +55157,7 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="Q163">
         <v>0.85</v>
@@ -54809,7 +55171,7 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -54823,7 +55185,7 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="Q165">
         <v>0.85</v>
@@ -54837,7 +55199,7 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -54851,7 +55213,7 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1592</v>
+        <v>1563</v>
       </c>
       <c r="Q167">
         <v>0.85</v>
@@ -54865,7 +55227,7 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -54879,10 +55241,10 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="Q169">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="170" spans="14:17" x14ac:dyDescent="0.45">
@@ -54893,7 +55255,7 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1594</v>
+        <v>1573</v>
       </c>
       <c r="Q170">
         <v>0.95</v>
@@ -54907,7 +55269,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1579</v>
+        <v>1591</v>
       </c>
       <c r="Q171">
         <v>0.95</v>
@@ -54921,7 +55283,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -54935,7 +55297,7 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -54949,7 +55311,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -54963,7 +55325,7 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -54977,7 +55339,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -54991,10 +55353,10 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q177">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="178" spans="14:17" x14ac:dyDescent="0.45">
@@ -55005,10 +55367,10 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1599</v>
+        <v>1556</v>
       </c>
       <c r="Q178">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -55019,10 +55381,10 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1554</v>
+        <v>1598</v>
       </c>
       <c r="Q179">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -55033,10 +55395,10 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="Q180">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -55047,10 +55409,10 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1584</v>
+        <v>1558</v>
       </c>
       <c r="Q181">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -55061,7 +55423,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -55075,7 +55437,7 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1586</v>
+        <v>1552</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -55103,7 +55465,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1553</v>
+        <v>1589</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55117,7 +55479,7 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1589</v>
+        <v>1562</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -55131,7 +55493,7 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q187">
         <v>0.85</v>
@@ -55145,7 +55507,7 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q188">
         <v>0.85</v>
@@ -55159,10 +55521,10 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q189">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="190" spans="14:17" x14ac:dyDescent="0.45">
@@ -55176,7 +55538,7 @@
         <v>1598</v>
       </c>
       <c r="Q190">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="191" spans="14:17" x14ac:dyDescent="0.45">
@@ -55187,7 +55549,7 @@
         <v>1691</v>
       </c>
       <c r="P191" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q191">
         <v>0.85</v>
@@ -55201,7 +55563,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55215,10 +55577,10 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="Q193">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="194" spans="14:17" x14ac:dyDescent="0.45">
@@ -55229,10 +55591,10 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="Q194">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="195" spans="14:17" x14ac:dyDescent="0.45">
@@ -55243,7 +55605,7 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1596</v>
+        <v>1562</v>
       </c>
       <c r="Q195">
         <v>0.85</v>
@@ -55271,7 +55633,7 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1580</v>
+        <v>1592</v>
       </c>
       <c r="Q197">
         <v>0.85</v>
@@ -55285,7 +55647,7 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q198">
         <v>0.85</v>
@@ -55299,7 +55661,7 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q199">
         <v>0.85</v>
@@ -55313,10 +55675,10 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="Q200">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="201" spans="14:17" x14ac:dyDescent="0.45">
@@ -55327,10 +55689,10 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="Q201">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="202" spans="14:17" x14ac:dyDescent="0.45">
@@ -55341,7 +55703,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55355,10 +55717,10 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1552</v>
+        <v>1599</v>
       </c>
       <c r="Q203">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="204" spans="14:17" x14ac:dyDescent="0.45">
@@ -55383,7 +55745,7 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -55397,7 +55759,7 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1565</v>
+        <v>1591</v>
       </c>
       <c r="Q206">
         <v>0.85</v>
@@ -55411,10 +55773,10 @@
         <v>1707</v>
       </c>
       <c r="P207" t="s">
-        <v>1552</v>
+        <v>1591</v>
       </c>
       <c r="Q207">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="208" spans="14:17" x14ac:dyDescent="0.45">
@@ -55425,10 +55787,10 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1592</v>
+        <v>1554</v>
       </c>
       <c r="Q208">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="209" spans="14:17" x14ac:dyDescent="0.45">
@@ -55439,7 +55801,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55453,7 +55815,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55467,7 +55829,7 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q211">
         <v>0.85</v>
@@ -55481,7 +55843,7 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -55509,10 +55871,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1563</v>
+        <v>1593</v>
       </c>
       <c r="Q214">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55523,10 +55885,10 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="Q215">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -55537,10 +55899,10 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1553</v>
+        <v>1598</v>
       </c>
       <c r="Q216">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -55551,10 +55913,10 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q217">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -55568,7 +55930,7 @@
         <v>1573</v>
       </c>
       <c r="Q218">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -55579,10 +55941,10 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="Q219">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -55593,10 +55955,10 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="Q220">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -55607,10 +55969,10 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1563</v>
+        <v>1576</v>
       </c>
       <c r="Q221">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -55621,7 +55983,7 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -55635,7 +55997,7 @@
         <v>1723</v>
       </c>
       <c r="P223" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -55649,7 +56011,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -55663,10 +56025,10 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="Q225">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="226" spans="14:17" x14ac:dyDescent="0.45">
@@ -55677,7 +56039,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -55691,7 +56053,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -55705,7 +56067,7 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -55719,7 +56081,7 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -55733,7 +56095,7 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1561</v>
+        <v>1589</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -55775,7 +56137,7 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1573</v>
+        <v>1553</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -55789,7 +56151,7 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -55803,7 +56165,7 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -55831,7 +56193,7 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="Q237">
         <v>0.95</v>
@@ -55845,10 +56207,10 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q238">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -55859,7 +56221,7 @@
         <v>1739</v>
       </c>
       <c r="P239" t="s">
-        <v>1565</v>
+        <v>1578</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -55873,7 +56235,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -55901,7 +56263,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -55915,7 +56277,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1553</v>
+        <v>1592</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -55943,10 +56305,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1592</v>
+        <v>1554</v>
       </c>
       <c r="Q245">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -55957,10 +56319,10 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q246">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="247" spans="14:17" x14ac:dyDescent="0.45">
@@ -55971,7 +56333,7 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -55985,7 +56347,7 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1596</v>
+        <v>1586</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -55999,7 +56361,7 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1568</v>
+        <v>1596</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -56013,10 +56375,10 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="Q250">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="251" spans="14:17" x14ac:dyDescent="0.45">
@@ -56030,7 +56392,7 @@
         <v>1562</v>
       </c>
       <c r="Q251">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="252" spans="14:17" x14ac:dyDescent="0.45">
@@ -56041,10 +56403,10 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1558</v>
+        <v>1589</v>
       </c>
       <c r="Q252">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="253" spans="14:17" x14ac:dyDescent="0.45">
@@ -56055,10 +56417,10 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q253">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="254" spans="14:17" x14ac:dyDescent="0.45">
@@ -56069,7 +56431,7 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1599</v>
+        <v>1573</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -56083,7 +56445,7 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -56097,7 +56459,7 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1599</v>
+        <v>1558</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -56111,7 +56473,7 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -56125,10 +56487,10 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1599</v>
+        <v>1562</v>
       </c>
       <c r="Q258">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -56139,10 +56501,10 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q259">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="260" spans="14:17" x14ac:dyDescent="0.45">
@@ -56153,10 +56515,10 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q260">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -56167,7 +56529,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1562</v>
+        <v>1596</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56181,7 +56543,7 @@
         <v>1762</v>
       </c>
       <c r="P262" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -56195,10 +56557,10 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q263">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="264" spans="14:17" x14ac:dyDescent="0.45">
@@ -56209,7 +56571,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1586</v>
+        <v>1563</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56223,7 +56585,7 @@
         <v>1765</v>
       </c>
       <c r="P265" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -56237,10 +56599,10 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q266">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="267" spans="14:17" x14ac:dyDescent="0.45">
@@ -56251,10 +56613,10 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q267">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="268" spans="14:17" x14ac:dyDescent="0.45">
@@ -56265,10 +56627,10 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q268">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="269" spans="14:17" x14ac:dyDescent="0.45">
@@ -56279,10 +56641,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="Q269">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56293,7 +56655,7 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="Q270">
         <v>0.95</v>
@@ -56307,7 +56669,7 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1564</v>
+        <v>1573</v>
       </c>
       <c r="Q271">
         <v>0.95</v>
@@ -56321,10 +56683,10 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1556</v>
+        <v>1583</v>
       </c>
       <c r="Q272">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="273" spans="14:17" x14ac:dyDescent="0.45">
@@ -56335,7 +56697,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56349,7 +56711,7 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1552</v>
+        <v>1599</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -56363,7 +56725,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56377,7 +56739,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1589</v>
+        <v>1565</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56391,7 +56753,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56405,7 +56767,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56419,7 +56781,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1568</v>
+        <v>1591</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56433,10 +56795,10 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1596</v>
+        <v>1573</v>
       </c>
       <c r="Q280">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="281" spans="14:17" x14ac:dyDescent="0.45">
@@ -56447,10 +56809,10 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1558</v>
+        <v>1586</v>
       </c>
       <c r="Q281">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="282" spans="14:17" x14ac:dyDescent="0.45">
@@ -56461,10 +56823,10 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="Q282">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -56473,8 +56835,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1D30AA-8EB2-468C-AC1D-FAFA65B7D249}">
-  <dimension ref="A1:I53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5684605C-F73E-4AD7-A38B-CA6F3FEA5964}">
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -57790,6 +58152,1488 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1886</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1887</v>
+      </c>
+      <c r="I54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1889</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1891</v>
+      </c>
+      <c r="I56">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1892</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1893</v>
+      </c>
+      <c r="I57">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1895</v>
+      </c>
+      <c r="I58">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1896</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1897</v>
+      </c>
+      <c r="I59">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1899</v>
+      </c>
+      <c r="I60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1901</v>
+      </c>
+      <c r="I61">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1902</v>
+      </c>
+      <c r="H62" t="s">
+        <v>1903</v>
+      </c>
+      <c r="I62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1906</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1907</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1909</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1911</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I67">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1914</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1915</v>
+      </c>
+      <c r="I68">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1916</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1917</v>
+      </c>
+      <c r="I69">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1919</v>
+      </c>
+      <c r="I70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1920</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1921</v>
+      </c>
+      <c r="I71">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1923</v>
+      </c>
+      <c r="I72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1925</v>
+      </c>
+      <c r="I73">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1926</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1927</v>
+      </c>
+      <c r="I74">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1928</v>
+      </c>
+      <c r="H75" t="s">
+        <v>1929</v>
+      </c>
+      <c r="I75">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1930</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1931</v>
+      </c>
+      <c r="I76">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1933</v>
+      </c>
+      <c r="I77">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1934</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1935</v>
+      </c>
+      <c r="I78">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1937</v>
+      </c>
+      <c r="I79">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1939</v>
+      </c>
+      <c r="I80">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H81" t="s">
+        <v>1941</v>
+      </c>
+      <c r="I81">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H82" t="s">
+        <v>1943</v>
+      </c>
+      <c r="I82">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H83" t="s">
+        <v>1945</v>
+      </c>
+      <c r="I83">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1946</v>
+      </c>
+      <c r="H84" t="s">
+        <v>1947</v>
+      </c>
+      <c r="I84">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H85" t="s">
+        <v>1949</v>
+      </c>
+      <c r="I85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1950</v>
+      </c>
+      <c r="H86" t="s">
+        <v>1951</v>
+      </c>
+      <c r="I86">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1952</v>
+      </c>
+      <c r="H87" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I87">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1954</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1955</v>
+      </c>
+      <c r="I88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="G89" t="s">
+        <v>1956</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1957</v>
+      </c>
+      <c r="I89">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H90" t="s">
+        <v>1959</v>
+      </c>
+      <c r="I90">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H91" t="s">
+        <v>1961</v>
+      </c>
+      <c r="I91">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1962</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1963</v>
+      </c>
+      <c r="I92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1964</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1965</v>
+      </c>
+      <c r="I93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H94" t="s">
+        <v>1967</v>
+      </c>
+      <c r="I94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1969</v>
+      </c>
+      <c r="I95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1971</v>
+      </c>
+      <c r="I96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1973</v>
+      </c>
+      <c r="I97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1975</v>
+      </c>
+      <c r="I98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1977</v>
+      </c>
+      <c r="I99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1979</v>
+      </c>
+      <c r="I100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1981</v>
+      </c>
+      <c r="I101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H102" t="s">
+        <v>1983</v>
+      </c>
+      <c r="I102">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1985</v>
+      </c>
+      <c r="I103">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="G104" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H104" t="s">
+        <v>1987</v>
+      </c>
+      <c r="I104">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1989</v>
+      </c>
+      <c r="I105">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="G106" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H106" t="s">
+        <v>1991</v>
+      </c>
+      <c r="I106">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1992</v>
+      </c>
+      <c r="H107" t="s">
+        <v>1993</v>
+      </c>
+      <c r="I107">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1994</v>
+      </c>
+      <c r="H108" t="s">
+        <v>1995</v>
+      </c>
+      <c r="I108">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H109" t="s">
+        <v>1997</v>
+      </c>
+      <c r="I109">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H110" t="s">
+        <v>1999</v>
+      </c>
+      <c r="I110">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA4472C-FB51-49D1-B76B-58936723C25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0E7331-7BFB-4BCD-A178-FF5F1DF77B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12298" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12013" uniqueCount="1886">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -4891,36 +4891,117 @@
     <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
+    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
   </si>
   <si>
@@ -4933,507 +5014,426 @@
     <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
     <t>~UC_Sets: R_S: Allregions</t>
   </si>
   <si>
@@ -5569,174 +5569,6 @@
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>UCE_elcagg_spv_POL_021</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_022</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_023</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_023</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_024</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_025</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_025</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_026</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_027</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_027</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_028</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_029</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_030</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_031</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_032</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_033</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_034</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_035</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_036</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_037</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_038</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_039</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_040</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_041</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_042</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_043</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_044</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_045</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_046</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_047</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_spv_POL_048</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_048</t>
-  </si>
-  <si>
     <t>UCE_elcagg_wof_POL_001</t>
   </si>
   <si>
@@ -5909,180 +5741,6 @@
   </si>
   <si>
     <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_020</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_032</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_042</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_046</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_047</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
-  </si>
-  <si>
-    <t>UCE_elcagg_won_POL_048</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
   </si>
 </sst>
 </file>
@@ -6097,7 +5755,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -6124,7 +5782,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -6132,14 +5790,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -6148,7 +5806,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -6251,39 +5909,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -6335,7 +5993,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -6446,6 +6104,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -6454,13 +6119,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -6525,31 +6183,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6720,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122767FA-7A80-4ACA-9C44-5FD5F7FAAAD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6CC482-8921-475E-B023-BAAD326AA9C1}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37907,7 +37545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E2D7C2-BE5C-4348-AA76-9A4C01BD0FC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B860D5-4C1C-4E89-898E-09CEFFC7FDCF}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37951,7 +37589,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B11">
         <v>2030</v>
       </c>
@@ -38021,7 +37659,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B13">
         <v>2030</v>
       </c>
@@ -38091,7 +37729,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B15">
         <v>2030</v>
       </c>
@@ -38161,7 +37799,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B17">
         <v>2030</v>
       </c>
@@ -38172,7 +37810,7 @@
         <v>86</v>
       </c>
       <c r="E17">
-        <v>1.1000000000000001</v>
+        <v>1.1180000000000001</v>
       </c>
       <c r="F17" t="s">
         <v>87</v>
@@ -38184,19 +37822,19 @@
         <v>89</v>
       </c>
       <c r="I17" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
-      </c>
-      <c r="K17" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B18">
         <v>2030</v>
       </c>
@@ -38207,7 +37845,7 @@
         <v>86</v>
       </c>
       <c r="E18">
-        <v>1.1180000000000001</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F18" t="s">
         <v>87</v>
@@ -38219,16 +37857,16 @@
         <v>89</v>
       </c>
       <c r="I18" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J18" t="s">
-        <v>93</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K18" t="s">
+        <v>91</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -38263,7 +37901,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B20">
         <v>2030</v>
       </c>
@@ -38333,7 +37971,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B22">
         <v>2030</v>
       </c>
@@ -38403,7 +38041,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B24">
         <v>2030</v>
       </c>
@@ -38426,19 +38064,19 @@
         <v>89</v>
       </c>
       <c r="I24" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K24" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B25">
         <v>2030</v>
       </c>
@@ -38461,19 +38099,19 @@
         <v>89</v>
       </c>
       <c r="I25" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J25" t="s">
-        <v>93</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K25" t="s">
+        <v>91</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B26">
         <v>2030</v>
       </c>
@@ -38543,7 +38181,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B28">
         <v>2030</v>
       </c>
@@ -38613,7 +38251,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B30">
         <v>2030</v>
       </c>
@@ -38624,7 +38262,7 @@
         <v>104</v>
       </c>
       <c r="E30">
-        <v>57.6</v>
+        <v>43.3</v>
       </c>
       <c r="F30" t="s">
         <v>87</v>
@@ -38636,19 +38274,19 @@
         <v>89</v>
       </c>
       <c r="I30" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J30" t="s">
-        <v>93</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K30" t="s">
+        <v>91</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B31">
         <v>2030</v>
       </c>
@@ -38659,7 +38297,7 @@
         <v>104</v>
       </c>
       <c r="E31">
-        <v>43.3</v>
+        <v>57.6</v>
       </c>
       <c r="F31" t="s">
         <v>87</v>
@@ -38671,19 +38309,19 @@
         <v>89</v>
       </c>
       <c r="I31" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J31" t="s">
-        <v>90</v>
-      </c>
-      <c r="K31" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B32">
         <v>2030</v>
       </c>
@@ -38753,7 +38391,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>2030</v>
       </c>
@@ -38855,7 +38493,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B37">
         <v>2030</v>
       </c>
@@ -38925,7 +38563,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B39">
         <v>2030</v>
       </c>
@@ -38936,7 +38574,7 @@
         <v>104</v>
       </c>
       <c r="E39">
-        <v>38.1</v>
+        <v>47.4</v>
       </c>
       <c r="F39" t="s">
         <v>87</v>
@@ -38948,19 +38586,19 @@
         <v>89</v>
       </c>
       <c r="I39" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J39" t="s">
-        <v>93</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K39" t="s">
+        <v>91</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B40">
         <v>2030</v>
       </c>
@@ -38971,7 +38609,7 @@
         <v>104</v>
       </c>
       <c r="E40">
-        <v>47.4</v>
+        <v>38.1</v>
       </c>
       <c r="F40" t="s">
         <v>87</v>
@@ -38983,16 +38621,16 @@
         <v>89</v>
       </c>
       <c r="I40" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J40" t="s">
-        <v>90</v>
-      </c>
-      <c r="K40" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -39030,7 +38668,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B42">
         <v>2030</v>
       </c>
@@ -39065,7 +38703,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B43">
         <v>2030</v>
       </c>
@@ -39135,7 +38773,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B45">
         <v>2030</v>
       </c>
@@ -39240,7 +38878,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B48">
         <v>2030</v>
       </c>
@@ -39275,7 +38913,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B49">
         <v>2030</v>
       </c>
@@ -39345,7 +38983,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B51">
         <v>2030</v>
       </c>
@@ -39447,7 +39085,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B54">
         <v>2030</v>
       </c>
@@ -39458,7 +39096,7 @@
         <v>105</v>
       </c>
       <c r="E54">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="F54" t="s">
         <v>87</v>
@@ -39470,19 +39108,19 @@
         <v>89</v>
       </c>
       <c r="I54" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J54" t="s">
-        <v>93</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K54" t="s">
+        <v>91</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B55">
         <v>2030</v>
       </c>
@@ -39493,7 +39131,7 @@
         <v>105</v>
       </c>
       <c r="E55">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F55" t="s">
         <v>87</v>
@@ -39505,19 +39143,19 @@
         <v>89</v>
       </c>
       <c r="I55" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J55" t="s">
-        <v>90</v>
-      </c>
-      <c r="K55" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B56">
         <v>2030</v>
       </c>
@@ -39528,7 +39166,7 @@
         <v>105</v>
       </c>
       <c r="E56">
-        <v>25.5</v>
+        <v>19.8</v>
       </c>
       <c r="F56" t="s">
         <v>87</v>
@@ -39540,19 +39178,19 @@
         <v>89</v>
       </c>
       <c r="I56" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J56" t="s">
-        <v>90</v>
-      </c>
-      <c r="K56" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B57">
         <v>2030</v>
       </c>
@@ -39563,7 +39201,7 @@
         <v>105</v>
       </c>
       <c r="E57">
-        <v>19.8</v>
+        <v>25.5</v>
       </c>
       <c r="F57" t="s">
         <v>87</v>
@@ -39575,16 +39213,16 @@
         <v>89</v>
       </c>
       <c r="I57" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J57" t="s">
-        <v>93</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K57" t="s">
+        <v>91</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -39622,7 +39260,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B59">
         <v>2030</v>
       </c>
@@ -39657,7 +39295,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="2:12" ht="299.25" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="B60">
         <v>2030</v>
       </c>
@@ -39668,7 +39306,7 @@
         <v>105</v>
       </c>
       <c r="E60">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F60" t="s">
         <v>87</v>
@@ -39680,19 +39318,19 @@
         <v>89</v>
       </c>
       <c r="I60" s="10">
-        <v>45566</v>
+        <v>45356</v>
       </c>
       <c r="J60" t="s">
-        <v>90</v>
-      </c>
-      <c r="K60" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" ht="313.5" x14ac:dyDescent="0.45">
       <c r="B61">
         <v>2030</v>
       </c>
@@ -39703,7 +39341,7 @@
         <v>105</v>
       </c>
       <c r="E61">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="F61" t="s">
         <v>87</v>
@@ -39715,16 +39353,16 @@
         <v>89</v>
       </c>
       <c r="I61" s="10">
-        <v>45356</v>
+        <v>45566</v>
       </c>
       <c r="J61" t="s">
-        <v>93</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="K61" t="s">
+        <v>91</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
@@ -52168,7 +51806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14155DC-10BE-4C72-AA97-A2EFEDF24626}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B712E537-29F2-4C33-B682-EC6583100085}">
   <dimension ref="B2:Q282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -54303,7 +53941,7 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="Q102">
         <v>0.85</v>
@@ -54345,7 +53983,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -54359,7 +53997,7 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
       <c r="Q106">
         <v>0.85</v>
@@ -54373,7 +54011,7 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="Q107">
         <v>0.85</v>
@@ -54401,7 +54039,7 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q109">
         <v>0.95</v>
@@ -54415,10 +54053,10 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="Q110">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="111" spans="14:17" x14ac:dyDescent="0.45">
@@ -54429,10 +54067,10 @@
         <v>1611</v>
       </c>
       <c r="P111" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q111">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="112" spans="14:17" x14ac:dyDescent="0.45">
@@ -54443,7 +54081,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54457,7 +54095,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1552</v>
+        <v>1584</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54471,7 +54109,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54485,7 +54123,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54499,7 +54137,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54513,7 +54151,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54527,7 +54165,7 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="Q118">
         <v>0.85</v>
@@ -54541,7 +54179,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1587</v>
+        <v>1578</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54555,7 +54193,7 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1592</v>
+        <v>1563</v>
       </c>
       <c r="Q120">
         <v>0.85</v>
@@ -54569,10 +54207,10 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="Q121">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="122" spans="14:17" x14ac:dyDescent="0.45">
@@ -54583,10 +54221,10 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="Q122">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="123" spans="14:17" x14ac:dyDescent="0.45">
@@ -54597,10 +54235,10 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1598</v>
+        <v>1579</v>
       </c>
       <c r="Q123">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="124" spans="14:17" x14ac:dyDescent="0.45">
@@ -54625,7 +54263,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1592</v>
+        <v>1565</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54639,7 +54277,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54667,7 +54305,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54695,7 +54333,7 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="Q130">
         <v>0.85</v>
@@ -54723,7 +54361,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54737,7 +54375,7 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -54751,10 +54389,10 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1558</v>
+        <v>1591</v>
       </c>
       <c r="Q134">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="135" spans="14:17" x14ac:dyDescent="0.45">
@@ -54765,10 +54403,10 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q135">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="136" spans="14:17" x14ac:dyDescent="0.45">
@@ -54779,7 +54417,7 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="Q136">
         <v>0.95</v>
@@ -54793,10 +54431,10 @@
         <v>1637</v>
       </c>
       <c r="P137" t="s">
-        <v>1598</v>
+        <v>1563</v>
       </c>
       <c r="Q137">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="138" spans="14:17" x14ac:dyDescent="0.45">
@@ -54807,10 +54445,10 @@
         <v>1638</v>
       </c>
       <c r="P138" t="s">
-        <v>1586</v>
+        <v>1553</v>
       </c>
       <c r="Q138">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="139" spans="14:17" x14ac:dyDescent="0.45">
@@ -54821,7 +54459,7 @@
         <v>1639</v>
       </c>
       <c r="P139" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="Q139">
         <v>0.85</v>
@@ -54835,7 +54473,7 @@
         <v>1640</v>
       </c>
       <c r="P140" t="s">
-        <v>1592</v>
+        <v>1552</v>
       </c>
       <c r="Q140">
         <v>0.85</v>
@@ -54849,7 +54487,7 @@
         <v>1641</v>
       </c>
       <c r="P141" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q141">
         <v>0.85</v>
@@ -54863,7 +54501,7 @@
         <v>1642</v>
       </c>
       <c r="P142" t="s">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="Q142">
         <v>0.85</v>
@@ -54877,7 +54515,7 @@
         <v>1643</v>
       </c>
       <c r="P143" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q143">
         <v>0.85</v>
@@ -54891,7 +54529,7 @@
         <v>1644</v>
       </c>
       <c r="P144" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="Q144">
         <v>0.85</v>
@@ -54905,7 +54543,7 @@
         <v>1645</v>
       </c>
       <c r="P145" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="Q145">
         <v>0.85</v>
@@ -54919,7 +54557,7 @@
         <v>1646</v>
       </c>
       <c r="P146" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="Q146">
         <v>0.85</v>
@@ -54933,10 +54571,10 @@
         <v>1647</v>
       </c>
       <c r="P147" t="s">
-        <v>1594</v>
+        <v>1568</v>
       </c>
       <c r="Q147">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="148" spans="14:17" x14ac:dyDescent="0.45">
@@ -54947,7 +54585,7 @@
         <v>1648</v>
       </c>
       <c r="P148" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="Q148">
         <v>0.85</v>
@@ -54961,10 +54599,10 @@
         <v>1649</v>
       </c>
       <c r="P149" t="s">
-        <v>1586</v>
+        <v>1554</v>
       </c>
       <c r="Q149">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="150" spans="14:17" x14ac:dyDescent="0.45">
@@ -54975,10 +54613,10 @@
         <v>1650</v>
       </c>
       <c r="P150" t="s">
-        <v>1580</v>
+        <v>1591</v>
       </c>
       <c r="Q150">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="151" spans="14:17" x14ac:dyDescent="0.45">
@@ -54989,7 +54627,7 @@
         <v>1651</v>
       </c>
       <c r="P151" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q151">
         <v>0.85</v>
@@ -55003,7 +54641,7 @@
         <v>1652</v>
       </c>
       <c r="P152" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q152">
         <v>0.85</v>
@@ -55017,7 +54655,7 @@
         <v>1653</v>
       </c>
       <c r="P153" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q153">
         <v>0.85</v>
@@ -55031,7 +54669,7 @@
         <v>1654</v>
       </c>
       <c r="P154" t="s">
-        <v>1583</v>
+        <v>1561</v>
       </c>
       <c r="Q154">
         <v>0.85</v>
@@ -55059,10 +54697,10 @@
         <v>1656</v>
       </c>
       <c r="P156" t="s">
-        <v>1552</v>
+        <v>1578</v>
       </c>
       <c r="Q156">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="157" spans="14:17" x14ac:dyDescent="0.45">
@@ -55073,10 +54711,10 @@
         <v>1657</v>
       </c>
       <c r="P157" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="Q157">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="158" spans="14:17" x14ac:dyDescent="0.45">
@@ -55087,7 +54725,7 @@
         <v>1658</v>
       </c>
       <c r="P158" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q158">
         <v>0.85</v>
@@ -55101,7 +54739,7 @@
         <v>1659</v>
       </c>
       <c r="P159" t="s">
-        <v>1561</v>
+        <v>1598</v>
       </c>
       <c r="Q159">
         <v>0.85</v>
@@ -55115,7 +54753,7 @@
         <v>1660</v>
       </c>
       <c r="P160" t="s">
-        <v>1584</v>
+        <v>1573</v>
       </c>
       <c r="Q160">
         <v>0.85</v>
@@ -55129,7 +54767,7 @@
         <v>1661</v>
       </c>
       <c r="P161" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q161">
         <v>0.85</v>
@@ -55143,10 +54781,10 @@
         <v>1662</v>
       </c>
       <c r="P162" t="s">
-        <v>1599</v>
+        <v>1564</v>
       </c>
       <c r="Q162">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="163" spans="14:17" x14ac:dyDescent="0.45">
@@ -55157,10 +54795,10 @@
         <v>1663</v>
       </c>
       <c r="P163" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q163">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="164" spans="14:17" x14ac:dyDescent="0.45">
@@ -55171,7 +54809,7 @@
         <v>1664</v>
       </c>
       <c r="P164" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q164">
         <v>0.85</v>
@@ -55185,7 +54823,7 @@
         <v>1665</v>
       </c>
       <c r="P165" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q165">
         <v>0.85</v>
@@ -55199,7 +54837,7 @@
         <v>1666</v>
       </c>
       <c r="P166" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="Q166">
         <v>0.85</v>
@@ -55213,7 +54851,7 @@
         <v>1667</v>
       </c>
       <c r="P167" t="s">
-        <v>1563</v>
+        <v>1592</v>
       </c>
       <c r="Q167">
         <v>0.85</v>
@@ -55227,7 +54865,7 @@
         <v>1668</v>
       </c>
       <c r="P168" t="s">
-        <v>1562</v>
+        <v>1586</v>
       </c>
       <c r="Q168">
         <v>0.85</v>
@@ -55241,10 +54879,10 @@
         <v>1669</v>
       </c>
       <c r="P169" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q169">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="170" spans="14:17" x14ac:dyDescent="0.45">
@@ -55255,7 +54893,7 @@
         <v>1670</v>
       </c>
       <c r="P170" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="Q170">
         <v>0.95</v>
@@ -55269,7 +54907,7 @@
         <v>1671</v>
       </c>
       <c r="P171" t="s">
-        <v>1591</v>
+        <v>1576</v>
       </c>
       <c r="Q171">
         <v>0.95</v>
@@ -55283,7 +54921,7 @@
         <v>1672</v>
       </c>
       <c r="P172" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q172">
         <v>0.85</v>
@@ -55297,7 +54935,7 @@
         <v>1673</v>
       </c>
       <c r="P173" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="Q173">
         <v>0.85</v>
@@ -55311,7 +54949,7 @@
         <v>1674</v>
       </c>
       <c r="P174" t="s">
-        <v>1573</v>
+        <v>1584</v>
       </c>
       <c r="Q174">
         <v>0.85</v>
@@ -55325,7 +54963,7 @@
         <v>1675</v>
       </c>
       <c r="P175" t="s">
-        <v>1573</v>
+        <v>1598</v>
       </c>
       <c r="Q175">
         <v>0.85</v>
@@ -55339,7 +54977,7 @@
         <v>1676</v>
       </c>
       <c r="P176" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q176">
         <v>0.85</v>
@@ -55353,7 +54991,7 @@
         <v>1677</v>
       </c>
       <c r="P177" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q177">
         <v>0.85</v>
@@ -55367,10 +55005,10 @@
         <v>1678</v>
       </c>
       <c r="P178" t="s">
-        <v>1556</v>
+        <v>1592</v>
       </c>
       <c r="Q178">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="179" spans="14:17" x14ac:dyDescent="0.45">
@@ -55381,10 +55019,10 @@
         <v>1679</v>
       </c>
       <c r="P179" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="Q179">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="180" spans="14:17" x14ac:dyDescent="0.45">
@@ -55395,10 +55033,10 @@
         <v>1680</v>
       </c>
       <c r="P180" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="Q180">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="181" spans="14:17" x14ac:dyDescent="0.45">
@@ -55409,10 +55047,10 @@
         <v>1681</v>
       </c>
       <c r="P181" t="s">
-        <v>1558</v>
+        <v>1598</v>
       </c>
       <c r="Q181">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="182" spans="14:17" x14ac:dyDescent="0.45">
@@ -55423,7 +55061,7 @@
         <v>1682</v>
       </c>
       <c r="P182" t="s">
-        <v>1596</v>
+        <v>1563</v>
       </c>
       <c r="Q182">
         <v>0.85</v>
@@ -55437,7 +55075,7 @@
         <v>1683</v>
       </c>
       <c r="P183" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="Q183">
         <v>0.85</v>
@@ -55451,7 +55089,7 @@
         <v>1684</v>
       </c>
       <c r="P184" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="Q184">
         <v>0.85</v>
@@ -55465,7 +55103,7 @@
         <v>1685</v>
       </c>
       <c r="P185" t="s">
-        <v>1589</v>
+        <v>1568</v>
       </c>
       <c r="Q185">
         <v>0.85</v>
@@ -55479,7 +55117,7 @@
         <v>1686</v>
       </c>
       <c r="P186" t="s">
-        <v>1562</v>
+        <v>1583</v>
       </c>
       <c r="Q186">
         <v>0.85</v>
@@ -55493,10 +55131,10 @@
         <v>1687</v>
       </c>
       <c r="P187" t="s">
-        <v>1592</v>
+        <v>1579</v>
       </c>
       <c r="Q187">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="188" spans="14:17" x14ac:dyDescent="0.45">
@@ -55507,10 +55145,10 @@
         <v>1688</v>
       </c>
       <c r="P188" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q188">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="189" spans="14:17" x14ac:dyDescent="0.45">
@@ -55521,10 +55159,10 @@
         <v>1689</v>
       </c>
       <c r="P189" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q189">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="190" spans="14:17" x14ac:dyDescent="0.45">
@@ -55535,10 +55173,10 @@
         <v>1690</v>
       </c>
       <c r="P190" t="s">
-        <v>1598</v>
+        <v>1552</v>
       </c>
       <c r="Q190">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="191" spans="14:17" x14ac:dyDescent="0.45">
@@ -55563,7 +55201,7 @@
         <v>1692</v>
       </c>
       <c r="P192" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q192">
         <v>0.85</v>
@@ -55577,7 +55215,7 @@
         <v>1693</v>
       </c>
       <c r="P193" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="Q193">
         <v>0.85</v>
@@ -55591,10 +55229,10 @@
         <v>1694</v>
       </c>
       <c r="P194" t="s">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="Q194">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="195" spans="14:17" x14ac:dyDescent="0.45">
@@ -55605,10 +55243,10 @@
         <v>1695</v>
       </c>
       <c r="P195" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q195">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="196" spans="14:17" x14ac:dyDescent="0.45">
@@ -55619,10 +55257,10 @@
         <v>1696</v>
       </c>
       <c r="P196" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="Q196">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="197" spans="14:17" x14ac:dyDescent="0.45">
@@ -55633,10 +55271,10 @@
         <v>1697</v>
       </c>
       <c r="P197" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q197">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="198" spans="14:17" x14ac:dyDescent="0.45">
@@ -55647,10 +55285,10 @@
         <v>1698</v>
       </c>
       <c r="P198" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="Q198">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="199" spans="14:17" x14ac:dyDescent="0.45">
@@ -55661,10 +55299,10 @@
         <v>1699</v>
       </c>
       <c r="P199" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="Q199">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="200" spans="14:17" x14ac:dyDescent="0.45">
@@ -55675,10 +55313,10 @@
         <v>1700</v>
       </c>
       <c r="P200" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="Q200">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="201" spans="14:17" x14ac:dyDescent="0.45">
@@ -55689,10 +55327,10 @@
         <v>1701</v>
       </c>
       <c r="P201" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q201">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="202" spans="14:17" x14ac:dyDescent="0.45">
@@ -55703,7 +55341,7 @@
         <v>1702</v>
       </c>
       <c r="P202" t="s">
-        <v>1552</v>
+        <v>1599</v>
       </c>
       <c r="Q202">
         <v>0.85</v>
@@ -55717,7 +55355,7 @@
         <v>1703</v>
       </c>
       <c r="P203" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="Q203">
         <v>0.85</v>
@@ -55731,7 +55369,7 @@
         <v>1704</v>
       </c>
       <c r="P204" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="Q204">
         <v>0.85</v>
@@ -55745,7 +55383,7 @@
         <v>1705</v>
       </c>
       <c r="P205" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="Q205">
         <v>0.85</v>
@@ -55759,7 +55397,7 @@
         <v>1706</v>
       </c>
       <c r="P206" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q206">
         <v>0.85</v>
@@ -55776,7 +55414,7 @@
         <v>1591</v>
       </c>
       <c r="Q207">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="208" spans="14:17" x14ac:dyDescent="0.45">
@@ -55787,10 +55425,10 @@
         <v>1708</v>
       </c>
       <c r="P208" t="s">
-        <v>1554</v>
+        <v>1573</v>
       </c>
       <c r="Q208">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="209" spans="14:17" x14ac:dyDescent="0.45">
@@ -55801,7 +55439,7 @@
         <v>1709</v>
       </c>
       <c r="P209" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="Q209">
         <v>0.85</v>
@@ -55815,7 +55453,7 @@
         <v>1710</v>
       </c>
       <c r="P210" t="s">
-        <v>1561</v>
+        <v>1583</v>
       </c>
       <c r="Q210">
         <v>0.85</v>
@@ -55829,10 +55467,10 @@
         <v>1711</v>
       </c>
       <c r="P211" t="s">
-        <v>1561</v>
+        <v>1596</v>
       </c>
       <c r="Q211">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="212" spans="14:17" x14ac:dyDescent="0.45">
@@ -55843,10 +55481,10 @@
         <v>1712</v>
       </c>
       <c r="P212" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="Q212">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="213" spans="14:17" x14ac:dyDescent="0.45">
@@ -55857,10 +55495,10 @@
         <v>1713</v>
       </c>
       <c r="P213" t="s">
-        <v>1568</v>
+        <v>1556</v>
       </c>
       <c r="Q213">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="214" spans="14:17" x14ac:dyDescent="0.45">
@@ -55871,10 +55509,10 @@
         <v>1714</v>
       </c>
       <c r="P214" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="Q214">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -55885,7 +55523,7 @@
         <v>1715</v>
       </c>
       <c r="P215" t="s">
-        <v>1578</v>
+        <v>1596</v>
       </c>
       <c r="Q215">
         <v>0.85</v>
@@ -55899,7 +55537,7 @@
         <v>1716</v>
       </c>
       <c r="P216" t="s">
-        <v>1598</v>
+        <v>1562</v>
       </c>
       <c r="Q216">
         <v>0.85</v>
@@ -55913,7 +55551,7 @@
         <v>1717</v>
       </c>
       <c r="P217" t="s">
-        <v>1573</v>
+        <v>1592</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -55927,7 +55565,7 @@
         <v>1718</v>
       </c>
       <c r="P218" t="s">
-        <v>1573</v>
+        <v>1589</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -55941,7 +55579,7 @@
         <v>1719</v>
       </c>
       <c r="P219" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -55955,10 +55593,10 @@
         <v>1720</v>
       </c>
       <c r="P220" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q220">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -55969,10 +55607,10 @@
         <v>1721</v>
       </c>
       <c r="P221" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
       <c r="Q221">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -55983,10 +55621,10 @@
         <v>1722</v>
       </c>
       <c r="P222" t="s">
-        <v>1599</v>
+        <v>1562</v>
       </c>
       <c r="Q222">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="223" spans="14:17" x14ac:dyDescent="0.45">
@@ -56000,7 +55638,7 @@
         <v>1598</v>
       </c>
       <c r="Q223">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="224" spans="14:17" x14ac:dyDescent="0.45">
@@ -56011,7 +55649,7 @@
         <v>1724</v>
       </c>
       <c r="P224" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -56025,7 +55663,7 @@
         <v>1725</v>
       </c>
       <c r="P225" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -56039,7 +55677,7 @@
         <v>1726</v>
       </c>
       <c r="P226" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -56053,7 +55691,7 @@
         <v>1727</v>
       </c>
       <c r="P227" t="s">
-        <v>1554</v>
+        <v>1599</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -56067,7 +55705,7 @@
         <v>1728</v>
       </c>
       <c r="P228" t="s">
-        <v>1563</v>
+        <v>1599</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -56081,7 +55719,7 @@
         <v>1729</v>
       </c>
       <c r="P229" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -56095,7 +55733,7 @@
         <v>1730</v>
       </c>
       <c r="P230" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -56109,7 +55747,7 @@
         <v>1731</v>
       </c>
       <c r="P231" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -56123,7 +55761,7 @@
         <v>1732</v>
       </c>
       <c r="P232" t="s">
-        <v>1598</v>
+        <v>1568</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -56137,10 +55775,10 @@
         <v>1733</v>
       </c>
       <c r="P233" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="Q233">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -56151,10 +55789,10 @@
         <v>1734</v>
       </c>
       <c r="P234" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q234">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -56165,7 +55803,7 @@
         <v>1735</v>
       </c>
       <c r="P235" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -56179,7 +55817,7 @@
         <v>1736</v>
       </c>
       <c r="P236" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -56193,10 +55831,10 @@
         <v>1737</v>
       </c>
       <c r="P237" t="s">
-        <v>1564</v>
+        <v>1596</v>
       </c>
       <c r="Q237">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="238" spans="14:17" x14ac:dyDescent="0.45">
@@ -56207,10 +55845,10 @@
         <v>1738</v>
       </c>
       <c r="P238" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="Q238">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -56235,7 +55873,7 @@
         <v>1740</v>
       </c>
       <c r="P240" t="s">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -56249,7 +55887,7 @@
         <v>1741</v>
       </c>
       <c r="P241" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -56263,7 +55901,7 @@
         <v>1742</v>
       </c>
       <c r="P242" t="s">
-        <v>1592</v>
+        <v>1562</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -56277,7 +55915,7 @@
         <v>1743</v>
       </c>
       <c r="P243" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -56291,7 +55929,7 @@
         <v>1744</v>
       </c>
       <c r="P244" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -56305,10 +55943,10 @@
         <v>1745</v>
       </c>
       <c r="P245" t="s">
-        <v>1554</v>
+        <v>1589</v>
       </c>
       <c r="Q245">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -56319,7 +55957,7 @@
         <v>1746</v>
       </c>
       <c r="P246" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="Q246">
         <v>0.95</v>
@@ -56333,10 +55971,10 @@
         <v>1747</v>
       </c>
       <c r="P247" t="s">
-        <v>1584</v>
+        <v>1573</v>
       </c>
       <c r="Q247">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -56347,10 +55985,10 @@
         <v>1748</v>
       </c>
       <c r="P248" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="Q248">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="249" spans="14:17" x14ac:dyDescent="0.45">
@@ -56361,7 +55999,7 @@
         <v>1749</v>
       </c>
       <c r="P249" t="s">
-        <v>1596</v>
+        <v>1561</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -56375,7 +56013,7 @@
         <v>1750</v>
       </c>
       <c r="P250" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -56389,7 +56027,7 @@
         <v>1751</v>
       </c>
       <c r="P251" t="s">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -56403,7 +56041,7 @@
         <v>1752</v>
       </c>
       <c r="P252" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -56417,7 +56055,7 @@
         <v>1753</v>
       </c>
       <c r="P253" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -56431,7 +56069,7 @@
         <v>1754</v>
       </c>
       <c r="P254" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -56445,10 +56083,10 @@
         <v>1755</v>
       </c>
       <c r="P255" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="Q255">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="256" spans="14:17" x14ac:dyDescent="0.45">
@@ -56459,7 +56097,7 @@
         <v>1756</v>
       </c>
       <c r="P256" t="s">
-        <v>1558</v>
+        <v>1598</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -56473,7 +56111,7 @@
         <v>1757</v>
       </c>
       <c r="P257" t="s">
-        <v>1587</v>
+        <v>1558</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -56487,10 +56125,10 @@
         <v>1758</v>
       </c>
       <c r="P258" t="s">
-        <v>1562</v>
+        <v>1586</v>
       </c>
       <c r="Q258">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="259" spans="14:17" x14ac:dyDescent="0.45">
@@ -56501,10 +56139,10 @@
         <v>1759</v>
       </c>
       <c r="P259" t="s">
-        <v>1573</v>
+        <v>1596</v>
       </c>
       <c r="Q259">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="260" spans="14:17" x14ac:dyDescent="0.45">
@@ -56515,10 +56153,10 @@
         <v>1760</v>
       </c>
       <c r="P260" t="s">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="Q260">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="261" spans="14:17" x14ac:dyDescent="0.45">
@@ -56529,7 +56167,7 @@
         <v>1761</v>
       </c>
       <c r="P261" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -56557,7 +56195,7 @@
         <v>1763</v>
       </c>
       <c r="P263" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -56571,7 +56209,7 @@
         <v>1764</v>
       </c>
       <c r="P264" t="s">
-        <v>1563</v>
+        <v>1583</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -56599,7 +56237,7 @@
         <v>1766</v>
       </c>
       <c r="P266" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="Q266">
         <v>0.95</v>
@@ -56613,7 +56251,7 @@
         <v>1767</v>
       </c>
       <c r="P267" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="Q267">
         <v>0.95</v>
@@ -56627,7 +56265,7 @@
         <v>1768</v>
       </c>
       <c r="P268" t="s">
-        <v>1589</v>
+        <v>1562</v>
       </c>
       <c r="Q268">
         <v>0.95</v>
@@ -56641,10 +56279,10 @@
         <v>1769</v>
       </c>
       <c r="P269" t="s">
-        <v>1572</v>
+        <v>1596</v>
       </c>
       <c r="Q269">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="270" spans="14:17" x14ac:dyDescent="0.45">
@@ -56655,10 +56293,10 @@
         <v>1770</v>
       </c>
       <c r="P270" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="Q270">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="271" spans="14:17" x14ac:dyDescent="0.45">
@@ -56669,10 +56307,10 @@
         <v>1771</v>
       </c>
       <c r="P271" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="Q271">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -56683,7 +56321,7 @@
         <v>1772</v>
       </c>
       <c r="P272" t="s">
-        <v>1583</v>
+        <v>1563</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -56697,7 +56335,7 @@
         <v>1773</v>
       </c>
       <c r="P273" t="s">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -56711,10 +56349,10 @@
         <v>1774</v>
       </c>
       <c r="P274" t="s">
-        <v>1599</v>
+        <v>1552</v>
       </c>
       <c r="Q274">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="275" spans="14:17" x14ac:dyDescent="0.45">
@@ -56725,7 +56363,7 @@
         <v>1775</v>
       </c>
       <c r="P275" t="s">
-        <v>1561</v>
+        <v>1596</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -56739,7 +56377,7 @@
         <v>1776</v>
       </c>
       <c r="P276" t="s">
-        <v>1565</v>
+        <v>1591</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -56753,7 +56391,7 @@
         <v>1777</v>
       </c>
       <c r="P277" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -56767,7 +56405,7 @@
         <v>1778</v>
       </c>
       <c r="P278" t="s">
-        <v>1561</v>
+        <v>1586</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -56781,7 +56419,7 @@
         <v>1779</v>
       </c>
       <c r="P279" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -56795,7 +56433,7 @@
         <v>1780</v>
       </c>
       <c r="P280" t="s">
-        <v>1573</v>
+        <v>1580</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -56809,7 +56447,7 @@
         <v>1781</v>
       </c>
       <c r="P281" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -56823,7 +56461,7 @@
         <v>1782</v>
       </c>
       <c r="P282" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -56835,8 +56473,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5684605C-F73E-4AD7-A38B-CA6F3FEA5964}">
-  <dimension ref="A1:I110"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97194A4B-A255-4A68-9D8A-8655EBAD698F}">
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -58152,1488 +57790,6 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>2</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1886</v>
-      </c>
-      <c r="H54" t="s">
-        <v>1887</v>
-      </c>
-      <c r="I54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1888</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1889</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>2</v>
-      </c>
-      <c r="G55" t="s">
-        <v>1888</v>
-      </c>
-      <c r="H55" t="s">
-        <v>1889</v>
-      </c>
-      <c r="I55">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1890</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1891</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56">
-        <v>2</v>
-      </c>
-      <c r="G56" t="s">
-        <v>1890</v>
-      </c>
-      <c r="H56" t="s">
-        <v>1891</v>
-      </c>
-      <c r="I56">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1893</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57">
-        <v>2</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1892</v>
-      </c>
-      <c r="H57" t="s">
-        <v>1893</v>
-      </c>
-      <c r="I57">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1894</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1895</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58">
-        <v>2</v>
-      </c>
-      <c r="G58" t="s">
-        <v>1894</v>
-      </c>
-      <c r="H58" t="s">
-        <v>1895</v>
-      </c>
-      <c r="I58">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1896</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1897</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>2</v>
-      </c>
-      <c r="G59" t="s">
-        <v>1896</v>
-      </c>
-      <c r="H59" t="s">
-        <v>1897</v>
-      </c>
-      <c r="I59">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1898</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1899</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>2</v>
-      </c>
-      <c r="G60" t="s">
-        <v>1898</v>
-      </c>
-      <c r="H60" t="s">
-        <v>1899</v>
-      </c>
-      <c r="I60">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1900</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1901</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61">
-        <v>2</v>
-      </c>
-      <c r="G61" t="s">
-        <v>1900</v>
-      </c>
-      <c r="H61" t="s">
-        <v>1901</v>
-      </c>
-      <c r="I61">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62">
-        <v>2</v>
-      </c>
-      <c r="G62" t="s">
-        <v>1902</v>
-      </c>
-      <c r="H62" t="s">
-        <v>1903</v>
-      </c>
-      <c r="I62">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1904</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="G63" t="s">
-        <v>1904</v>
-      </c>
-      <c r="H63" t="s">
-        <v>1905</v>
-      </c>
-      <c r="I63">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1906</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1907</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="G64" t="s">
-        <v>1906</v>
-      </c>
-      <c r="H64" t="s">
-        <v>1907</v>
-      </c>
-      <c r="I64">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1908</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1909</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
-        <v>2</v>
-      </c>
-      <c r="G65" t="s">
-        <v>1908</v>
-      </c>
-      <c r="H65" t="s">
-        <v>1909</v>
-      </c>
-      <c r="I65">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1910</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1911</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
-      <c r="G66" t="s">
-        <v>1910</v>
-      </c>
-      <c r="H66" t="s">
-        <v>1911</v>
-      </c>
-      <c r="I66">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1912</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1913</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>2</v>
-      </c>
-      <c r="G67" t="s">
-        <v>1912</v>
-      </c>
-      <c r="H67" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I67">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1914</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1915</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>2</v>
-      </c>
-      <c r="G68" t="s">
-        <v>1914</v>
-      </c>
-      <c r="H68" t="s">
-        <v>1915</v>
-      </c>
-      <c r="I68">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1916</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
-      <c r="G69" t="s">
-        <v>1916</v>
-      </c>
-      <c r="H69" t="s">
-        <v>1917</v>
-      </c>
-      <c r="I69">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1918</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>2</v>
-      </c>
-      <c r="G70" t="s">
-        <v>1918</v>
-      </c>
-      <c r="H70" t="s">
-        <v>1919</v>
-      </c>
-      <c r="I70">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1920</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>2</v>
-      </c>
-      <c r="G71" t="s">
-        <v>1920</v>
-      </c>
-      <c r="H71" t="s">
-        <v>1921</v>
-      </c>
-      <c r="I71">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1922</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>2</v>
-      </c>
-      <c r="G72" t="s">
-        <v>1922</v>
-      </c>
-      <c r="H72" t="s">
-        <v>1923</v>
-      </c>
-      <c r="I72">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1924</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73">
-        <v>2</v>
-      </c>
-      <c r="G73" t="s">
-        <v>1924</v>
-      </c>
-      <c r="H73" t="s">
-        <v>1925</v>
-      </c>
-      <c r="I73">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1926</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1927</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>2</v>
-      </c>
-      <c r="G74" t="s">
-        <v>1926</v>
-      </c>
-      <c r="H74" t="s">
-        <v>1927</v>
-      </c>
-      <c r="I74">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1928</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>2</v>
-      </c>
-      <c r="G75" t="s">
-        <v>1928</v>
-      </c>
-      <c r="H75" t="s">
-        <v>1929</v>
-      </c>
-      <c r="I75">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1930</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>2</v>
-      </c>
-      <c r="G76" t="s">
-        <v>1930</v>
-      </c>
-      <c r="H76" t="s">
-        <v>1931</v>
-      </c>
-      <c r="I76">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>2</v>
-      </c>
-      <c r="G77" t="s">
-        <v>1932</v>
-      </c>
-      <c r="H77" t="s">
-        <v>1933</v>
-      </c>
-      <c r="I77">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1934</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1935</v>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78">
-        <v>2</v>
-      </c>
-      <c r="G78" t="s">
-        <v>1934</v>
-      </c>
-      <c r="H78" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I78">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A79" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1937</v>
-      </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
-      <c r="G79" t="s">
-        <v>1936</v>
-      </c>
-      <c r="H79" t="s">
-        <v>1937</v>
-      </c>
-      <c r="I79">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1938</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1939</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
-      <c r="G80" t="s">
-        <v>1938</v>
-      </c>
-      <c r="H80" t="s">
-        <v>1939</v>
-      </c>
-      <c r="I80">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1940</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1941</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81">
-        <v>2</v>
-      </c>
-      <c r="G81" t="s">
-        <v>1940</v>
-      </c>
-      <c r="H81" t="s">
-        <v>1941</v>
-      </c>
-      <c r="I81">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
-      <c r="G82" t="s">
-        <v>1942</v>
-      </c>
-      <c r="H82" t="s">
-        <v>1943</v>
-      </c>
-      <c r="I82">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83">
-        <v>2</v>
-      </c>
-      <c r="G83" t="s">
-        <v>1944</v>
-      </c>
-      <c r="H83" t="s">
-        <v>1945</v>
-      </c>
-      <c r="I83">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1946</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1947</v>
-      </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84">
-        <v>2</v>
-      </c>
-      <c r="G84" t="s">
-        <v>1946</v>
-      </c>
-      <c r="H84" t="s">
-        <v>1947</v>
-      </c>
-      <c r="I84">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1948</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-      <c r="E85">
-        <v>2</v>
-      </c>
-      <c r="G85" t="s">
-        <v>1948</v>
-      </c>
-      <c r="H85" t="s">
-        <v>1949</v>
-      </c>
-      <c r="I85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D86">
-        <v>1</v>
-      </c>
-      <c r="E86">
-        <v>2</v>
-      </c>
-      <c r="G86" t="s">
-        <v>1950</v>
-      </c>
-      <c r="H86" t="s">
-        <v>1951</v>
-      </c>
-      <c r="I86">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1952</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1953</v>
-      </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-      <c r="E87">
-        <v>2</v>
-      </c>
-      <c r="G87" t="s">
-        <v>1952</v>
-      </c>
-      <c r="H87" t="s">
-        <v>1953</v>
-      </c>
-      <c r="I87">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1954</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1955</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88">
-        <v>2</v>
-      </c>
-      <c r="G88" t="s">
-        <v>1954</v>
-      </c>
-      <c r="H88" t="s">
-        <v>1955</v>
-      </c>
-      <c r="I88">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D89">
-        <v>1</v>
-      </c>
-      <c r="E89">
-        <v>2</v>
-      </c>
-      <c r="G89" t="s">
-        <v>1956</v>
-      </c>
-      <c r="H89" t="s">
-        <v>1957</v>
-      </c>
-      <c r="I89">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1958</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>2</v>
-      </c>
-      <c r="G90" t="s">
-        <v>1958</v>
-      </c>
-      <c r="H90" t="s">
-        <v>1959</v>
-      </c>
-      <c r="I90">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1960</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91">
-        <v>2</v>
-      </c>
-      <c r="G91" t="s">
-        <v>1960</v>
-      </c>
-      <c r="H91" t="s">
-        <v>1961</v>
-      </c>
-      <c r="I91">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1962</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1963</v>
-      </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92">
-        <v>2</v>
-      </c>
-      <c r="G92" t="s">
-        <v>1962</v>
-      </c>
-      <c r="H92" t="s">
-        <v>1963</v>
-      </c>
-      <c r="I92">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1964</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
-      </c>
-      <c r="E93">
-        <v>2</v>
-      </c>
-      <c r="G93" t="s">
-        <v>1964</v>
-      </c>
-      <c r="H93" t="s">
-        <v>1965</v>
-      </c>
-      <c r="I93">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1966</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1967</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94">
-        <v>2</v>
-      </c>
-      <c r="G94" t="s">
-        <v>1966</v>
-      </c>
-      <c r="H94" t="s">
-        <v>1967</v>
-      </c>
-      <c r="I94">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1968</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1969</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95">
-        <v>2</v>
-      </c>
-      <c r="G95" t="s">
-        <v>1968</v>
-      </c>
-      <c r="H95" t="s">
-        <v>1969</v>
-      </c>
-      <c r="I95">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1970</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>2</v>
-      </c>
-      <c r="G96" t="s">
-        <v>1970</v>
-      </c>
-      <c r="H96" t="s">
-        <v>1971</v>
-      </c>
-      <c r="I96">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1972</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97">
-        <v>2</v>
-      </c>
-      <c r="G97" t="s">
-        <v>1972</v>
-      </c>
-      <c r="H97" t="s">
-        <v>1973</v>
-      </c>
-      <c r="I97">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1974</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1975</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="E98">
-        <v>2</v>
-      </c>
-      <c r="G98" t="s">
-        <v>1974</v>
-      </c>
-      <c r="H98" t="s">
-        <v>1975</v>
-      </c>
-      <c r="I98">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A99" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1976</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1977</v>
-      </c>
-      <c r="D99">
-        <v>1</v>
-      </c>
-      <c r="E99">
-        <v>2</v>
-      </c>
-      <c r="G99" t="s">
-        <v>1976</v>
-      </c>
-      <c r="H99" t="s">
-        <v>1977</v>
-      </c>
-      <c r="I99">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1978</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1979</v>
-      </c>
-      <c r="D100">
-        <v>1</v>
-      </c>
-      <c r="E100">
-        <v>2</v>
-      </c>
-      <c r="G100" t="s">
-        <v>1978</v>
-      </c>
-      <c r="H100" t="s">
-        <v>1979</v>
-      </c>
-      <c r="I100">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1980</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1981</v>
-      </c>
-      <c r="D101">
-        <v>1</v>
-      </c>
-      <c r="E101">
-        <v>2</v>
-      </c>
-      <c r="G101" t="s">
-        <v>1980</v>
-      </c>
-      <c r="H101" t="s">
-        <v>1981</v>
-      </c>
-      <c r="I101">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A102" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B102" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1983</v>
-      </c>
-      <c r="D102">
-        <v>1</v>
-      </c>
-      <c r="E102">
-        <v>2</v>
-      </c>
-      <c r="G102" t="s">
-        <v>1982</v>
-      </c>
-      <c r="H102" t="s">
-        <v>1983</v>
-      </c>
-      <c r="I102">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A103" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B103" t="s">
-        <v>1984</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103">
-        <v>2</v>
-      </c>
-      <c r="G103" t="s">
-        <v>1984</v>
-      </c>
-      <c r="H103" t="s">
-        <v>1985</v>
-      </c>
-      <c r="I103">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A104" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B104" t="s">
-        <v>1986</v>
-      </c>
-      <c r="C104" t="s">
-        <v>1987</v>
-      </c>
-      <c r="D104">
-        <v>1</v>
-      </c>
-      <c r="E104">
-        <v>2</v>
-      </c>
-      <c r="G104" t="s">
-        <v>1986</v>
-      </c>
-      <c r="H104" t="s">
-        <v>1987</v>
-      </c>
-      <c r="I104">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A105" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B105" t="s">
-        <v>1988</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D105">
-        <v>1</v>
-      </c>
-      <c r="E105">
-        <v>2</v>
-      </c>
-      <c r="G105" t="s">
-        <v>1988</v>
-      </c>
-      <c r="H105" t="s">
-        <v>1989</v>
-      </c>
-      <c r="I105">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A106" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1990</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
-      <c r="G106" t="s">
-        <v>1990</v>
-      </c>
-      <c r="H106" t="s">
-        <v>1991</v>
-      </c>
-      <c r="I106">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A107" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B107" t="s">
-        <v>1992</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1993</v>
-      </c>
-      <c r="D107">
-        <v>1</v>
-      </c>
-      <c r="E107">
-        <v>2</v>
-      </c>
-      <c r="G107" t="s">
-        <v>1992</v>
-      </c>
-      <c r="H107" t="s">
-        <v>1993</v>
-      </c>
-      <c r="I107">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A108" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1994</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1995</v>
-      </c>
-      <c r="D108">
-        <v>1</v>
-      </c>
-      <c r="E108">
-        <v>2</v>
-      </c>
-      <c r="G108" t="s">
-        <v>1994</v>
-      </c>
-      <c r="H108" t="s">
-        <v>1995</v>
-      </c>
-      <c r="I108">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A109" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1996</v>
-      </c>
-      <c r="C109" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D109">
-        <v>1</v>
-      </c>
-      <c r="E109">
-        <v>2</v>
-      </c>
-      <c r="G109" t="s">
-        <v>1996</v>
-      </c>
-      <c r="H109" t="s">
-        <v>1997</v>
-      </c>
-      <c r="I109">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A110" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1998</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1999</v>
-      </c>
-      <c r="D110">
-        <v>1</v>
-      </c>
-      <c r="E110">
-        <v>2</v>
-      </c>
-      <c r="G110" t="s">
-        <v>1998</v>
-      </c>
-      <c r="H110" t="s">
-        <v>1999</v>
-      </c>
-      <c r="I110">
-        <v>-1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0E7331-7BFB-4BCD-A178-FF5F1DF77B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDACEA55-0CFF-4A5D-B8F4-E1876E23B376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12013" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11845" uniqueCount="1848">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -4885,555 +4885,117 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
-    <t>ep_gas_steam_turbine_G100000410412-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000109353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105921_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108688-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108686-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102970-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000014-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107697-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106378-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110373-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105923_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105926_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106199_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102968-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102969-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108066-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107698_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000400579-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001027891-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_G100000105933-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108078-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109474-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100841-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106380-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106379-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110975-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104995-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104996-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111769-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102396_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_Bialystok_POL-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101143-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108077-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104998-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105620-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108068-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111517-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106381-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400574-CHP_ccs-rf</t>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110375-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108067-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100847-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108685-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105935-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400583-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000013-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104997-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101558-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100691-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113459-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400576-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000015-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103104-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109472-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107865_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109356-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104994-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108123-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105934-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107700-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108065-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400810-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400813-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106377-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113458-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108225-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111549-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102398_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000018-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406287-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001020486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400575-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110374-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000112582-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107864_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110376-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102397_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400580-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_gas_turbine_G100000410411-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090297-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090159-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110973-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102971-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101557-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108124-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101144-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105000-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001090160-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108226-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108227-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000113571-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102966-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111770-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109357-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400573-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400577-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109349-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000103057-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108062-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109780-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100001053981-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102967-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100846-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105925_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108125-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000019-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400578-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104999-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106198_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000108687-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101142-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109473-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109779-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111548-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110974-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000106202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000104993-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109778-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_steam_turbine_G100001000017-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100000406284-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109348-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110413-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105924_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107699_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_internal_combustion_G100001000012-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109350-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000102395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105922_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000101868-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>~UC_Sets: R_S: Allregions</t>
   </si>
   <si>
@@ -5569,6 +5131,174 @@
     <t>elc_spv_POL_020</t>
   </si>
   <si>
+    <t>UCE_elcagg_spv_POL_021</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_022</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_023</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_024</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_025</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_026</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_027</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_028</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_029</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_030</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_031</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_032</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_033</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_034</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_035</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_036</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_037</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_038</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_039</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_040</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_041</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_042</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_043</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_044</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_045</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_046</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_047</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_spv_POL_048</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_048</t>
+  </si>
+  <si>
     <t>UCE_elcagg_wof_POL_001</t>
   </si>
   <si>
@@ -5741,6 +5471,162 @@
   </si>
   <si>
     <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
   </si>
 </sst>
 </file>
@@ -6358,7 +6244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6CC482-8921-475E-B023-BAAD326AA9C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15218B0-1716-4091-B5E2-97909F624C85}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37545,7 +37431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B860D5-4C1C-4E89-898E-09CEFFC7FDCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0FE72D-2ED1-4B36-8CF8-0D15BF6F566A}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51806,8 +51692,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B712E537-29F2-4C33-B682-EC6583100085}">
-  <dimension ref="B2:Q282"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F910C9-C19A-4108-AFD5-27C6ED14673E}">
+  <dimension ref="B2:Q136"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.45">
@@ -53913,7 +53799,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1554</v>
+        <v>1581</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53927,10 +53813,10 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1581</v>
+        <v>1568</v>
       </c>
       <c r="Q101">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="102" spans="14:17" x14ac:dyDescent="0.45">
@@ -53941,10 +53827,10 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="Q102">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="103" spans="14:17" x14ac:dyDescent="0.45">
@@ -53955,7 +53841,7 @@
         <v>1603</v>
       </c>
       <c r="P103" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q103">
         <v>0.85</v>
@@ -53969,7 +53855,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -53983,7 +53869,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -53997,10 +53883,10 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1578</v>
+        <v>1563</v>
       </c>
       <c r="Q106">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="107" spans="14:17" x14ac:dyDescent="0.45">
@@ -54011,10 +53897,10 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1562</v>
+        <v>1584</v>
       </c>
       <c r="Q107">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="108" spans="14:17" x14ac:dyDescent="0.45">
@@ -54025,7 +53911,7 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="Q108">
         <v>0.85</v>
@@ -54039,7 +53925,7 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="Q109">
         <v>0.95</v>
@@ -54053,7 +53939,7 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1563</v>
+        <v>1583</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -54081,7 +53967,7 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1561</v>
+        <v>1599</v>
       </c>
       <c r="Q112">
         <v>0.85</v>
@@ -54095,7 +53981,7 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="Q113">
         <v>0.85</v>
@@ -54109,7 +53995,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54123,7 +54009,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54137,7 +54023,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54151,7 +54037,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54165,10 +54051,10 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1562</v>
+        <v>1594</v>
       </c>
       <c r="Q118">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="119" spans="14:17" x14ac:dyDescent="0.45">
@@ -54179,7 +54065,7 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="Q119">
         <v>0.85</v>
@@ -54193,10 +54079,10 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="Q120">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="121" spans="14:17" x14ac:dyDescent="0.45">
@@ -54207,10 +54093,10 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="Q121">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="122" spans="14:17" x14ac:dyDescent="0.45">
@@ -54221,10 +54107,10 @@
         <v>1622</v>
       </c>
       <c r="P122" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="Q122">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="123" spans="14:17" x14ac:dyDescent="0.45">
@@ -54235,10 +54121,10 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1579</v>
+        <v>1568</v>
       </c>
       <c r="Q123">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="124" spans="14:17" x14ac:dyDescent="0.45">
@@ -54249,10 +54135,10 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1598</v>
+        <v>1562</v>
       </c>
       <c r="Q124">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="125" spans="14:17" x14ac:dyDescent="0.45">
@@ -54263,7 +54149,7 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="Q125">
         <v>0.85</v>
@@ -54277,7 +54163,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54291,7 +54177,7 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1553</v>
+        <v>1592</v>
       </c>
       <c r="Q127">
         <v>0.85</v>
@@ -54305,7 +54191,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54319,7 +54205,7 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q129">
         <v>0.85</v>
@@ -54333,10 +54219,10 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1596</v>
+        <v>1573</v>
       </c>
       <c r="Q130">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="131" spans="14:17" x14ac:dyDescent="0.45">
@@ -54347,10 +54233,10 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="Q131">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -54361,7 +54247,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54375,7 +54261,7 @@
         <v>1633</v>
       </c>
       <c r="P133" t="s">
-        <v>1592</v>
+        <v>1583</v>
       </c>
       <c r="Q133">
         <v>0.85</v>
@@ -54389,7 +54275,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54417,2054 +54303,10 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
       <c r="Q136">
         <v>0.95</v>
-      </c>
-    </row>
-    <row r="137" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N137" t="s">
-        <v>27</v>
-      </c>
-      <c r="O137" t="s">
-        <v>1637</v>
-      </c>
-      <c r="P137" t="s">
-        <v>1563</v>
-      </c>
-      <c r="Q137">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="138" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N138" t="s">
-        <v>27</v>
-      </c>
-      <c r="O138" t="s">
-        <v>1638</v>
-      </c>
-      <c r="P138" t="s">
-        <v>1553</v>
-      </c>
-      <c r="Q138">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="139" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N139" t="s">
-        <v>27</v>
-      </c>
-      <c r="O139" t="s">
-        <v>1639</v>
-      </c>
-      <c r="P139" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q139">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="140" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N140" t="s">
-        <v>27</v>
-      </c>
-      <c r="O140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="P140" t="s">
-        <v>1552</v>
-      </c>
-      <c r="Q140">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="141" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N141" t="s">
-        <v>27</v>
-      </c>
-      <c r="O141" t="s">
-        <v>1641</v>
-      </c>
-      <c r="P141" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="142" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N142" t="s">
-        <v>27</v>
-      </c>
-      <c r="O142" t="s">
-        <v>1642</v>
-      </c>
-      <c r="P142" t="s">
-        <v>1565</v>
-      </c>
-      <c r="Q142">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="143" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N143" t="s">
-        <v>27</v>
-      </c>
-      <c r="O143" t="s">
-        <v>1643</v>
-      </c>
-      <c r="P143" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q143">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="144" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N144" t="s">
-        <v>27</v>
-      </c>
-      <c r="O144" t="s">
-        <v>1644</v>
-      </c>
-      <c r="P144" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q144">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="145" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N145" t="s">
-        <v>27</v>
-      </c>
-      <c r="O145" t="s">
-        <v>1645</v>
-      </c>
-      <c r="P145" t="s">
-        <v>1578</v>
-      </c>
-      <c r="Q145">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="146" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N146" t="s">
-        <v>27</v>
-      </c>
-      <c r="O146" t="s">
-        <v>1646</v>
-      </c>
-      <c r="P146" t="s">
-        <v>1587</v>
-      </c>
-      <c r="Q146">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="147" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O147" t="s">
-        <v>1647</v>
-      </c>
-      <c r="P147" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q147">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="148" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N148" t="s">
-        <v>27</v>
-      </c>
-      <c r="O148" t="s">
-        <v>1648</v>
-      </c>
-      <c r="P148" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q148">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="149" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N149" t="s">
-        <v>27</v>
-      </c>
-      <c r="O149" t="s">
-        <v>1649</v>
-      </c>
-      <c r="P149" t="s">
-        <v>1554</v>
-      </c>
-      <c r="Q149">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="150" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O150" t="s">
-        <v>1650</v>
-      </c>
-      <c r="P150" t="s">
-        <v>1591</v>
-      </c>
-      <c r="Q150">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="151" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O151" t="s">
-        <v>1651</v>
-      </c>
-      <c r="P151" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q151">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="152" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N152" t="s">
-        <v>27</v>
-      </c>
-      <c r="O152" t="s">
-        <v>1652</v>
-      </c>
-      <c r="P152" t="s">
-        <v>1561</v>
-      </c>
-      <c r="Q152">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="153" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N153" t="s">
-        <v>27</v>
-      </c>
-      <c r="O153" t="s">
-        <v>1653</v>
-      </c>
-      <c r="P153" t="s">
-        <v>1561</v>
-      </c>
-      <c r="Q153">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="154" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N154" t="s">
-        <v>27</v>
-      </c>
-      <c r="O154" t="s">
-        <v>1654</v>
-      </c>
-      <c r="P154" t="s">
-        <v>1561</v>
-      </c>
-      <c r="Q154">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="155" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N155" t="s">
-        <v>27</v>
-      </c>
-      <c r="O155" t="s">
-        <v>1655</v>
-      </c>
-      <c r="P155" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q155">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="156" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N156" t="s">
-        <v>27</v>
-      </c>
-      <c r="O156" t="s">
-        <v>1656</v>
-      </c>
-      <c r="P156" t="s">
-        <v>1578</v>
-      </c>
-      <c r="Q156">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="157" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N157" t="s">
-        <v>27</v>
-      </c>
-      <c r="O157" t="s">
-        <v>1657</v>
-      </c>
-      <c r="P157" t="s">
-        <v>1593</v>
-      </c>
-      <c r="Q157">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="158" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N158" t="s">
-        <v>27</v>
-      </c>
-      <c r="O158" t="s">
-        <v>1658</v>
-      </c>
-      <c r="P158" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q158">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="159" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N159" t="s">
-        <v>27</v>
-      </c>
-      <c r="O159" t="s">
-        <v>1659</v>
-      </c>
-      <c r="P159" t="s">
-        <v>1598</v>
-      </c>
-      <c r="Q159">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="160" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N160" t="s">
-        <v>27</v>
-      </c>
-      <c r="O160" t="s">
-        <v>1660</v>
-      </c>
-      <c r="P160" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q160">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="161" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N161" t="s">
-        <v>27</v>
-      </c>
-      <c r="O161" t="s">
-        <v>1661</v>
-      </c>
-      <c r="P161" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q161">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="162" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N162" t="s">
-        <v>27</v>
-      </c>
-      <c r="O162" t="s">
-        <v>1662</v>
-      </c>
-      <c r="P162" t="s">
-        <v>1564</v>
-      </c>
-      <c r="Q162">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="163" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N163" t="s">
-        <v>27</v>
-      </c>
-      <c r="O163" t="s">
-        <v>1663</v>
-      </c>
-      <c r="P163" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q163">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="164" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N164" t="s">
-        <v>27</v>
-      </c>
-      <c r="O164" t="s">
-        <v>1664</v>
-      </c>
-      <c r="P164" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q164">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="165" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N165" t="s">
-        <v>27</v>
-      </c>
-      <c r="O165" t="s">
-        <v>1665</v>
-      </c>
-      <c r="P165" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q165">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="166" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N166" t="s">
-        <v>27</v>
-      </c>
-      <c r="O166" t="s">
-        <v>1666</v>
-      </c>
-      <c r="P166" t="s">
-        <v>1578</v>
-      </c>
-      <c r="Q166">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="167" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N167" t="s">
-        <v>27</v>
-      </c>
-      <c r="O167" t="s">
-        <v>1667</v>
-      </c>
-      <c r="P167" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q167">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="168" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N168" t="s">
-        <v>27</v>
-      </c>
-      <c r="O168" t="s">
-        <v>1668</v>
-      </c>
-      <c r="P168" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q168">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="169" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N169" t="s">
-        <v>27</v>
-      </c>
-      <c r="O169" t="s">
-        <v>1669</v>
-      </c>
-      <c r="P169" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q169">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="170" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N170" t="s">
-        <v>27</v>
-      </c>
-      <c r="O170" t="s">
-        <v>1670</v>
-      </c>
-      <c r="P170" t="s">
-        <v>1576</v>
-      </c>
-      <c r="Q170">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="171" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N171" t="s">
-        <v>27</v>
-      </c>
-      <c r="O171" t="s">
-        <v>1671</v>
-      </c>
-      <c r="P171" t="s">
-        <v>1576</v>
-      </c>
-      <c r="Q171">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="172" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N172" t="s">
-        <v>27</v>
-      </c>
-      <c r="O172" t="s">
-        <v>1672</v>
-      </c>
-      <c r="P172" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q172">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="173" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N173" t="s">
-        <v>27</v>
-      </c>
-      <c r="O173" t="s">
-        <v>1673</v>
-      </c>
-      <c r="P173" t="s">
-        <v>1554</v>
-      </c>
-      <c r="Q173">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="174" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N174" t="s">
-        <v>27</v>
-      </c>
-      <c r="O174" t="s">
-        <v>1674</v>
-      </c>
-      <c r="P174" t="s">
-        <v>1584</v>
-      </c>
-      <c r="Q174">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="175" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N175" t="s">
-        <v>27</v>
-      </c>
-      <c r="O175" t="s">
-        <v>1675</v>
-      </c>
-      <c r="P175" t="s">
-        <v>1598</v>
-      </c>
-      <c r="Q175">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="176" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N176" t="s">
-        <v>27</v>
-      </c>
-      <c r="O176" t="s">
-        <v>1676</v>
-      </c>
-      <c r="P176" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q176">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="177" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N177" t="s">
-        <v>27</v>
-      </c>
-      <c r="O177" t="s">
-        <v>1677</v>
-      </c>
-      <c r="P177" t="s">
-        <v>1584</v>
-      </c>
-      <c r="Q177">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="178" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N178" t="s">
-        <v>27</v>
-      </c>
-      <c r="O178" t="s">
-        <v>1678</v>
-      </c>
-      <c r="P178" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q178">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="179" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N179" t="s">
-        <v>27</v>
-      </c>
-      <c r="O179" t="s">
-        <v>1679</v>
-      </c>
-      <c r="P179" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q179">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="180" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N180" t="s">
-        <v>27</v>
-      </c>
-      <c r="O180" t="s">
-        <v>1680</v>
-      </c>
-      <c r="P180" t="s">
-        <v>1589</v>
-      </c>
-      <c r="Q180">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="181" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N181" t="s">
-        <v>27</v>
-      </c>
-      <c r="O181" t="s">
-        <v>1681</v>
-      </c>
-      <c r="P181" t="s">
-        <v>1598</v>
-      </c>
-      <c r="Q181">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="182" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N182" t="s">
-        <v>27</v>
-      </c>
-      <c r="O182" t="s">
-        <v>1682</v>
-      </c>
-      <c r="P182" t="s">
-        <v>1563</v>
-      </c>
-      <c r="Q182">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="183" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N183" t="s">
-        <v>27</v>
-      </c>
-      <c r="O183" t="s">
-        <v>1683</v>
-      </c>
-      <c r="P183" t="s">
-        <v>1553</v>
-      </c>
-      <c r="Q183">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="184" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N184" t="s">
-        <v>27</v>
-      </c>
-      <c r="O184" t="s">
-        <v>1684</v>
-      </c>
-      <c r="P184" t="s">
-        <v>1578</v>
-      </c>
-      <c r="Q184">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="185" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N185" t="s">
-        <v>27</v>
-      </c>
-      <c r="O185" t="s">
-        <v>1685</v>
-      </c>
-      <c r="P185" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q185">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="186" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N186" t="s">
-        <v>27</v>
-      </c>
-      <c r="O186" t="s">
-        <v>1686</v>
-      </c>
-      <c r="P186" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q186">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="187" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N187" t="s">
-        <v>27</v>
-      </c>
-      <c r="O187" t="s">
-        <v>1687</v>
-      </c>
-      <c r="P187" t="s">
-        <v>1579</v>
-      </c>
-      <c r="Q187">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="188" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N188" t="s">
-        <v>27</v>
-      </c>
-      <c r="O188" t="s">
-        <v>1688</v>
-      </c>
-      <c r="P188" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q188">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="189" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N189" t="s">
-        <v>27</v>
-      </c>
-      <c r="O189" t="s">
-        <v>1689</v>
-      </c>
-      <c r="P189" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q189">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="190" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N190" t="s">
-        <v>27</v>
-      </c>
-      <c r="O190" t="s">
-        <v>1690</v>
-      </c>
-      <c r="P190" t="s">
-        <v>1552</v>
-      </c>
-      <c r="Q190">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="191" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N191" t="s">
-        <v>27</v>
-      </c>
-      <c r="O191" t="s">
-        <v>1691</v>
-      </c>
-      <c r="P191" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q191">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="192" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N192" t="s">
-        <v>27</v>
-      </c>
-      <c r="O192" t="s">
-        <v>1692</v>
-      </c>
-      <c r="P192" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q192">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="193" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N193" t="s">
-        <v>27</v>
-      </c>
-      <c r="O193" t="s">
-        <v>1693</v>
-      </c>
-      <c r="P193" t="s">
-        <v>1591</v>
-      </c>
-      <c r="Q193">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="194" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N194" t="s">
-        <v>27</v>
-      </c>
-      <c r="O194" t="s">
-        <v>1694</v>
-      </c>
-      <c r="P194" t="s">
-        <v>1595</v>
-      </c>
-      <c r="Q194">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="195" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N195" t="s">
-        <v>27</v>
-      </c>
-      <c r="O195" t="s">
-        <v>1695</v>
-      </c>
-      <c r="P195" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q195">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="196" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N196" t="s">
-        <v>27</v>
-      </c>
-      <c r="O196" t="s">
-        <v>1696</v>
-      </c>
-      <c r="P196" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q196">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="197" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N197" t="s">
-        <v>27</v>
-      </c>
-      <c r="O197" t="s">
-        <v>1697</v>
-      </c>
-      <c r="P197" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q197">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="198" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N198" t="s">
-        <v>27</v>
-      </c>
-      <c r="O198" t="s">
-        <v>1698</v>
-      </c>
-      <c r="P198" t="s">
-        <v>1589</v>
-      </c>
-      <c r="Q198">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="199" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N199" t="s">
-        <v>27</v>
-      </c>
-      <c r="O199" t="s">
-        <v>1699</v>
-      </c>
-      <c r="P199" t="s">
-        <v>1572</v>
-      </c>
-      <c r="Q199">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="200" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N200" t="s">
-        <v>27</v>
-      </c>
-      <c r="O200" t="s">
-        <v>1700</v>
-      </c>
-      <c r="P200" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q200">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="201" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N201" t="s">
-        <v>27</v>
-      </c>
-      <c r="O201" t="s">
-        <v>1701</v>
-      </c>
-      <c r="P201" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q201">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="202" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N202" t="s">
-        <v>27</v>
-      </c>
-      <c r="O202" t="s">
-        <v>1702</v>
-      </c>
-      <c r="P202" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q202">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="203" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N203" t="s">
-        <v>27</v>
-      </c>
-      <c r="O203" t="s">
-        <v>1703</v>
-      </c>
-      <c r="P203" t="s">
-        <v>1561</v>
-      </c>
-      <c r="Q203">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="204" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N204" t="s">
-        <v>27</v>
-      </c>
-      <c r="O204" t="s">
-        <v>1704</v>
-      </c>
-      <c r="P204" t="s">
-        <v>1565</v>
-      </c>
-      <c r="Q204">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="205" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N205" t="s">
-        <v>27</v>
-      </c>
-      <c r="O205" t="s">
-        <v>1705</v>
-      </c>
-      <c r="P205" t="s">
-        <v>1584</v>
-      </c>
-      <c r="Q205">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="206" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N206" t="s">
-        <v>27</v>
-      </c>
-      <c r="O206" t="s">
-        <v>1706</v>
-      </c>
-      <c r="P206" t="s">
-        <v>1561</v>
-      </c>
-      <c r="Q206">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="207" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N207" t="s">
-        <v>27</v>
-      </c>
-      <c r="O207" t="s">
-        <v>1707</v>
-      </c>
-      <c r="P207" t="s">
-        <v>1591</v>
-      </c>
-      <c r="Q207">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="208" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N208" t="s">
-        <v>27</v>
-      </c>
-      <c r="O208" t="s">
-        <v>1708</v>
-      </c>
-      <c r="P208" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q208">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="209" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N209" t="s">
-        <v>27</v>
-      </c>
-      <c r="O209" t="s">
-        <v>1709</v>
-      </c>
-      <c r="P209" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q209">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="210" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N210" t="s">
-        <v>27</v>
-      </c>
-      <c r="O210" t="s">
-        <v>1710</v>
-      </c>
-      <c r="P210" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q210">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="211" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N211" t="s">
-        <v>27</v>
-      </c>
-      <c r="O211" t="s">
-        <v>1711</v>
-      </c>
-      <c r="P211" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q211">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="212" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N212" t="s">
-        <v>27</v>
-      </c>
-      <c r="O212" t="s">
-        <v>1712</v>
-      </c>
-      <c r="P212" t="s">
-        <v>1558</v>
-      </c>
-      <c r="Q212">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="213" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N213" t="s">
-        <v>27</v>
-      </c>
-      <c r="O213" t="s">
-        <v>1713</v>
-      </c>
-      <c r="P213" t="s">
-        <v>1556</v>
-      </c>
-      <c r="Q213">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="214" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N214" t="s">
-        <v>27</v>
-      </c>
-      <c r="O214" t="s">
-        <v>1714</v>
-      </c>
-      <c r="P214" t="s">
-        <v>1598</v>
-      </c>
-      <c r="Q214">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="215" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N215" t="s">
-        <v>27</v>
-      </c>
-      <c r="O215" t="s">
-        <v>1715</v>
-      </c>
-      <c r="P215" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q215">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="216" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N216" t="s">
-        <v>27</v>
-      </c>
-      <c r="O216" t="s">
-        <v>1716</v>
-      </c>
-      <c r="P216" t="s">
-        <v>1562</v>
-      </c>
-      <c r="Q216">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="217" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N217" t="s">
-        <v>27</v>
-      </c>
-      <c r="O217" t="s">
-        <v>1717</v>
-      </c>
-      <c r="P217" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q217">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="218" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N218" t="s">
-        <v>27</v>
-      </c>
-      <c r="O218" t="s">
-        <v>1718</v>
-      </c>
-      <c r="P218" t="s">
-        <v>1589</v>
-      </c>
-      <c r="Q218">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="219" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N219" t="s">
-        <v>27</v>
-      </c>
-      <c r="O219" t="s">
-        <v>1719</v>
-      </c>
-      <c r="P219" t="s">
-        <v>1552</v>
-      </c>
-      <c r="Q219">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="220" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N220" t="s">
-        <v>27</v>
-      </c>
-      <c r="O220" t="s">
-        <v>1720</v>
-      </c>
-      <c r="P220" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q220">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="221" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N221" t="s">
-        <v>27</v>
-      </c>
-      <c r="O221" t="s">
-        <v>1721</v>
-      </c>
-      <c r="P221" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q221">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="222" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N222" t="s">
-        <v>27</v>
-      </c>
-      <c r="O222" t="s">
-        <v>1722</v>
-      </c>
-      <c r="P222" t="s">
-        <v>1562</v>
-      </c>
-      <c r="Q222">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="223" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N223" t="s">
-        <v>27</v>
-      </c>
-      <c r="O223" t="s">
-        <v>1723</v>
-      </c>
-      <c r="P223" t="s">
-        <v>1598</v>
-      </c>
-      <c r="Q223">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="224" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N224" t="s">
-        <v>27</v>
-      </c>
-      <c r="O224" t="s">
-        <v>1724</v>
-      </c>
-      <c r="P224" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q224">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="225" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N225" t="s">
-        <v>27</v>
-      </c>
-      <c r="O225" t="s">
-        <v>1725</v>
-      </c>
-      <c r="P225" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q225">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="226" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N226" t="s">
-        <v>27</v>
-      </c>
-      <c r="O226" t="s">
-        <v>1726</v>
-      </c>
-      <c r="P226" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q226">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="227" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N227" t="s">
-        <v>27</v>
-      </c>
-      <c r="O227" t="s">
-        <v>1727</v>
-      </c>
-      <c r="P227" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q227">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="228" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N228" t="s">
-        <v>27</v>
-      </c>
-      <c r="O228" t="s">
-        <v>1728</v>
-      </c>
-      <c r="P228" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q228">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="229" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N229" t="s">
-        <v>27</v>
-      </c>
-      <c r="O229" t="s">
-        <v>1729</v>
-      </c>
-      <c r="P229" t="s">
-        <v>1562</v>
-      </c>
-      <c r="Q229">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="230" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N230" t="s">
-        <v>27</v>
-      </c>
-      <c r="O230" t="s">
-        <v>1730</v>
-      </c>
-      <c r="P230" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q230">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="231" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N231" t="s">
-        <v>27</v>
-      </c>
-      <c r="O231" t="s">
-        <v>1731</v>
-      </c>
-      <c r="P231" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q231">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="232" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N232" t="s">
-        <v>27</v>
-      </c>
-      <c r="O232" t="s">
-        <v>1732</v>
-      </c>
-      <c r="P232" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q232">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="233" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N233" t="s">
-        <v>27</v>
-      </c>
-      <c r="O233" t="s">
-        <v>1733</v>
-      </c>
-      <c r="P233" t="s">
-        <v>1554</v>
-      </c>
-      <c r="Q233">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="234" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N234" t="s">
-        <v>27</v>
-      </c>
-      <c r="O234" t="s">
-        <v>1734</v>
-      </c>
-      <c r="P234" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q234">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="235" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N235" t="s">
-        <v>27</v>
-      </c>
-      <c r="O235" t="s">
-        <v>1735</v>
-      </c>
-      <c r="P235" t="s">
-        <v>1584</v>
-      </c>
-      <c r="Q235">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="236" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N236" t="s">
-        <v>27</v>
-      </c>
-      <c r="O236" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P236" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q236">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="237" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N237" t="s">
-        <v>27</v>
-      </c>
-      <c r="O237" t="s">
-        <v>1737</v>
-      </c>
-      <c r="P237" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q237">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="238" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N238" t="s">
-        <v>27</v>
-      </c>
-      <c r="O238" t="s">
-        <v>1738</v>
-      </c>
-      <c r="P238" t="s">
-        <v>1587</v>
-      </c>
-      <c r="Q238">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="239" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N239" t="s">
-        <v>27</v>
-      </c>
-      <c r="O239" t="s">
-        <v>1739</v>
-      </c>
-      <c r="P239" t="s">
-        <v>1578</v>
-      </c>
-      <c r="Q239">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="240" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N240" t="s">
-        <v>27</v>
-      </c>
-      <c r="O240" t="s">
-        <v>1740</v>
-      </c>
-      <c r="P240" t="s">
-        <v>1558</v>
-      </c>
-      <c r="Q240">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="241" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N241" t="s">
-        <v>27</v>
-      </c>
-      <c r="O241" t="s">
-        <v>1741</v>
-      </c>
-      <c r="P241" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q241">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="242" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N242" t="s">
-        <v>27</v>
-      </c>
-      <c r="O242" t="s">
-        <v>1742</v>
-      </c>
-      <c r="P242" t="s">
-        <v>1562</v>
-      </c>
-      <c r="Q242">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="243" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N243" t="s">
-        <v>27</v>
-      </c>
-      <c r="O243" t="s">
-        <v>1743</v>
-      </c>
-      <c r="P243" t="s">
-        <v>1593</v>
-      </c>
-      <c r="Q243">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="244" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N244" t="s">
-        <v>27</v>
-      </c>
-      <c r="O244" t="s">
-        <v>1744</v>
-      </c>
-      <c r="P244" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q244">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="245" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N245" t="s">
-        <v>27</v>
-      </c>
-      <c r="O245" t="s">
-        <v>1745</v>
-      </c>
-      <c r="P245" t="s">
-        <v>1589</v>
-      </c>
-      <c r="Q245">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="246" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N246" t="s">
-        <v>27</v>
-      </c>
-      <c r="O246" t="s">
-        <v>1746</v>
-      </c>
-      <c r="P246" t="s">
-        <v>1591</v>
-      </c>
-      <c r="Q246">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="247" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N247" t="s">
-        <v>27</v>
-      </c>
-      <c r="O247" t="s">
-        <v>1747</v>
-      </c>
-      <c r="P247" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q247">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="248" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N248" t="s">
-        <v>27</v>
-      </c>
-      <c r="O248" t="s">
-        <v>1748</v>
-      </c>
-      <c r="P248" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q248">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="249" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N249" t="s">
-        <v>27</v>
-      </c>
-      <c r="O249" t="s">
-        <v>1749</v>
-      </c>
-      <c r="P249" t="s">
-        <v>1561</v>
-      </c>
-      <c r="Q249">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="250" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N250" t="s">
-        <v>27</v>
-      </c>
-      <c r="O250" t="s">
-        <v>1750</v>
-      </c>
-      <c r="P250" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q250">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="251" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N251" t="s">
-        <v>27</v>
-      </c>
-      <c r="O251" t="s">
-        <v>1751</v>
-      </c>
-      <c r="P251" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q251">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="252" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N252" t="s">
-        <v>27</v>
-      </c>
-      <c r="O252" t="s">
-        <v>1752</v>
-      </c>
-      <c r="P252" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q252">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="253" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N253" t="s">
-        <v>27</v>
-      </c>
-      <c r="O253" t="s">
-        <v>1753</v>
-      </c>
-      <c r="P253" t="s">
-        <v>1552</v>
-      </c>
-      <c r="Q253">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="254" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N254" t="s">
-        <v>27</v>
-      </c>
-      <c r="O254" t="s">
-        <v>1754</v>
-      </c>
-      <c r="P254" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q254">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="255" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N255" t="s">
-        <v>27</v>
-      </c>
-      <c r="O255" t="s">
-        <v>1755</v>
-      </c>
-      <c r="P255" t="s">
-        <v>1594</v>
-      </c>
-      <c r="Q255">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="256" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N256" t="s">
-        <v>27</v>
-      </c>
-      <c r="O256" t="s">
-        <v>1756</v>
-      </c>
-      <c r="P256" t="s">
-        <v>1598</v>
-      </c>
-      <c r="Q256">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="257" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N257" t="s">
-        <v>27</v>
-      </c>
-      <c r="O257" t="s">
-        <v>1757</v>
-      </c>
-      <c r="P257" t="s">
-        <v>1558</v>
-      </c>
-      <c r="Q257">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="258" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N258" t="s">
-        <v>27</v>
-      </c>
-      <c r="O258" t="s">
-        <v>1758</v>
-      </c>
-      <c r="P258" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q258">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="259" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N259" t="s">
-        <v>27</v>
-      </c>
-      <c r="O259" t="s">
-        <v>1759</v>
-      </c>
-      <c r="P259" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q259">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="260" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N260" t="s">
-        <v>27</v>
-      </c>
-      <c r="O260" t="s">
-        <v>1760</v>
-      </c>
-      <c r="P260" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q260">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="261" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N261" t="s">
-        <v>27</v>
-      </c>
-      <c r="O261" t="s">
-        <v>1761</v>
-      </c>
-      <c r="P261" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q261">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="262" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N262" t="s">
-        <v>27</v>
-      </c>
-      <c r="O262" t="s">
-        <v>1762</v>
-      </c>
-      <c r="P262" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q262">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="263" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N263" t="s">
-        <v>27</v>
-      </c>
-      <c r="O263" t="s">
-        <v>1763</v>
-      </c>
-      <c r="P263" t="s">
-        <v>1558</v>
-      </c>
-      <c r="Q263">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="264" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N264" t="s">
-        <v>27</v>
-      </c>
-      <c r="O264" t="s">
-        <v>1764</v>
-      </c>
-      <c r="P264" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q264">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="265" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N265" t="s">
-        <v>27</v>
-      </c>
-      <c r="O265" t="s">
-        <v>1765</v>
-      </c>
-      <c r="P265" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q265">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="266" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N266" t="s">
-        <v>27</v>
-      </c>
-      <c r="O266" t="s">
-        <v>1766</v>
-      </c>
-      <c r="P266" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q266">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="267" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N267" t="s">
-        <v>27</v>
-      </c>
-      <c r="O267" t="s">
-        <v>1767</v>
-      </c>
-      <c r="P267" t="s">
-        <v>1573</v>
-      </c>
-      <c r="Q267">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="268" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N268" t="s">
-        <v>27</v>
-      </c>
-      <c r="O268" t="s">
-        <v>1768</v>
-      </c>
-      <c r="P268" t="s">
-        <v>1562</v>
-      </c>
-      <c r="Q268">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="269" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N269" t="s">
-        <v>27</v>
-      </c>
-      <c r="O269" t="s">
-        <v>1769</v>
-      </c>
-      <c r="P269" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q269">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="270" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N270" t="s">
-        <v>27</v>
-      </c>
-      <c r="O270" t="s">
-        <v>1770</v>
-      </c>
-      <c r="P270" t="s">
-        <v>1592</v>
-      </c>
-      <c r="Q270">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="271" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N271" t="s">
-        <v>27</v>
-      </c>
-      <c r="O271" t="s">
-        <v>1771</v>
-      </c>
-      <c r="P271" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q271">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="272" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N272" t="s">
-        <v>27</v>
-      </c>
-      <c r="O272" t="s">
-        <v>1772</v>
-      </c>
-      <c r="P272" t="s">
-        <v>1563</v>
-      </c>
-      <c r="Q272">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="273" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N273" t="s">
-        <v>27</v>
-      </c>
-      <c r="O273" t="s">
-        <v>1773</v>
-      </c>
-      <c r="P273" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q273">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="274" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N274" t="s">
-        <v>27</v>
-      </c>
-      <c r="O274" t="s">
-        <v>1774</v>
-      </c>
-      <c r="P274" t="s">
-        <v>1552</v>
-      </c>
-      <c r="Q274">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="275" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N275" t="s">
-        <v>27</v>
-      </c>
-      <c r="O275" t="s">
-        <v>1775</v>
-      </c>
-      <c r="P275" t="s">
-        <v>1596</v>
-      </c>
-      <c r="Q275">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="276" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N276" t="s">
-        <v>27</v>
-      </c>
-      <c r="O276" t="s">
-        <v>1776</v>
-      </c>
-      <c r="P276" t="s">
-        <v>1591</v>
-      </c>
-      <c r="Q276">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="277" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N277" t="s">
-        <v>27</v>
-      </c>
-      <c r="O277" t="s">
-        <v>1777</v>
-      </c>
-      <c r="P277" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q277">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="278" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N278" t="s">
-        <v>27</v>
-      </c>
-      <c r="O278" t="s">
-        <v>1778</v>
-      </c>
-      <c r="P278" t="s">
-        <v>1586</v>
-      </c>
-      <c r="Q278">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="279" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N279" t="s">
-        <v>27</v>
-      </c>
-      <c r="O279" t="s">
-        <v>1779</v>
-      </c>
-      <c r="P279" t="s">
-        <v>1599</v>
-      </c>
-      <c r="Q279">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="280" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N280" t="s">
-        <v>27</v>
-      </c>
-      <c r="O280" t="s">
-        <v>1780</v>
-      </c>
-      <c r="P280" t="s">
-        <v>1580</v>
-      </c>
-      <c r="Q280">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="281" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N281" t="s">
-        <v>27</v>
-      </c>
-      <c r="O281" t="s">
-        <v>1781</v>
-      </c>
-      <c r="P281" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q281">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="282" spans="14:17" x14ac:dyDescent="0.45">
-      <c r="N282" t="s">
-        <v>27</v>
-      </c>
-      <c r="O282" t="s">
-        <v>1782</v>
-      </c>
-      <c r="P282" t="s">
-        <v>1568</v>
-      </c>
-      <c r="Q282">
-        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -56473,13 +54315,13 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97194A4B-A255-4A68-9D8A-8655EBAD698F}">
-  <dimension ref="A1:I53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAC7CE8-9EFF-40B4-9836-F2F1A13F0504}">
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C1" t="s">
-        <v>1783</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -56487,7 +54329,7 @@
         <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>1784</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -56501,10 +54343,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>1785</v>
+        <v>1639</v>
       </c>
       <c r="E4" t="s">
-        <v>1786</v>
+        <v>1640</v>
       </c>
       <c r="G4" t="s">
         <v>60</v>
@@ -56513,18 +54355,18 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>1785</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B5" t="s">
-        <v>1788</v>
+        <v>1642</v>
       </c>
       <c r="C5" t="s">
-        <v>1789</v>
+        <v>1643</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -56533,10 +54375,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>1788</v>
+        <v>1642</v>
       </c>
       <c r="H5" t="s">
-        <v>1789</v>
+        <v>1643</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -56544,13 +54386,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B6" t="s">
-        <v>1790</v>
+        <v>1644</v>
       </c>
       <c r="C6" t="s">
-        <v>1791</v>
+        <v>1645</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -56559,10 +54401,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>1790</v>
+        <v>1644</v>
       </c>
       <c r="H6" t="s">
-        <v>1791</v>
+        <v>1645</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -56570,13 +54412,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B7" t="s">
-        <v>1792</v>
+        <v>1646</v>
       </c>
       <c r="C7" t="s">
-        <v>1793</v>
+        <v>1647</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -56585,10 +54427,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>1792</v>
+        <v>1646</v>
       </c>
       <c r="H7" t="s">
-        <v>1793</v>
+        <v>1647</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -56596,13 +54438,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B8" t="s">
-        <v>1794</v>
+        <v>1648</v>
       </c>
       <c r="C8" t="s">
-        <v>1795</v>
+        <v>1649</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -56611,10 +54453,10 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>1794</v>
+        <v>1648</v>
       </c>
       <c r="H8" t="s">
-        <v>1795</v>
+        <v>1649</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -56622,13 +54464,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B9" t="s">
-        <v>1796</v>
+        <v>1650</v>
       </c>
       <c r="C9" t="s">
-        <v>1797</v>
+        <v>1651</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -56637,10 +54479,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>1796</v>
+        <v>1650</v>
       </c>
       <c r="H9" t="s">
-        <v>1797</v>
+        <v>1651</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -56648,13 +54490,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B10" t="s">
-        <v>1798</v>
+        <v>1652</v>
       </c>
       <c r="C10" t="s">
-        <v>1799</v>
+        <v>1653</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -56663,10 +54505,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>1798</v>
+        <v>1652</v>
       </c>
       <c r="H10" t="s">
-        <v>1799</v>
+        <v>1653</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -56674,13 +54516,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B11" t="s">
-        <v>1800</v>
+        <v>1654</v>
       </c>
       <c r="C11" t="s">
-        <v>1801</v>
+        <v>1655</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -56689,10 +54531,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>1800</v>
+        <v>1654</v>
       </c>
       <c r="H11" t="s">
-        <v>1801</v>
+        <v>1655</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -56700,13 +54542,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B12" t="s">
-        <v>1802</v>
+        <v>1656</v>
       </c>
       <c r="C12" t="s">
-        <v>1803</v>
+        <v>1657</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -56715,10 +54557,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>1802</v>
+        <v>1656</v>
       </c>
       <c r="H12" t="s">
-        <v>1803</v>
+        <v>1657</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -56726,13 +54568,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B13" t="s">
-        <v>1804</v>
+        <v>1658</v>
       </c>
       <c r="C13" t="s">
-        <v>1805</v>
+        <v>1659</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -56741,10 +54583,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>1804</v>
+        <v>1658</v>
       </c>
       <c r="H13" t="s">
-        <v>1805</v>
+        <v>1659</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -56752,13 +54594,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B14" t="s">
-        <v>1806</v>
+        <v>1660</v>
       </c>
       <c r="C14" t="s">
-        <v>1807</v>
+        <v>1661</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -56767,10 +54609,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>1806</v>
+        <v>1660</v>
       </c>
       <c r="H14" t="s">
-        <v>1807</v>
+        <v>1661</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -56778,13 +54620,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B15" t="s">
-        <v>1808</v>
+        <v>1662</v>
       </c>
       <c r="C15" t="s">
-        <v>1809</v>
+        <v>1663</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -56793,10 +54635,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>1808</v>
+        <v>1662</v>
       </c>
       <c r="H15" t="s">
-        <v>1809</v>
+        <v>1663</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -56804,13 +54646,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B16" t="s">
-        <v>1810</v>
+        <v>1664</v>
       </c>
       <c r="C16" t="s">
-        <v>1811</v>
+        <v>1665</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -56819,10 +54661,10 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>1810</v>
+        <v>1664</v>
       </c>
       <c r="H16" t="s">
-        <v>1811</v>
+        <v>1665</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -56830,13 +54672,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B17" t="s">
-        <v>1812</v>
+        <v>1666</v>
       </c>
       <c r="C17" t="s">
-        <v>1813</v>
+        <v>1667</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -56845,10 +54687,10 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>1812</v>
+        <v>1666</v>
       </c>
       <c r="H17" t="s">
-        <v>1813</v>
+        <v>1667</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -56856,13 +54698,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B18" t="s">
-        <v>1814</v>
+        <v>1668</v>
       </c>
       <c r="C18" t="s">
-        <v>1815</v>
+        <v>1669</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -56871,10 +54713,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>1814</v>
+        <v>1668</v>
       </c>
       <c r="H18" t="s">
-        <v>1815</v>
+        <v>1669</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -56882,13 +54724,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B19" t="s">
-        <v>1816</v>
+        <v>1670</v>
       </c>
       <c r="C19" t="s">
-        <v>1817</v>
+        <v>1671</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -56897,10 +54739,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>1816</v>
+        <v>1670</v>
       </c>
       <c r="H19" t="s">
-        <v>1817</v>
+        <v>1671</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -56908,13 +54750,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B20" t="s">
-        <v>1818</v>
+        <v>1672</v>
       </c>
       <c r="C20" t="s">
-        <v>1819</v>
+        <v>1673</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -56923,10 +54765,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>1818</v>
+        <v>1672</v>
       </c>
       <c r="H20" t="s">
-        <v>1819</v>
+        <v>1673</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -56934,13 +54776,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B21" t="s">
-        <v>1820</v>
+        <v>1674</v>
       </c>
       <c r="C21" t="s">
-        <v>1821</v>
+        <v>1675</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -56949,10 +54791,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>1820</v>
+        <v>1674</v>
       </c>
       <c r="H21" t="s">
-        <v>1821</v>
+        <v>1675</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -56960,13 +54802,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B22" t="s">
-        <v>1822</v>
+        <v>1676</v>
       </c>
       <c r="C22" t="s">
-        <v>1823</v>
+        <v>1677</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -56975,10 +54817,10 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>1822</v>
+        <v>1676</v>
       </c>
       <c r="H22" t="s">
-        <v>1823</v>
+        <v>1677</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -56986,13 +54828,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B23" t="s">
-        <v>1824</v>
+        <v>1678</v>
       </c>
       <c r="C23" t="s">
-        <v>1825</v>
+        <v>1679</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -57001,10 +54843,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>1824</v>
+        <v>1678</v>
       </c>
       <c r="H23" t="s">
-        <v>1825</v>
+        <v>1679</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -57012,13 +54854,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B24" t="s">
-        <v>1826</v>
+        <v>1680</v>
       </c>
       <c r="C24" t="s">
-        <v>1827</v>
+        <v>1681</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -57027,10 +54869,10 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>1826</v>
+        <v>1680</v>
       </c>
       <c r="H24" t="s">
-        <v>1827</v>
+        <v>1681</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -57038,13 +54880,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B25" t="s">
-        <v>1828</v>
+        <v>1682</v>
       </c>
       <c r="C25" t="s">
-        <v>1829</v>
+        <v>1683</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -57053,10 +54895,10 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>1828</v>
+        <v>1682</v>
       </c>
       <c r="H25" t="s">
-        <v>1829</v>
+        <v>1683</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -57064,13 +54906,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B26" t="s">
-        <v>1830</v>
+        <v>1684</v>
       </c>
       <c r="C26" t="s">
-        <v>1831</v>
+        <v>1685</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -57079,10 +54921,10 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>1830</v>
+        <v>1684</v>
       </c>
       <c r="H26" t="s">
-        <v>1831</v>
+        <v>1685</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -57090,13 +54932,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B27" t="s">
-        <v>1832</v>
+        <v>1686</v>
       </c>
       <c r="C27" t="s">
-        <v>1833</v>
+        <v>1687</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -57105,10 +54947,10 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>1832</v>
+        <v>1686</v>
       </c>
       <c r="H27" t="s">
-        <v>1833</v>
+        <v>1687</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -57116,13 +54958,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B28" t="s">
-        <v>1834</v>
+        <v>1688</v>
       </c>
       <c r="C28" t="s">
-        <v>1835</v>
+        <v>1689</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -57131,10 +54973,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>1834</v>
+        <v>1688</v>
       </c>
       <c r="H28" t="s">
-        <v>1835</v>
+        <v>1689</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -57142,13 +54984,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B29" t="s">
-        <v>1836</v>
+        <v>1690</v>
       </c>
       <c r="C29" t="s">
-        <v>1837</v>
+        <v>1691</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -57157,10 +54999,10 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>1836</v>
+        <v>1690</v>
       </c>
       <c r="H29" t="s">
-        <v>1837</v>
+        <v>1691</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -57168,13 +55010,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B30" t="s">
-        <v>1838</v>
+        <v>1692</v>
       </c>
       <c r="C30" t="s">
-        <v>1839</v>
+        <v>1693</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -57183,10 +55025,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>1838</v>
+        <v>1692</v>
       </c>
       <c r="H30" t="s">
-        <v>1839</v>
+        <v>1693</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -57194,13 +55036,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B31" t="s">
-        <v>1840</v>
+        <v>1694</v>
       </c>
       <c r="C31" t="s">
-        <v>1841</v>
+        <v>1695</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -57209,10 +55051,10 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>1840</v>
+        <v>1694</v>
       </c>
       <c r="H31" t="s">
-        <v>1841</v>
+        <v>1695</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -57220,13 +55062,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B32" t="s">
-        <v>1842</v>
+        <v>1696</v>
       </c>
       <c r="C32" t="s">
-        <v>1843</v>
+        <v>1697</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -57235,10 +55077,10 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>1842</v>
+        <v>1696</v>
       </c>
       <c r="H32" t="s">
-        <v>1843</v>
+        <v>1697</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -57246,13 +55088,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B33" t="s">
-        <v>1844</v>
+        <v>1698</v>
       </c>
       <c r="C33" t="s">
-        <v>1845</v>
+        <v>1699</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -57261,10 +55103,10 @@
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>1844</v>
+        <v>1698</v>
       </c>
       <c r="H33" t="s">
-        <v>1845</v>
+        <v>1699</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -57272,13 +55114,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B34" t="s">
-        <v>1846</v>
+        <v>1700</v>
       </c>
       <c r="C34" t="s">
-        <v>1847</v>
+        <v>1701</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -57287,10 +55129,10 @@
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>1846</v>
+        <v>1700</v>
       </c>
       <c r="H34" t="s">
-        <v>1847</v>
+        <v>1701</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -57298,13 +55140,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B35" t="s">
-        <v>1848</v>
+        <v>1702</v>
       </c>
       <c r="C35" t="s">
-        <v>1849</v>
+        <v>1703</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -57313,10 +55155,10 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>1848</v>
+        <v>1702</v>
       </c>
       <c r="H35" t="s">
-        <v>1849</v>
+        <v>1703</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -57324,13 +55166,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B36" t="s">
-        <v>1850</v>
+        <v>1704</v>
       </c>
       <c r="C36" t="s">
-        <v>1851</v>
+        <v>1705</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -57339,10 +55181,10 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>1850</v>
+        <v>1704</v>
       </c>
       <c r="H36" t="s">
-        <v>1851</v>
+        <v>1705</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -57350,13 +55192,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B37" t="s">
-        <v>1852</v>
+        <v>1706</v>
       </c>
       <c r="C37" t="s">
-        <v>1853</v>
+        <v>1707</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -57365,10 +55207,10 @@
         <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>1852</v>
+        <v>1706</v>
       </c>
       <c r="H37" t="s">
-        <v>1853</v>
+        <v>1707</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -57376,13 +55218,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B38" t="s">
-        <v>1854</v>
+        <v>1708</v>
       </c>
       <c r="C38" t="s">
-        <v>1855</v>
+        <v>1709</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -57391,10 +55233,10 @@
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>1854</v>
+        <v>1708</v>
       </c>
       <c r="H38" t="s">
-        <v>1855</v>
+        <v>1709</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -57402,13 +55244,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B39" t="s">
-        <v>1856</v>
+        <v>1710</v>
       </c>
       <c r="C39" t="s">
-        <v>1857</v>
+        <v>1711</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -57417,10 +55259,10 @@
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>1856</v>
+        <v>1710</v>
       </c>
       <c r="H39" t="s">
-        <v>1857</v>
+        <v>1711</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -57428,13 +55270,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B40" t="s">
-        <v>1858</v>
+        <v>1712</v>
       </c>
       <c r="C40" t="s">
-        <v>1859</v>
+        <v>1713</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -57443,10 +55285,10 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1858</v>
+        <v>1712</v>
       </c>
       <c r="H40" t="s">
-        <v>1859</v>
+        <v>1713</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -57454,13 +55296,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B41" t="s">
-        <v>1860</v>
+        <v>1714</v>
       </c>
       <c r="C41" t="s">
-        <v>1861</v>
+        <v>1715</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -57469,10 +55311,10 @@
         <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>1860</v>
+        <v>1714</v>
       </c>
       <c r="H41" t="s">
-        <v>1861</v>
+        <v>1715</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -57480,13 +55322,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B42" t="s">
-        <v>1862</v>
+        <v>1716</v>
       </c>
       <c r="C42" t="s">
-        <v>1863</v>
+        <v>1717</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -57495,10 +55337,10 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>1862</v>
+        <v>1716</v>
       </c>
       <c r="H42" t="s">
-        <v>1863</v>
+        <v>1717</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -57506,13 +55348,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B43" t="s">
-        <v>1864</v>
+        <v>1718</v>
       </c>
       <c r="C43" t="s">
-        <v>1865</v>
+        <v>1719</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -57521,10 +55363,10 @@
         <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>1864</v>
+        <v>1718</v>
       </c>
       <c r="H43" t="s">
-        <v>1865</v>
+        <v>1719</v>
       </c>
       <c r="I43">
         <v>-1</v>
@@ -57532,13 +55374,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B44" t="s">
-        <v>1866</v>
+        <v>1720</v>
       </c>
       <c r="C44" t="s">
-        <v>1867</v>
+        <v>1721</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -57547,10 +55389,10 @@
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>1866</v>
+        <v>1720</v>
       </c>
       <c r="H44" t="s">
-        <v>1867</v>
+        <v>1721</v>
       </c>
       <c r="I44">
         <v>-1</v>
@@ -57558,13 +55400,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B45" t="s">
-        <v>1868</v>
+        <v>1722</v>
       </c>
       <c r="C45" t="s">
-        <v>1869</v>
+        <v>1723</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -57573,10 +55415,10 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>1868</v>
+        <v>1722</v>
       </c>
       <c r="H45" t="s">
-        <v>1869</v>
+        <v>1723</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -57584,13 +55426,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B46" t="s">
-        <v>1870</v>
+        <v>1724</v>
       </c>
       <c r="C46" t="s">
-        <v>1871</v>
+        <v>1725</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -57599,10 +55441,10 @@
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>1870</v>
+        <v>1724</v>
       </c>
       <c r="H46" t="s">
-        <v>1871</v>
+        <v>1725</v>
       </c>
       <c r="I46">
         <v>-1</v>
@@ -57610,13 +55452,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B47" t="s">
-        <v>1872</v>
+        <v>1726</v>
       </c>
       <c r="C47" t="s">
-        <v>1873</v>
+        <v>1727</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -57625,10 +55467,10 @@
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>1872</v>
+        <v>1726</v>
       </c>
       <c r="H47" t="s">
-        <v>1873</v>
+        <v>1727</v>
       </c>
       <c r="I47">
         <v>-1</v>
@@ -57636,13 +55478,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B48" t="s">
-        <v>1874</v>
+        <v>1728</v>
       </c>
       <c r="C48" t="s">
-        <v>1875</v>
+        <v>1729</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -57651,10 +55493,10 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>1874</v>
+        <v>1728</v>
       </c>
       <c r="H48" t="s">
-        <v>1875</v>
+        <v>1729</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -57662,13 +55504,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B49" t="s">
-        <v>1876</v>
+        <v>1730</v>
       </c>
       <c r="C49" t="s">
-        <v>1877</v>
+        <v>1731</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -57677,10 +55519,10 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>1876</v>
+        <v>1730</v>
       </c>
       <c r="H49" t="s">
-        <v>1877</v>
+        <v>1731</v>
       </c>
       <c r="I49">
         <v>-1</v>
@@ -57688,13 +55530,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B50" t="s">
-        <v>1878</v>
+        <v>1732</v>
       </c>
       <c r="C50" t="s">
-        <v>1879</v>
+        <v>1733</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -57703,10 +55545,10 @@
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>1878</v>
+        <v>1732</v>
       </c>
       <c r="H50" t="s">
-        <v>1879</v>
+        <v>1733</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -57714,13 +55556,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B51" t="s">
-        <v>1880</v>
+        <v>1734</v>
       </c>
       <c r="C51" t="s">
-        <v>1881</v>
+        <v>1735</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -57729,10 +55571,10 @@
         <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>1880</v>
+        <v>1734</v>
       </c>
       <c r="H51" t="s">
-        <v>1881</v>
+        <v>1735</v>
       </c>
       <c r="I51">
         <v>-1</v>
@@ -57740,13 +55582,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B52" t="s">
-        <v>1882</v>
+        <v>1736</v>
       </c>
       <c r="C52" t="s">
-        <v>1883</v>
+        <v>1737</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -57755,10 +55597,10 @@
         <v>2</v>
       </c>
       <c r="G52" t="s">
-        <v>1882</v>
+        <v>1736</v>
       </c>
       <c r="H52" t="s">
-        <v>1883</v>
+        <v>1737</v>
       </c>
       <c r="I52">
         <v>-1</v>
@@ -57766,13 +55608,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>1787</v>
+        <v>1641</v>
       </c>
       <c r="B53" t="s">
-        <v>1884</v>
+        <v>1738</v>
       </c>
       <c r="C53" t="s">
-        <v>1885</v>
+        <v>1739</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -57781,12 +55623,1416 @@
         <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>1884</v>
+        <v>1738</v>
       </c>
       <c r="H53" t="s">
-        <v>1885</v>
+        <v>1739</v>
       </c>
       <c r="I53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1741</v>
+      </c>
+      <c r="I54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1742</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1743</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1745</v>
+      </c>
+      <c r="I56">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1747</v>
+      </c>
+      <c r="I57">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1748</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1749</v>
+      </c>
+      <c r="I58">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1751</v>
+      </c>
+      <c r="I59">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1753</v>
+      </c>
+      <c r="I60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1755</v>
+      </c>
+      <c r="I61">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1756</v>
+      </c>
+      <c r="H62" t="s">
+        <v>1757</v>
+      </c>
+      <c r="I62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1759</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1760</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1761</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1762</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1763</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1765</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1766</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1767</v>
+      </c>
+      <c r="I67">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1769</v>
+      </c>
+      <c r="I68">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1771</v>
+      </c>
+      <c r="I69">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1772</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1773</v>
+      </c>
+      <c r="I70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1774</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1775</v>
+      </c>
+      <c r="I71">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1778</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1779</v>
+      </c>
+      <c r="I73">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1781</v>
+      </c>
+      <c r="I74">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H75" t="s">
+        <v>1783</v>
+      </c>
+      <c r="I75">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1784</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1785</v>
+      </c>
+      <c r="I76">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1786</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1787</v>
+      </c>
+      <c r="I77">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1789</v>
+      </c>
+      <c r="I78">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1790</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I79">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1792</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1793</v>
+      </c>
+      <c r="I80">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1794</v>
+      </c>
+      <c r="H81" t="s">
+        <v>1795</v>
+      </c>
+      <c r="I81">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1796</v>
+      </c>
+      <c r="H82" t="s">
+        <v>1797</v>
+      </c>
+      <c r="I82">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H83" t="s">
+        <v>1799</v>
+      </c>
+      <c r="I83">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1800</v>
+      </c>
+      <c r="H84" t="s">
+        <v>1801</v>
+      </c>
+      <c r="I84">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H85" t="s">
+        <v>1803</v>
+      </c>
+      <c r="I85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H86" t="s">
+        <v>1805</v>
+      </c>
+      <c r="I86">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1806</v>
+      </c>
+      <c r="H87" t="s">
+        <v>1807</v>
+      </c>
+      <c r="I87">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1808</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="G89" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1811</v>
+      </c>
+      <c r="I89">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1812</v>
+      </c>
+      <c r="H90" t="s">
+        <v>1813</v>
+      </c>
+      <c r="I90">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H91" t="s">
+        <v>1815</v>
+      </c>
+      <c r="I91">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1817</v>
+      </c>
+      <c r="I92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1818</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1819</v>
+      </c>
+      <c r="I93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1820</v>
+      </c>
+      <c r="H94" t="s">
+        <v>1821</v>
+      </c>
+      <c r="I94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1822</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1823</v>
+      </c>
+      <c r="I95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1825</v>
+      </c>
+      <c r="I96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1826</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1827</v>
+      </c>
+      <c r="I97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1828</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1829</v>
+      </c>
+      <c r="I98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1831</v>
+      </c>
+      <c r="I99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1832</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1833</v>
+      </c>
+      <c r="I100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1835</v>
+      </c>
+      <c r="I101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H102" t="s">
+        <v>1837</v>
+      </c>
+      <c r="I102">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1838</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1839</v>
+      </c>
+      <c r="I103">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="G104" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H104" t="s">
+        <v>1841</v>
+      </c>
+      <c r="I104">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1842</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1843</v>
+      </c>
+      <c r="I105">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="G106" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H106" t="s">
+        <v>1845</v>
+      </c>
+      <c r="I106">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H107" t="s">
+        <v>1847</v>
+      </c>
+      <c r="I107">
         <v>-1</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDACEA55-0CFF-4A5D-B8F4-E1876E23B376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA82E87-87D7-4062-9583-50E01431E671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4885,115 +4885,115 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400812-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000100725-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100729-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000100722_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100728-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406283_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000410414-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100727-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100726-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100001000616_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000111550-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100734-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107651_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100731-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401072_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100733-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105920_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000106102-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100730-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100001030927_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100732-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000104991-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105928_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000107652_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401340_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000107859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000100735-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6244,7 +6244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15218B0-1716-4091-B5E2-97909F624C85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C7DDBE-45F0-4F39-B5E5-B9FE00AB6972}">
   <dimension ref="B2:AG1251"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37431,7 +37431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0FE72D-2ED1-4B36-8CF8-0D15BF6F566A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01772024-7A26-4C6C-B62F-1C67662EDE26}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51692,7 +51692,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F910C9-C19A-4108-AFD5-27C6ED14673E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261B1F34-B63E-467B-9931-4B1BF2BC7A7F}">
   <dimension ref="B2:Q136"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53799,7 +53799,7 @@
         <v>1600</v>
       </c>
       <c r="P100" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="Q100">
         <v>0.95</v>
@@ -53813,7 +53813,7 @@
         <v>1601</v>
       </c>
       <c r="P101" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q101">
         <v>0.85</v>
@@ -53827,10 +53827,10 @@
         <v>1602</v>
       </c>
       <c r="P102" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="Q102">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="103" spans="14:17" x14ac:dyDescent="0.45">
@@ -53855,7 +53855,7 @@
         <v>1604</v>
       </c>
       <c r="P104" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q104">
         <v>0.85</v>
@@ -53869,7 +53869,7 @@
         <v>1605</v>
       </c>
       <c r="P105" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q105">
         <v>0.85</v>
@@ -53883,10 +53883,10 @@
         <v>1606</v>
       </c>
       <c r="P106" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q106">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="107" spans="14:17" x14ac:dyDescent="0.45">
@@ -53897,10 +53897,10 @@
         <v>1607</v>
       </c>
       <c r="P107" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="Q107">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="108" spans="14:17" x14ac:dyDescent="0.45">
@@ -53911,10 +53911,10 @@
         <v>1608</v>
       </c>
       <c r="P108" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="Q108">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="109" spans="14:17" x14ac:dyDescent="0.45">
@@ -53925,7 +53925,7 @@
         <v>1609</v>
       </c>
       <c r="P109" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="Q109">
         <v>0.95</v>
@@ -53939,7 +53939,7 @@
         <v>1610</v>
       </c>
       <c r="P110" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q110">
         <v>0.85</v>
@@ -53967,10 +53967,10 @@
         <v>1612</v>
       </c>
       <c r="P112" t="s">
-        <v>1599</v>
+        <v>1581</v>
       </c>
       <c r="Q112">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="113" spans="14:17" x14ac:dyDescent="0.45">
@@ -53981,10 +53981,10 @@
         <v>1613</v>
       </c>
       <c r="P113" t="s">
-        <v>1586</v>
+        <v>1562</v>
       </c>
       <c r="Q113">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="114" spans="14:17" x14ac:dyDescent="0.45">
@@ -53995,7 +53995,7 @@
         <v>1614</v>
       </c>
       <c r="P114" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q114">
         <v>0.85</v>
@@ -54009,7 +54009,7 @@
         <v>1615</v>
       </c>
       <c r="P115" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="Q115">
         <v>0.85</v>
@@ -54023,7 +54023,7 @@
         <v>1616</v>
       </c>
       <c r="P116" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q116">
         <v>0.85</v>
@@ -54037,7 +54037,7 @@
         <v>1617</v>
       </c>
       <c r="P117" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q117">
         <v>0.85</v>
@@ -54051,10 +54051,10 @@
         <v>1618</v>
       </c>
       <c r="P118" t="s">
-        <v>1594</v>
+        <v>1568</v>
       </c>
       <c r="Q118">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="119" spans="14:17" x14ac:dyDescent="0.45">
@@ -54065,10 +54065,10 @@
         <v>1619</v>
       </c>
       <c r="P119" t="s">
-        <v>1568</v>
+        <v>1595</v>
       </c>
       <c r="Q119">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="120" spans="14:17" x14ac:dyDescent="0.45">
@@ -54079,7 +54079,7 @@
         <v>1620</v>
       </c>
       <c r="P120" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="Q120">
         <v>0.95</v>
@@ -54093,7 +54093,7 @@
         <v>1621</v>
       </c>
       <c r="P121" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="Q121">
         <v>0.85</v>
@@ -54121,7 +54121,7 @@
         <v>1623</v>
       </c>
       <c r="P123" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="Q123">
         <v>0.85</v>
@@ -54135,10 +54135,10 @@
         <v>1624</v>
       </c>
       <c r="P124" t="s">
-        <v>1562</v>
+        <v>1583</v>
       </c>
       <c r="Q124">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="125" spans="14:17" x14ac:dyDescent="0.45">
@@ -54149,10 +54149,10 @@
         <v>1625</v>
       </c>
       <c r="P125" t="s">
-        <v>1568</v>
+        <v>1586</v>
       </c>
       <c r="Q125">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="126" spans="14:17" x14ac:dyDescent="0.45">
@@ -54163,7 +54163,7 @@
         <v>1626</v>
       </c>
       <c r="P126" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q126">
         <v>0.85</v>
@@ -54177,10 +54177,10 @@
         <v>1627</v>
       </c>
       <c r="P127" t="s">
-        <v>1592</v>
+        <v>1579</v>
       </c>
       <c r="Q127">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="128" spans="14:17" x14ac:dyDescent="0.45">
@@ -54191,7 +54191,7 @@
         <v>1628</v>
       </c>
       <c r="P128" t="s">
-        <v>1599</v>
+        <v>1568</v>
       </c>
       <c r="Q128">
         <v>0.85</v>
@@ -54205,7 +54205,7 @@
         <v>1629</v>
       </c>
       <c r="P129" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="Q129">
         <v>0.85</v>
@@ -54219,7 +54219,7 @@
         <v>1630</v>
       </c>
       <c r="P130" t="s">
-        <v>1573</v>
+        <v>1594</v>
       </c>
       <c r="Q130">
         <v>0.95</v>
@@ -54233,10 +54233,10 @@
         <v>1631</v>
       </c>
       <c r="P131" t="s">
-        <v>1595</v>
+        <v>1583</v>
       </c>
       <c r="Q131">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="132" spans="14:17" x14ac:dyDescent="0.45">
@@ -54247,7 +54247,7 @@
         <v>1632</v>
       </c>
       <c r="P132" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="Q132">
         <v>0.85</v>
@@ -54275,7 +54275,7 @@
         <v>1634</v>
       </c>
       <c r="P134" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="Q134">
         <v>0.85</v>
@@ -54289,10 +54289,10 @@
         <v>1635</v>
       </c>
       <c r="P135" t="s">
-        <v>1568</v>
+        <v>1591</v>
       </c>
       <c r="Q135">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="136" spans="14:17" x14ac:dyDescent="0.45">
@@ -54303,10 +54303,10 @@
         <v>1636</v>
       </c>
       <c r="P136" t="s">
-        <v>1591</v>
+        <v>1568</v>
       </c>
       <c r="Q136">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -54315,7 +54315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAC7CE8-9EFF-40B4-9836-F2F1A13F0504}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EBFB5C-BE56-49D1-AFCA-446A91D78348}">
   <dimension ref="A1:I107"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA82E87-87D7-4062-9583-50E01431E671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD99DA0-FCD6-4E03-86E5-A121AFBCAADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="co2_network" sheetId="8" r:id="rId7"/>
     <sheet name="vre agg cap" sheetId="9" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">grids!$H$3:$K$829</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5785,9 +5788,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5825,7 +5828,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5931,7 +5934,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6073,7 +6076,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -25207,7 +25210,7 @@
         <v>403</v>
       </c>
       <c r="J587">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K587" t="s">
         <v>209</v>
@@ -25415,7 +25418,7 @@
         <v>403</v>
       </c>
       <c r="J595">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K595" t="s">
         <v>209</v>
@@ -25701,7 +25704,7 @@
         <v>403</v>
       </c>
       <c r="J606">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K606" t="s">
         <v>209</v>
@@ -25883,7 +25886,7 @@
         <v>403</v>
       </c>
       <c r="J613">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K613" t="s">
         <v>209</v>
@@ -25961,7 +25964,7 @@
         <v>403</v>
       </c>
       <c r="J616">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K616" t="s">
         <v>209</v>
@@ -26455,7 +26458,7 @@
         <v>403</v>
       </c>
       <c r="J635">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K635" t="s">
         <v>209</v>
@@ -26663,7 +26666,7 @@
         <v>403</v>
       </c>
       <c r="J643">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K643" t="s">
         <v>209</v>
@@ -26949,7 +26952,7 @@
         <v>403</v>
       </c>
       <c r="J654">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K654" t="s">
         <v>209</v>
@@ -27131,7 +27134,7 @@
         <v>403</v>
       </c>
       <c r="J661">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K661" t="s">
         <v>209</v>
@@ -27209,7 +27212,7 @@
         <v>403</v>
       </c>
       <c r="J664">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K664" t="s">
         <v>209</v>
@@ -27703,7 +27706,7 @@
         <v>403</v>
       </c>
       <c r="J683">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K683" t="s">
         <v>209</v>
@@ -27911,7 +27914,7 @@
         <v>403</v>
       </c>
       <c r="J691">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K691" t="s">
         <v>209</v>
@@ -28197,7 +28200,7 @@
         <v>403</v>
       </c>
       <c r="J702">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K702" t="s">
         <v>209</v>
@@ -28379,7 +28382,7 @@
         <v>403</v>
       </c>
       <c r="J709">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K709" t="s">
         <v>209</v>
@@ -28457,7 +28460,7 @@
         <v>403</v>
       </c>
       <c r="J712">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K712" t="s">
         <v>209</v>
@@ -28951,7 +28954,7 @@
         <v>403</v>
       </c>
       <c r="J731">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K731" t="s">
         <v>209</v>
@@ -29159,7 +29162,7 @@
         <v>403</v>
       </c>
       <c r="J739">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K739" t="s">
         <v>209</v>
@@ -29445,7 +29448,7 @@
         <v>403</v>
       </c>
       <c r="J750">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K750" t="s">
         <v>209</v>
@@ -29627,7 +29630,7 @@
         <v>403</v>
       </c>
       <c r="J757">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K757" t="s">
         <v>209</v>
@@ -29705,7 +29708,7 @@
         <v>403</v>
       </c>
       <c r="J760">
-        <v>1.216880055244586E-14</v>
+        <v>0</v>
       </c>
       <c r="K760" t="s">
         <v>209</v>
@@ -30199,7 +30202,7 @@
         <v>406</v>
       </c>
       <c r="J779">
-        <v>3.1766272737673782E-5</v>
+        <v>0</v>
       </c>
       <c r="K779" t="s">
         <v>209</v>
@@ -30303,7 +30306,7 @@
         <v>406</v>
       </c>
       <c r="J783">
-        <v>2.3219364488935016E-14</v>
+        <v>0</v>
       </c>
       <c r="K783" t="s">
         <v>209</v>
@@ -30615,7 +30618,7 @@
         <v>406</v>
       </c>
       <c r="J795">
-        <v>6.0452004156822784E-5</v>
+        <v>0</v>
       </c>
       <c r="K795" t="s">
         <v>209</v>
@@ -30771,7 +30774,7 @@
         <v>406</v>
       </c>
       <c r="J801">
-        <v>3.1604428420161466E-6</v>
+        <v>0</v>
       </c>
       <c r="K801" t="s">
         <v>209</v>
@@ -31343,7 +31346,7 @@
         <v>406</v>
       </c>
       <c r="J823">
-        <v>8.3145282183326921E-5</v>
+        <v>0</v>
       </c>
       <c r="K823" t="s">
         <v>209</v>
@@ -31395,7 +31398,7 @@
         <v>406</v>
       </c>
       <c r="J825">
-        <v>4.4691808847567723E-5</v>
+        <v>0</v>
       </c>
       <c r="K825" t="s">
         <v>209</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD99DA0-FCD6-4E03-86E5-A121AFBCAADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F608E8E4-EAB7-4605-8984-5D8D4E895BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25054,7 +25054,7 @@
         <v>403</v>
       </c>
       <c r="J581">
-        <v>1.56248615985588E-4</v>
+        <v>0</v>
       </c>
       <c r="K581" t="s">
         <v>209</v>
@@ -25080,7 +25080,7 @@
         <v>403</v>
       </c>
       <c r="J582">
-        <v>1.7762080207294078E-3</v>
+        <v>0</v>
       </c>
       <c r="K582" t="s">
         <v>209</v>
@@ -25106,7 +25106,7 @@
         <v>403</v>
       </c>
       <c r="J583">
-        <v>3.7670633397113222E-3</v>
+        <v>0</v>
       </c>
       <c r="K583" t="s">
         <v>209</v>
@@ -25132,7 +25132,7 @@
         <v>403</v>
       </c>
       <c r="J584">
-        <v>2.0752915839369001E-4</v>
+        <v>0</v>
       </c>
       <c r="K584" t="s">
         <v>209</v>
@@ -25158,7 +25158,7 @@
         <v>403</v>
       </c>
       <c r="J585">
-        <v>3.3088574983894357E-3</v>
+        <v>0</v>
       </c>
       <c r="K585" t="s">
         <v>209</v>
@@ -25236,7 +25236,7 @@
         <v>403</v>
       </c>
       <c r="J588">
-        <v>8.1234957629163797E-4</v>
+        <v>0</v>
       </c>
       <c r="K588" t="s">
         <v>209</v>
@@ -25262,7 +25262,7 @@
         <v>403</v>
       </c>
       <c r="J589">
-        <v>9.8670293372704197E-4</v>
+        <v>0</v>
       </c>
       <c r="K589" t="s">
         <v>209</v>
@@ -25340,7 +25340,7 @@
         <v>403</v>
       </c>
       <c r="J592">
-        <v>1.1029697386053499E-3</v>
+        <v>0</v>
       </c>
       <c r="K592" t="s">
         <v>209</v>
@@ -25392,7 +25392,7 @@
         <v>403</v>
       </c>
       <c r="J594">
-        <v>3.2313185097092478E-3</v>
+        <v>0</v>
       </c>
       <c r="K594" t="s">
         <v>209</v>
@@ -25496,7 +25496,7 @@
         <v>403</v>
       </c>
       <c r="J598">
-        <v>3.3658293889246598E-4</v>
+        <v>0</v>
       </c>
       <c r="K598" t="s">
         <v>209</v>
@@ -25522,7 +25522,7 @@
         <v>403</v>
       </c>
       <c r="J599">
-        <v>1.8366066455004798E-4</v>
+        <v>0</v>
       </c>
       <c r="K599" t="s">
         <v>209</v>
@@ -25652,7 +25652,7 @@
         <v>403</v>
       </c>
       <c r="J604">
-        <v>3.879099661077634E-3</v>
+        <v>0</v>
       </c>
       <c r="K604" t="s">
         <v>209</v>
@@ -25730,7 +25730,7 @@
         <v>403</v>
       </c>
       <c r="J607">
-        <v>1.686144294080638E-3</v>
+        <v>0</v>
       </c>
       <c r="K607" t="s">
         <v>209</v>
@@ -25912,7 +25912,7 @@
         <v>403</v>
       </c>
       <c r="J614">
-        <v>4.5595899398908606E-3</v>
+        <v>0</v>
       </c>
       <c r="K614" t="s">
         <v>209</v>
@@ -26042,7 +26042,7 @@
         <v>403</v>
       </c>
       <c r="J619">
-        <v>1.16238816649158E-4</v>
+        <v>0</v>
       </c>
       <c r="K619" t="s">
         <v>209</v>
@@ -26094,7 +26094,7 @@
         <v>403</v>
       </c>
       <c r="J621">
-        <v>4.6582046827972601E-4</v>
+        <v>0</v>
       </c>
       <c r="K621" t="s">
         <v>209</v>
@@ -26172,7 +26172,7 @@
         <v>403</v>
       </c>
       <c r="J624">
-        <v>4.6568539459356596E-4</v>
+        <v>0</v>
       </c>
       <c r="K624" t="s">
         <v>209</v>
@@ -26198,7 +26198,7 @@
         <v>403</v>
       </c>
       <c r="J625">
-        <v>2.1574188188649599E-4</v>
+        <v>0</v>
       </c>
       <c r="K625" t="s">
         <v>209</v>
@@ -26302,7 +26302,7 @@
         <v>403</v>
       </c>
       <c r="J629">
-        <v>1.56248615985588E-4</v>
+        <v>0</v>
       </c>
       <c r="K629" t="s">
         <v>209</v>
@@ -26328,7 +26328,7 @@
         <v>403</v>
       </c>
       <c r="J630">
-        <v>1.7762080207294078E-3</v>
+        <v>0</v>
       </c>
       <c r="K630" t="s">
         <v>209</v>
@@ -26354,7 +26354,7 @@
         <v>403</v>
       </c>
       <c r="J631">
-        <v>3.7670633397113222E-3</v>
+        <v>0</v>
       </c>
       <c r="K631" t="s">
         <v>209</v>
@@ -26380,7 +26380,7 @@
         <v>403</v>
       </c>
       <c r="J632">
-        <v>2.0752915839369001E-4</v>
+        <v>0</v>
       </c>
       <c r="K632" t="s">
         <v>209</v>
@@ -26406,7 +26406,7 @@
         <v>403</v>
       </c>
       <c r="J633">
-        <v>3.3088574983894357E-3</v>
+        <v>0</v>
       </c>
       <c r="K633" t="s">
         <v>209</v>
@@ -26484,7 +26484,7 @@
         <v>403</v>
       </c>
       <c r="J636">
-        <v>8.1234957629163797E-4</v>
+        <v>0</v>
       </c>
       <c r="K636" t="s">
         <v>209</v>
@@ -26510,7 +26510,7 @@
         <v>403</v>
       </c>
       <c r="J637">
-        <v>9.8670293372704197E-4</v>
+        <v>0</v>
       </c>
       <c r="K637" t="s">
         <v>209</v>
@@ -26588,7 +26588,7 @@
         <v>403</v>
       </c>
       <c r="J640">
-        <v>1.1029697386053499E-3</v>
+        <v>0</v>
       </c>
       <c r="K640" t="s">
         <v>209</v>
@@ -26640,7 +26640,7 @@
         <v>403</v>
       </c>
       <c r="J642">
-        <v>3.2313185097092478E-3</v>
+        <v>0</v>
       </c>
       <c r="K642" t="s">
         <v>209</v>
@@ -26744,7 +26744,7 @@
         <v>403</v>
       </c>
       <c r="J646">
-        <v>3.3658293889246598E-4</v>
+        <v>0</v>
       </c>
       <c r="K646" t="s">
         <v>209</v>
@@ -26770,7 +26770,7 @@
         <v>403</v>
       </c>
       <c r="J647">
-        <v>1.8366066455004798E-4</v>
+        <v>0</v>
       </c>
       <c r="K647" t="s">
         <v>209</v>
@@ -26900,7 +26900,7 @@
         <v>403</v>
       </c>
       <c r="J652">
-        <v>3.879099661077634E-3</v>
+        <v>0</v>
       </c>
       <c r="K652" t="s">
         <v>209</v>
@@ -26978,7 +26978,7 @@
         <v>403</v>
       </c>
       <c r="J655">
-        <v>1.686144294080638E-3</v>
+        <v>0</v>
       </c>
       <c r="K655" t="s">
         <v>209</v>
@@ -27160,7 +27160,7 @@
         <v>403</v>
       </c>
       <c r="J662">
-        <v>4.5595899398908606E-3</v>
+        <v>0</v>
       </c>
       <c r="K662" t="s">
         <v>209</v>
@@ -27290,7 +27290,7 @@
         <v>403</v>
       </c>
       <c r="J667">
-        <v>1.16238816649158E-4</v>
+        <v>0</v>
       </c>
       <c r="K667" t="s">
         <v>209</v>
@@ -27342,7 +27342,7 @@
         <v>403</v>
       </c>
       <c r="J669">
-        <v>4.6582046827972601E-4</v>
+        <v>0</v>
       </c>
       <c r="K669" t="s">
         <v>209</v>
@@ -27420,7 +27420,7 @@
         <v>403</v>
       </c>
       <c r="J672">
-        <v>4.6568539459356596E-4</v>
+        <v>0</v>
       </c>
       <c r="K672" t="s">
         <v>209</v>
@@ -27446,7 +27446,7 @@
         <v>403</v>
       </c>
       <c r="J673">
-        <v>2.1574188188649599E-4</v>
+        <v>0</v>
       </c>
       <c r="K673" t="s">
         <v>209</v>
@@ -27550,7 +27550,7 @@
         <v>403</v>
       </c>
       <c r="J677">
-        <v>1.56248615985588E-4</v>
+        <v>0</v>
       </c>
       <c r="K677" t="s">
         <v>209</v>
@@ -27576,7 +27576,7 @@
         <v>403</v>
       </c>
       <c r="J678">
-        <v>1.7762080207294078E-3</v>
+        <v>0</v>
       </c>
       <c r="K678" t="s">
         <v>209</v>
@@ -27602,7 +27602,7 @@
         <v>403</v>
       </c>
       <c r="J679">
-        <v>3.7670633397113222E-3</v>
+        <v>0</v>
       </c>
       <c r="K679" t="s">
         <v>209</v>
@@ -27628,7 +27628,7 @@
         <v>403</v>
       </c>
       <c r="J680">
-        <v>2.0752915839369001E-4</v>
+        <v>0</v>
       </c>
       <c r="K680" t="s">
         <v>209</v>
@@ -27654,7 +27654,7 @@
         <v>403</v>
       </c>
       <c r="J681">
-        <v>3.3088574983894357E-3</v>
+        <v>0</v>
       </c>
       <c r="K681" t="s">
         <v>209</v>
@@ -27732,7 +27732,7 @@
         <v>403</v>
       </c>
       <c r="J684">
-        <v>8.1234957629163797E-4</v>
+        <v>0</v>
       </c>
       <c r="K684" t="s">
         <v>209</v>
@@ -27758,7 +27758,7 @@
         <v>403</v>
       </c>
       <c r="J685">
-        <v>9.8670293372704197E-4</v>
+        <v>0</v>
       </c>
       <c r="K685" t="s">
         <v>209</v>
@@ -27836,7 +27836,7 @@
         <v>403</v>
       </c>
       <c r="J688">
-        <v>1.1029697386053499E-3</v>
+        <v>0</v>
       </c>
       <c r="K688" t="s">
         <v>209</v>
@@ -27888,7 +27888,7 @@
         <v>403</v>
       </c>
       <c r="J690">
-        <v>3.2313185097092478E-3</v>
+        <v>0</v>
       </c>
       <c r="K690" t="s">
         <v>209</v>
@@ -27992,7 +27992,7 @@
         <v>403</v>
       </c>
       <c r="J694">
-        <v>3.3658293889246598E-4</v>
+        <v>0</v>
       </c>
       <c r="K694" t="s">
         <v>209</v>
@@ -28018,7 +28018,7 @@
         <v>403</v>
       </c>
       <c r="J695">
-        <v>1.8366066455004798E-4</v>
+        <v>0</v>
       </c>
       <c r="K695" t="s">
         <v>209</v>
@@ -28148,7 +28148,7 @@
         <v>403</v>
       </c>
       <c r="J700">
-        <v>3.879099661077634E-3</v>
+        <v>0</v>
       </c>
       <c r="K700" t="s">
         <v>209</v>
@@ -28226,7 +28226,7 @@
         <v>403</v>
       </c>
       <c r="J703">
-        <v>1.686144294080638E-3</v>
+        <v>0</v>
       </c>
       <c r="K703" t="s">
         <v>209</v>
@@ -28408,7 +28408,7 @@
         <v>403</v>
       </c>
       <c r="J710">
-        <v>4.5595899398908606E-3</v>
+        <v>0</v>
       </c>
       <c r="K710" t="s">
         <v>209</v>
@@ -28538,7 +28538,7 @@
         <v>403</v>
       </c>
       <c r="J715">
-        <v>1.16238816649158E-4</v>
+        <v>0</v>
       </c>
       <c r="K715" t="s">
         <v>209</v>
@@ -28590,7 +28590,7 @@
         <v>403</v>
       </c>
       <c r="J717">
-        <v>4.6582046827972601E-4</v>
+        <v>0</v>
       </c>
       <c r="K717" t="s">
         <v>209</v>
@@ -28668,7 +28668,7 @@
         <v>403</v>
       </c>
       <c r="J720">
-        <v>4.6568539459356596E-4</v>
+        <v>0</v>
       </c>
       <c r="K720" t="s">
         <v>209</v>
@@ -28694,7 +28694,7 @@
         <v>403</v>
       </c>
       <c r="J721">
-        <v>2.1574188188649599E-4</v>
+        <v>0</v>
       </c>
       <c r="K721" t="s">
         <v>209</v>
@@ -28798,7 +28798,7 @@
         <v>403</v>
       </c>
       <c r="J725">
-        <v>1.56248615985588E-4</v>
+        <v>0</v>
       </c>
       <c r="K725" t="s">
         <v>209</v>
@@ -28824,7 +28824,7 @@
         <v>403</v>
       </c>
       <c r="J726">
-        <v>1.7762080207294078E-3</v>
+        <v>0</v>
       </c>
       <c r="K726" t="s">
         <v>209</v>
@@ -28850,7 +28850,7 @@
         <v>403</v>
       </c>
       <c r="J727">
-        <v>3.7670633397113222E-3</v>
+        <v>0</v>
       </c>
       <c r="K727" t="s">
         <v>209</v>
@@ -28876,7 +28876,7 @@
         <v>403</v>
       </c>
       <c r="J728">
-        <v>2.0752915839369001E-4</v>
+        <v>0</v>
       </c>
       <c r="K728" t="s">
         <v>209</v>
@@ -28902,7 +28902,7 @@
         <v>403</v>
       </c>
       <c r="J729">
-        <v>3.3088574983894357E-3</v>
+        <v>0</v>
       </c>
       <c r="K729" t="s">
         <v>209</v>
@@ -28980,7 +28980,7 @@
         <v>403</v>
       </c>
       <c r="J732">
-        <v>8.1234957629163797E-4</v>
+        <v>0</v>
       </c>
       <c r="K732" t="s">
         <v>209</v>
@@ -29006,7 +29006,7 @@
         <v>403</v>
       </c>
       <c r="J733">
-        <v>9.8670293372704197E-4</v>
+        <v>0</v>
       </c>
       <c r="K733" t="s">
         <v>209</v>
@@ -29084,7 +29084,7 @@
         <v>403</v>
       </c>
       <c r="J736">
-        <v>1.1029697386053499E-3</v>
+        <v>0</v>
       </c>
       <c r="K736" t="s">
         <v>209</v>
@@ -29136,7 +29136,7 @@
         <v>403</v>
       </c>
       <c r="J738">
-        <v>3.2313185097092478E-3</v>
+        <v>0</v>
       </c>
       <c r="K738" t="s">
         <v>209</v>
@@ -29240,7 +29240,7 @@
         <v>403</v>
       </c>
       <c r="J742">
-        <v>3.3658293889246598E-4</v>
+        <v>0</v>
       </c>
       <c r="K742" t="s">
         <v>209</v>
@@ -29266,7 +29266,7 @@
         <v>403</v>
       </c>
       <c r="J743">
-        <v>1.8366066455004798E-4</v>
+        <v>0</v>
       </c>
       <c r="K743" t="s">
         <v>209</v>
@@ -29396,7 +29396,7 @@
         <v>403</v>
       </c>
       <c r="J748">
-        <v>3.879099661077634E-3</v>
+        <v>0</v>
       </c>
       <c r="K748" t="s">
         <v>209</v>
@@ -29474,7 +29474,7 @@
         <v>403</v>
       </c>
       <c r="J751">
-        <v>1.686144294080638E-3</v>
+        <v>0</v>
       </c>
       <c r="K751" t="s">
         <v>209</v>
@@ -29656,7 +29656,7 @@
         <v>403</v>
       </c>
       <c r="J758">
-        <v>4.5595899398908606E-3</v>
+        <v>0</v>
       </c>
       <c r="K758" t="s">
         <v>209</v>
@@ -29786,7 +29786,7 @@
         <v>403</v>
       </c>
       <c r="J763">
-        <v>1.16238816649158E-4</v>
+        <v>0</v>
       </c>
       <c r="K763" t="s">
         <v>209</v>
@@ -29838,7 +29838,7 @@
         <v>403</v>
       </c>
       <c r="J765">
-        <v>4.6582046827972601E-4</v>
+        <v>0</v>
       </c>
       <c r="K765" t="s">
         <v>209</v>
@@ -29916,7 +29916,7 @@
         <v>403</v>
       </c>
       <c r="J768">
-        <v>4.6568539459356596E-4</v>
+        <v>0</v>
       </c>
       <c r="K768" t="s">
         <v>209</v>
@@ -29942,7 +29942,7 @@
         <v>403</v>
       </c>
       <c r="J769">
-        <v>2.1574188188649599E-4</v>
+        <v>0</v>
       </c>
       <c r="K769" t="s">
         <v>209</v>
@@ -30020,7 +30020,7 @@
         <v>405</v>
       </c>
       <c r="J772">
-        <v>3.9428613757716002E-3</v>
+        <v>0</v>
       </c>
       <c r="K772" t="s">
         <v>209</v>
@@ -30046,7 +30046,7 @@
         <v>406</v>
       </c>
       <c r="J773">
-        <v>1.9851137780628001E-3</v>
+        <v>0</v>
       </c>
       <c r="K773" t="s">
         <v>209</v>
@@ -30072,7 +30072,7 @@
         <v>405</v>
       </c>
       <c r="J774">
-        <v>4.8023107872191004E-3</v>
+        <v>0</v>
       </c>
       <c r="K774" t="s">
         <v>209</v>
@@ -30098,7 +30098,7 @@
         <v>406</v>
       </c>
       <c r="J775">
-        <v>2.2593570491199E-3</v>
+        <v>0</v>
       </c>
       <c r="K775" t="s">
         <v>209</v>
@@ -30384,7 +30384,7 @@
         <v>405</v>
       </c>
       <c r="J786">
-        <v>3.8102369187982999E-3</v>
+        <v>0</v>
       </c>
       <c r="K786" t="s">
         <v>209</v>
@@ -30410,7 +30410,7 @@
         <v>406</v>
       </c>
       <c r="J787">
-        <v>3.2023451034527998E-3</v>
+        <v>0</v>
       </c>
       <c r="K787" t="s">
         <v>209</v>
@@ -30644,7 +30644,7 @@
         <v>405</v>
       </c>
       <c r="J796">
-        <v>1.6909781829823E-3</v>
+        <v>0</v>
       </c>
       <c r="K796" t="s">
         <v>209</v>
@@ -30670,7 +30670,7 @@
         <v>406</v>
       </c>
       <c r="J797">
-        <v>2.1829117424150001E-4</v>
+        <v>0</v>
       </c>
       <c r="K797" t="s">
         <v>209</v>
@@ -30696,7 +30696,7 @@
         <v>405</v>
       </c>
       <c r="J798">
-        <v>3.569910180092E-4</v>
+        <v>0</v>
       </c>
       <c r="K798" t="s">
         <v>209</v>
@@ -30722,7 +30722,7 @@
         <v>406</v>
       </c>
       <c r="J799">
-        <v>5.8907049311150001E-4</v>
+        <v>0</v>
       </c>
       <c r="K799" t="s">
         <v>209</v>
@@ -30748,7 +30748,7 @@
         <v>405</v>
       </c>
       <c r="J800">
-        <v>2.089474727021E-4</v>
+        <v>0</v>
       </c>
       <c r="K800" t="s">
         <v>209</v>
@@ -30904,7 +30904,7 @@
         <v>405</v>
       </c>
       <c r="J806">
-        <v>2.2749706629629001E-3</v>
+        <v>0</v>
       </c>
       <c r="K806" t="s">
         <v>209</v>
@@ -30930,7 +30930,7 @@
         <v>406</v>
       </c>
       <c r="J807">
-        <v>3.7169106823590001E-4</v>
+        <v>0</v>
       </c>
       <c r="K807" t="s">
         <v>209</v>
@@ -31034,7 +31034,7 @@
         <v>406</v>
       </c>
       <c r="J811">
-        <v>2.5226756115567998E-3</v>
+        <v>0</v>
       </c>
       <c r="K811" t="s">
         <v>209</v>
@@ -31060,7 +31060,7 @@
         <v>405</v>
       </c>
       <c r="J812">
-        <v>1.3221557731659E-3</v>
+        <v>0</v>
       </c>
       <c r="K812" t="s">
         <v>209</v>
@@ -31086,7 +31086,7 @@
         <v>406</v>
       </c>
       <c r="J813">
-        <v>2.6731192694199999E-4</v>
+        <v>0</v>
       </c>
       <c r="K813" t="s">
         <v>209</v>
@@ -31138,7 +31138,7 @@
         <v>406</v>
       </c>
       <c r="J815">
-        <v>2.0690562488760001E-4</v>
+        <v>0</v>
       </c>
       <c r="K815" t="s">
         <v>209</v>
@@ -31268,7 +31268,7 @@
         <v>405</v>
       </c>
       <c r="J820">
-        <v>2.7560721986664002E-3</v>
+        <v>0</v>
       </c>
       <c r="K820" t="s">
         <v>209</v>
@@ -31320,7 +31320,7 @@
         <v>405</v>
       </c>
       <c r="J822">
-        <v>1.5456674208639001E-3</v>
+        <v>0</v>
       </c>
       <c r="K822" t="s">
         <v>209</v>
@@ -31372,7 +31372,7 @@
         <v>405</v>
       </c>
       <c r="J824">
-        <v>3.2493263348597999E-3</v>
+        <v>0</v>
       </c>
       <c r="K824" t="s">
         <v>209</v>
@@ -31502,7 +31502,7 @@
         <v>406</v>
       </c>
       <c r="J829">
-        <v>1.3415578861402E-3</v>
+        <v>0</v>
       </c>
       <c r="K829" t="s">
         <v>209</v>
